--- a/Vehicle Catalogue.xlsx
+++ b/Vehicle Catalogue.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Games\Tank Conversion Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samhi\Documents\My Games\Sprocket\Ostfront Tank Collection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E655E29-A86B-4BB1-BF68-CE5E10BE9718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1164B612-E385-4CF7-80AA-EB9772E2BEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15360" xr2:uid="{3FAC36FE-B102-4B04-8548-70F58966D145}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{3FAC36FE-B102-4B04-8548-70F58966D145}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="570">
   <si>
     <t>Tank</t>
   </si>
@@ -266,9 +266,6 @@
     <t>Matilda I</t>
   </si>
   <si>
-    <t>Otsu-Gata Sensha</t>
-  </si>
-  <si>
     <t>Panzer I Ausf. B</t>
   </si>
   <si>
@@ -737,12 +734,6 @@
     <t>Vickers Infantry Tank No. 1</t>
   </si>
   <si>
-    <t>Vickers Medium Mk I</t>
-  </si>
-  <si>
-    <t>Vickers Medium Mk III</t>
-  </si>
-  <si>
     <t>Wolverine Mk I</t>
   </si>
   <si>
@@ -821,9 +812,6 @@
     <t>T95</t>
   </si>
   <si>
-    <t>Light Tank Mk VI</t>
-  </si>
-  <si>
     <t>M19 GMC</t>
   </si>
   <si>
@@ -842,12 +830,6 @@
     <t>Churchill Kangaroo</t>
   </si>
   <si>
-    <t>AMX 13</t>
-  </si>
-  <si>
-    <t>AMX 50</t>
-  </si>
-  <si>
     <t>14TP</t>
   </si>
   <si>
@@ -921,6 +903,855 @@
   </si>
   <si>
     <t>43M Toldi III</t>
+  </si>
+  <si>
+    <t>39M Csaba</t>
+  </si>
+  <si>
+    <t>Armoured Car</t>
+  </si>
+  <si>
+    <t>40M Csaba</t>
+  </si>
+  <si>
+    <t>AB43</t>
+  </si>
+  <si>
+    <t>AEC AA</t>
+  </si>
+  <si>
+    <t>AM 39 Gendron-Somua</t>
+  </si>
+  <si>
+    <t>BA-64</t>
+  </si>
+  <si>
+    <t>Braat Overvalwagen</t>
+  </si>
+  <si>
+    <t>Dutch</t>
+  </si>
+  <si>
+    <t>Daimler Dingo</t>
+  </si>
+  <si>
+    <t>Daimler Mk I</t>
+  </si>
+  <si>
+    <t>Daimler Mk II</t>
+  </si>
+  <si>
+    <t>De Dion-Bouton Autocanon</t>
+  </si>
+  <si>
+    <t>FAI-M</t>
+  </si>
+  <si>
+    <t>Humber LRC Mk II</t>
+  </si>
+  <si>
+    <t>Humber LRC Mk III</t>
+  </si>
+  <si>
+    <t>Humber Mk II</t>
+  </si>
+  <si>
+    <t>Humber Mk IV</t>
+  </si>
+  <si>
+    <t>Humber Scout</t>
+  </si>
+  <si>
+    <t>Kfz. 13</t>
+  </si>
+  <si>
+    <t>Kfz. 14</t>
+  </si>
+  <si>
+    <t>Laffly S15TOE</t>
+  </si>
+  <si>
+    <t>Landsverk L-182</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>M20 Armored Utility Car</t>
+  </si>
+  <si>
+    <t>M8 Greyhound</t>
+  </si>
+  <si>
+    <t>Morris CS9</t>
+  </si>
+  <si>
+    <t>Panhard 178</t>
+  </si>
+  <si>
+    <t>Sd.Kfz. 221</t>
+  </si>
+  <si>
+    <t>Sd.Kfz. 222</t>
+  </si>
+  <si>
+    <t>Sd.Kfz. 231</t>
+  </si>
+  <si>
+    <t>Sd.Kfz. 234/1</t>
+  </si>
+  <si>
+    <t>Sd.Kfz. 234/2 "Puma"</t>
+  </si>
+  <si>
+    <t>Sd.Kfz. 234/3</t>
+  </si>
+  <si>
+    <t>Sd.Kfz. 234/4 "Pakwagen"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staghound Mk AA </t>
+  </si>
+  <si>
+    <t>Staghound Mk I</t>
+  </si>
+  <si>
+    <t>Staghound Mk II</t>
+  </si>
+  <si>
+    <t>Staghound Mk III</t>
+  </si>
+  <si>
+    <t>Type 87 Armoured Car</t>
+  </si>
+  <si>
+    <t>Type 93 Armoured Car</t>
+  </si>
+  <si>
+    <t>Wz.29 Ursus</t>
+  </si>
+  <si>
+    <t>Wz.34 Ursus</t>
+  </si>
+  <si>
+    <t>AS.42 Sahariana</t>
+  </si>
+  <si>
+    <t>Car</t>
+  </si>
+  <si>
+    <t>AS37</t>
+  </si>
+  <si>
+    <t>Citroën 7CV</t>
+  </si>
+  <si>
+    <t>Citroën Traction Avant 11CV</t>
+  </si>
+  <si>
+    <t>Dodge WC51</t>
+  </si>
+  <si>
+    <t>Dodge WC52</t>
+  </si>
+  <si>
+    <t>Dodge WC55</t>
+  </si>
+  <si>
+    <t>Ford GPA</t>
+  </si>
+  <si>
+    <t>GAZ-67</t>
+  </si>
+  <si>
+    <t>GAZ-67B</t>
+  </si>
+  <si>
+    <t>Kfz. 15</t>
+  </si>
+  <si>
+    <t>Laffly V15T</t>
+  </si>
+  <si>
+    <t>M3A1 Scout</t>
+  </si>
+  <si>
+    <t>M3A1 Scout Car</t>
+  </si>
+  <si>
+    <t>M6 GMC</t>
+  </si>
+  <si>
+    <t>Polski Fiat 508 "Łazik"</t>
+  </si>
+  <si>
+    <t>SPA-Viberti AS.42</t>
+  </si>
+  <si>
+    <t>Type 95 Kurogane Scout Car</t>
+  </si>
+  <si>
+    <t>Volkswagen Kübelwagen</t>
+  </si>
+  <si>
+    <t>Volkswagen Schwimmwagen</t>
+  </si>
+  <si>
+    <t>VW Type 87 "Beetle"</t>
+  </si>
+  <si>
+    <t>Willys MB Jeep</t>
+  </si>
+  <si>
+    <t>A33 Excelsior</t>
+  </si>
+  <si>
+    <t>ARL V39</t>
+  </si>
+  <si>
+    <t>AT 15</t>
+  </si>
+  <si>
+    <t>AT 8</t>
+  </si>
+  <si>
+    <t>BDR G1 B</t>
+  </si>
+  <si>
+    <t>Carro d'assalto P.88</t>
+  </si>
+  <si>
+    <t>Chi-Se</t>
+  </si>
+  <si>
+    <t>Durchbruchswagen II</t>
+  </si>
+  <si>
+    <t>E 75</t>
+  </si>
+  <si>
+    <t>FV201 (A45)</t>
+  </si>
+  <si>
+    <t>G.W. E 100</t>
+  </si>
+  <si>
+    <t>G.W. Tiger</t>
+  </si>
+  <si>
+    <t>Grille 15</t>
+  </si>
+  <si>
+    <t>Jagdpanther II</t>
+  </si>
+  <si>
+    <t>KV-220</t>
+  </si>
+  <si>
+    <t>KV-4</t>
+  </si>
+  <si>
+    <t>Mäuschen</t>
+  </si>
+  <si>
+    <t>Object 212</t>
+  </si>
+  <si>
+    <t>Object 244</t>
+  </si>
+  <si>
+    <t>Object 704</t>
+  </si>
+  <si>
+    <t>Object-257-2</t>
+  </si>
+  <si>
+    <t>Object-705</t>
+  </si>
+  <si>
+    <t>O-Ho</t>
+  </si>
+  <si>
+    <t>Pawlack</t>
+  </si>
+  <si>
+    <t>Porsche Tiger</t>
+  </si>
+  <si>
+    <t>ST-I</t>
+  </si>
+  <si>
+    <t>ST-II</t>
+  </si>
+  <si>
+    <t>SU-100M1</t>
+  </si>
+  <si>
+    <t>SU-101</t>
+  </si>
+  <si>
+    <t>SU-122-44</t>
+  </si>
+  <si>
+    <t>SU-2-122</t>
+  </si>
+  <si>
+    <t>T-103</t>
+  </si>
+  <si>
+    <t>T14</t>
+  </si>
+  <si>
+    <t>T-150</t>
+  </si>
+  <si>
+    <t>T26E5</t>
+  </si>
+  <si>
+    <t>T28 Concept</t>
+  </si>
+  <si>
+    <t>T32</t>
+  </si>
+  <si>
+    <t>Type 4 Heavy</t>
+  </si>
+  <si>
+    <t>Type 5 Ka-Ri</t>
+  </si>
+  <si>
+    <t>VK 100.01 (P)</t>
+  </si>
+  <si>
+    <t>VK 30.01 (P)</t>
+  </si>
+  <si>
+    <t>VK 30.02 (D)</t>
+  </si>
+  <si>
+    <t>VK 36.01 (H)</t>
+  </si>
+  <si>
+    <t>VK 45.02 (P) Ausf. A</t>
+  </si>
+  <si>
+    <t>VK 65.01 (H)</t>
+  </si>
+  <si>
+    <t>Vz. 44-1</t>
+  </si>
+  <si>
+    <t>Waffenträger auf Pz. IV</t>
+  </si>
+  <si>
+    <t>Wz.40</t>
+  </si>
+  <si>
+    <t>4TP</t>
+  </si>
+  <si>
+    <t>A-20</t>
+  </si>
+  <si>
+    <t>AMR P.103</t>
+  </si>
+  <si>
+    <t>AMX 40</t>
+  </si>
+  <si>
+    <t>AT-1</t>
+  </si>
+  <si>
+    <t>BT-SV</t>
+  </si>
+  <si>
+    <t>Convertible Medium Tank T3</t>
+  </si>
+  <si>
+    <t>FCM 36 Pak 40</t>
+  </si>
+  <si>
+    <t>G.Pz. Mk. VI (e)</t>
+  </si>
+  <si>
+    <t>Harry Hopkins Mk 1 CS Alecto</t>
+  </si>
+  <si>
+    <t>Kolohousenka</t>
+  </si>
+  <si>
+    <t>Lago M38</t>
+  </si>
+  <si>
+    <t>Landsverk L-60</t>
+  </si>
+  <si>
+    <t>Leichttraktor</t>
+  </si>
+  <si>
+    <t>Light Tank Mk. VIC</t>
+  </si>
+  <si>
+    <t>Loyd Gun Carriage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LTTB </t>
+  </si>
+  <si>
+    <t>M37 SPG</t>
+  </si>
+  <si>
+    <t>M41 HMC</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>M8A1</t>
+  </si>
+  <si>
+    <t>MKA</t>
+  </si>
+  <si>
+    <t>MS-1</t>
+  </si>
+  <si>
+    <t>MT-25</t>
+  </si>
+  <si>
+    <t>Panzerwagen 39</t>
+  </si>
+  <si>
+    <t>Pvlvv fm-42</t>
+  </si>
+  <si>
+    <t>Pz.Kpfw. 38 n.A</t>
+  </si>
+  <si>
+    <t>Pz.Kpfw. II Ausf. D</t>
+  </si>
+  <si>
+    <t>Renault FT 75 BS</t>
+  </si>
+  <si>
+    <t>Renault FT AC</t>
+  </si>
+  <si>
+    <t>Renault UE 57</t>
+  </si>
+  <si>
+    <t>Sav m-43</t>
+  </si>
+  <si>
+    <t>Škoda T 15A</t>
+  </si>
+  <si>
+    <t>Škoda T 17</t>
+  </si>
+  <si>
+    <t>Straussler V-4-40</t>
+  </si>
+  <si>
+    <t>Strv m-21-29</t>
+  </si>
+  <si>
+    <t>Strv m-31</t>
+  </si>
+  <si>
+    <t>Strv m-38</t>
+  </si>
+  <si>
+    <t>Strv m-40L</t>
+  </si>
+  <si>
+    <t>SU-18</t>
+  </si>
+  <si>
+    <t>T1 HMC</t>
+  </si>
+  <si>
+    <t>T-116</t>
+  </si>
+  <si>
+    <t>T-127</t>
+  </si>
+  <si>
+    <t>T18 HMC</t>
+  </si>
+  <si>
+    <t>T1E6</t>
+  </si>
+  <si>
+    <t>T2 Light Tank</t>
+  </si>
+  <si>
+    <t>T21</t>
+  </si>
+  <si>
+    <t>T40</t>
+  </si>
+  <si>
+    <t>T-45</t>
+  </si>
+  <si>
+    <t>T-46</t>
+  </si>
+  <si>
+    <t>T-50-2</t>
+  </si>
+  <si>
+    <t>T56 GMC</t>
+  </si>
+  <si>
+    <t>T67</t>
+  </si>
+  <si>
+    <t>T7 Combat Car</t>
+  </si>
+  <si>
+    <t>T82</t>
+  </si>
+  <si>
+    <t>Type 1 Ho-Ni II</t>
+  </si>
+  <si>
+    <t>Type 5 Ke-Ho</t>
+  </si>
+  <si>
+    <t>Type 97 Chi-Ni</t>
+  </si>
+  <si>
+    <t>VK 28.01</t>
+  </si>
+  <si>
+    <t>VK 28.01 mit 10,5 cm L-28</t>
+  </si>
+  <si>
+    <t>25TP KSUST II</t>
+  </si>
+  <si>
+    <t>A24 Cavalier</t>
+  </si>
+  <si>
+    <t>A24 Cruiser Mk VII Cavalier</t>
+  </si>
+  <si>
+    <t>A-32</t>
+  </si>
+  <si>
+    <t>A38 Valiant</t>
+  </si>
+  <si>
+    <t>A-44</t>
+  </si>
+  <si>
+    <t>A7E3</t>
+  </si>
+  <si>
+    <t>AC 1 Sentinel</t>
+  </si>
+  <si>
+    <t>AC 4 Sentinel</t>
+  </si>
+  <si>
+    <t>AT 2</t>
+  </si>
+  <si>
+    <t>AT 7</t>
+  </si>
+  <si>
+    <t>Birch Gun</t>
+  </si>
+  <si>
+    <t>Borsig</t>
+  </si>
+  <si>
+    <t>Carro Armato P.43</t>
+  </si>
+  <si>
+    <t>Carro Armato P.43 bis</t>
+  </si>
+  <si>
+    <t>Convertible Medium Tank T3E2</t>
+  </si>
+  <si>
+    <t>DS PZInż</t>
+  </si>
+  <si>
+    <t>Grosstraktor</t>
+  </si>
+  <si>
+    <t>Ikv 72</t>
+  </si>
+  <si>
+    <t>IT-3</t>
+  </si>
+  <si>
+    <t>Krupp-Steyr Waffenträger</t>
+  </si>
+  <si>
+    <t>Lago</t>
+  </si>
+  <si>
+    <t>LTG</t>
+  </si>
+  <si>
+    <t>M10 RBFM</t>
+  </si>
+  <si>
+    <t>M16-43 Sahariano</t>
+  </si>
+  <si>
+    <t>M2 Medium</t>
+  </si>
+  <si>
+    <t>M4 Improved</t>
+  </si>
+  <si>
+    <t>M40-M43</t>
+  </si>
+  <si>
+    <t>M46 Patton</t>
+  </si>
+  <si>
+    <t>P.44 Pantera</t>
+  </si>
+  <si>
+    <t>Pz.Kpfw. 38 (K)</t>
+  </si>
+  <si>
+    <t>Pz.Kpfw. T 25</t>
+  </si>
+  <si>
+    <t>Pz.Sfl. IC</t>
+  </si>
+  <si>
+    <t>Pz.Sfl. IVb</t>
+  </si>
+  <si>
+    <t>Pz.Sfl. IVc</t>
+  </si>
+  <si>
+    <t>Ram II</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Renault G1 R</t>
+  </si>
+  <si>
+    <t>Rheinmetall Skorpion G</t>
+  </si>
+  <si>
+    <t>S-51 SPG</t>
+  </si>
+  <si>
+    <t>SARL 42</t>
+  </si>
+  <si>
+    <t>Sexton I</t>
+  </si>
+  <si>
+    <t>Škoda T 24</t>
+  </si>
+  <si>
+    <t>Škoda T 25</t>
+  </si>
+  <si>
+    <t>SOMUA S35 CA</t>
+  </si>
+  <si>
+    <t>ST vz. 39</t>
+  </si>
+  <si>
+    <t>Strv m-42</t>
+  </si>
+  <si>
+    <t>SU-8</t>
+  </si>
+  <si>
+    <t>T-115</t>
+  </si>
+  <si>
+    <t>T2 Medium</t>
+  </si>
+  <si>
+    <t>T20</t>
+  </si>
+  <si>
+    <t>T23E3</t>
+  </si>
+  <si>
+    <t>T-43</t>
+  </si>
+  <si>
+    <t>T-44-122</t>
+  </si>
+  <si>
+    <t>T-54</t>
+  </si>
+  <si>
+    <t>T-54 '45</t>
+  </si>
+  <si>
+    <t>T6 Medium</t>
+  </si>
+  <si>
+    <t>Type 5 Ho-Ri I</t>
+  </si>
+  <si>
+    <t>Type 5 Ho-Ri II</t>
+  </si>
+  <si>
+    <t>Type 5 Ho-Ri III</t>
+  </si>
+  <si>
+    <t>Valentine AT</t>
+  </si>
+  <si>
+    <t>Vickers Medium Mk. I</t>
+  </si>
+  <si>
+    <t>Vickers Medium Mk. II</t>
+  </si>
+  <si>
+    <t>Vickers Medium Mk. III</t>
+  </si>
+  <si>
+    <t>VK 20.01 (D)</t>
+  </si>
+  <si>
+    <t>VK 30.01 (D)</t>
+  </si>
+  <si>
+    <t>VK 30.01 (H)</t>
+  </si>
+  <si>
+    <t>VK 30.02 (M)</t>
+  </si>
+  <si>
+    <t>AEC Matador</t>
+  </si>
+  <si>
+    <t>Truck</t>
+  </si>
+  <si>
+    <t>Autocannone da 100/17 su Lancia 3Ro</t>
+  </si>
+  <si>
+    <t>Bedford OYD</t>
+  </si>
+  <si>
+    <t>Bedford QLT</t>
+  </si>
+  <si>
+    <t>BM-13 Studebaker</t>
+  </si>
+  <si>
+    <t>BM-31-12</t>
+  </si>
+  <si>
+    <t>BM-8-48</t>
+  </si>
+  <si>
+    <t>Chevrolet 15 cwt</t>
+  </si>
+  <si>
+    <t>Chevrolet 30 cwt</t>
+  </si>
+  <si>
+    <t>Chevrolet G506</t>
+  </si>
+  <si>
+    <t>Citroën 23R</t>
+  </si>
+  <si>
+    <t>CMP Tri-Polsten</t>
+  </si>
+  <si>
+    <t>Fiat 626</t>
+  </si>
+  <si>
+    <t>Fiat-SPA 38R</t>
+  </si>
+  <si>
+    <t>Ford G917T</t>
+  </si>
+  <si>
+    <t>Ford V3000</t>
+  </si>
+  <si>
+    <t>GAZ-AAA</t>
+  </si>
+  <si>
+    <t>GMC CCKW</t>
+  </si>
+  <si>
+    <t>GMC CCKW 352</t>
+  </si>
+  <si>
+    <t>Isuzu Type 94 truck</t>
+  </si>
+  <si>
+    <t>Kfz. 70</t>
+  </si>
+  <si>
+    <t>L 2 H 43</t>
+  </si>
+  <si>
+    <t>Lancia 3Ro</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz L3000</t>
+  </si>
+  <si>
+    <t>Morris Commercial C8 FAT</t>
+  </si>
+  <si>
+    <t>Morris-Commercial C9/B</t>
+  </si>
+  <si>
+    <t>Opel Blitz 3.6</t>
+  </si>
+  <si>
+    <t>Polski Fiat 621</t>
+  </si>
+  <si>
+    <t>Praga RV</t>
+  </si>
+  <si>
+    <t>Rába 38M Botond</t>
+  </si>
+  <si>
+    <t>Renault AGK</t>
+  </si>
+  <si>
+    <t>SU-12</t>
+  </si>
+  <si>
+    <t>suzu Type 94 truck (20mm AA)</t>
+  </si>
+  <si>
+    <t>Volvo LV127</t>
+  </si>
+  <si>
+    <t>Volvo LV127 ITK40</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>YaG-10 (29K)</t>
+  </si>
+  <si>
+    <t>ZiS-12 (94-KM)</t>
+  </si>
+  <si>
+    <t>ZiS-5</t>
+  </si>
+  <si>
+    <t>ZiS-6</t>
   </si>
 </sst>
 </file>
@@ -1328,7 +2159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C50DCCC-8446-4FAC-BA76-D53F2D86B716}">
-  <dimension ref="A1:C273"/>
+  <dimension ref="A1:C559"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.81640625" customWidth="1"/>
@@ -1349,442 +2180,442 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>289</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>290</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>291</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="B6" t="s">
-        <v>242</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>293</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>294</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>295</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>296</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>254</v>
+        <v>297</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>255</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="B11" t="s">
         <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>301</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>302</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>303</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>305</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>306</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>307</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>308</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>309</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>310</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>311</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>248</v>
+        <v>312</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>256</v>
+        <v>313</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>314</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>315</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>316</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>246</v>
+      <c r="A29" t="s">
+        <v>317</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>318</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>319</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>249</v>
+        <v>321</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>323</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>274</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C36" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>325</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>273</v>
+        <v>326</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>272</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>252</v>
+        <v>328</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>239</v>
       </c>
       <c r="C40" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="3" t="s">
-        <v>279</v>
+      <c r="A41" t="s">
+        <v>329</v>
       </c>
       <c r="B41" t="s">
-        <v>16</v>
+        <v>239</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
@@ -1795,2548 +2626,5694 @@
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>285</v>
+        <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>281</v>
+        <v>10</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C45" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>263</v>
       </c>
       <c r="B46" t="s">
-        <v>16</v>
+        <v>239</v>
       </c>
       <c r="C46" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>251</v>
+        <v>14</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>39</v>
+        <v>330</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>40</v>
+        <v>332</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>333</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>42</v>
+        <v>334</v>
       </c>
       <c r="B53" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>43</v>
+        <v>335</v>
       </c>
       <c r="B54" t="s">
         <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>44</v>
+        <v>336</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>337</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>258</v>
+        <v>338</v>
       </c>
       <c r="B57" t="s">
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>46</v>
+        <v>339</v>
       </c>
       <c r="B58" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>47</v>
+        <v>340</v>
       </c>
       <c r="B59" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>48</v>
+        <v>341</v>
       </c>
       <c r="B60" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>247</v>
+        <v>342</v>
       </c>
       <c r="B61" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C61" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>290</v>
+        <v>343</v>
       </c>
       <c r="B62" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>50</v>
+        <v>344</v>
       </c>
       <c r="B63" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>51</v>
+        <v>345</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>52</v>
+        <v>346</v>
       </c>
       <c r="B65" t="s">
-        <v>49</v>
+        <v>239</v>
       </c>
       <c r="C65" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>53</v>
+        <v>347</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="C66" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>271</v>
+        <v>348</v>
       </c>
       <c r="B67" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>54</v>
+        <v>349</v>
       </c>
       <c r="B68" t="s">
         <v>16</v>
       </c>
       <c r="C68" t="s">
-        <v>17</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>292</v>
+        <v>350</v>
       </c>
       <c r="B69" t="s">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="C69" t="s">
-        <v>56</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>266</v>
+        <v>351</v>
       </c>
       <c r="B70" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>56</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>55</v>
+        <v>352</v>
       </c>
       <c r="B71" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C71" t="s">
-        <v>56</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>276</v>
+        <v>251</v>
       </c>
       <c r="B72" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>56</v>
+        <v>252</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>57</v>
+        <v>353</v>
       </c>
       <c r="B73" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="C73" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>58</v>
+        <v>254</v>
       </c>
       <c r="B74" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C74" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>60</v>
+        <v>354</v>
       </c>
       <c r="B75" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C75" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>61</v>
+        <v>355</v>
       </c>
       <c r="B76" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C76" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>62</v>
+        <v>356</v>
       </c>
       <c r="B77" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C77" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>259</v>
+        <v>357</v>
       </c>
       <c r="B78" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="C78" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>63</v>
+        <v>358</v>
       </c>
       <c r="B79" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="C79" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>64</v>
+        <v>359</v>
       </c>
       <c r="B80" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C80" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>65</v>
+        <v>261</v>
       </c>
       <c r="B81" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="C81" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>260</v>
+        <v>360</v>
       </c>
       <c r="B82" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C82" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>66</v>
+        <v>361</v>
       </c>
       <c r="B83" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C83" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="B84" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C84" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="B85" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C85" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>69</v>
+        <v>362</v>
       </c>
       <c r="B86" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C86" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>70</v>
+        <v>363</v>
       </c>
       <c r="B87" t="s">
         <v>16</v>
       </c>
       <c r="C87" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>71</v>
+        <v>364</v>
       </c>
       <c r="B88" t="s">
         <v>16</v>
       </c>
       <c r="C88" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>72</v>
+        <v>365</v>
       </c>
       <c r="B89" t="s">
         <v>16</v>
       </c>
       <c r="C89" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="B90" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C90" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="B91" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="B92" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C92" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="B93" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="B94" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="B95" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="B96" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="B97" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="B98" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>278</v>
+        <v>253</v>
       </c>
       <c r="B99" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="B100" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C100" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>275</v>
+        <v>27</v>
       </c>
       <c r="B101" t="s">
         <v>16</v>
       </c>
       <c r="C101" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="B102" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="B103" t="s">
         <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="B104" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>86</v>
+        <v>367</v>
       </c>
       <c r="B105" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>87</v>
+      <c r="A106" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="B106" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="C106" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>88</v>
+        <v>243</v>
       </c>
       <c r="B107" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>89</v>
+        <v>368</v>
       </c>
       <c r="B108" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="B109" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="B110" t="s">
         <v>13</v>
       </c>
       <c r="C110" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="B111" t="s">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="C111" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>93</v>
+        <v>246</v>
       </c>
       <c r="B112" t="s">
         <v>13</v>
       </c>
       <c r="C112" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="B113" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C113" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="B114" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C114" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>96</v>
+        <v>369</v>
       </c>
       <c r="B115" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C115" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>97</v>
+        <v>370</v>
       </c>
       <c r="B116" t="s">
         <v>13</v>
       </c>
       <c r="C116" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>98</v>
+        <v>371</v>
       </c>
       <c r="B117" t="s">
         <v>13</v>
       </c>
       <c r="C117" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="B118" t="s">
         <v>13</v>
       </c>
       <c r="C118" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>100</v>
+        <v>372</v>
       </c>
       <c r="B119" t="s">
         <v>13</v>
       </c>
       <c r="C119" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>261</v>
+        <v>373</v>
       </c>
       <c r="B120" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C120" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>101</v>
+        <v>374</v>
       </c>
       <c r="B121" t="s">
         <v>13</v>
       </c>
       <c r="C121" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>102</v>
+        <v>375</v>
       </c>
       <c r="B122" t="s">
         <v>11</v>
       </c>
       <c r="C122" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
       <c r="B123" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C123" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>103</v>
+        <v>376</v>
       </c>
       <c r="B124" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C124" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>106</v>
+        <v>377</v>
       </c>
       <c r="B125" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C125" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>107</v>
+        <v>35</v>
       </c>
       <c r="B126" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C126" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>108</v>
+        <v>267</v>
       </c>
       <c r="B127" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C127" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>109</v>
+        <v>266</v>
       </c>
       <c r="B128" t="s">
         <v>16</v>
       </c>
       <c r="C128" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>110</v>
+        <v>249</v>
       </c>
       <c r="B129" t="s">
         <v>13</v>
       </c>
       <c r="C129" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
-        <v>268</v>
+      <c r="A130" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="B130" t="s">
-        <v>242</v>
+        <v>16</v>
       </c>
       <c r="C130" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>111</v>
+        <v>274</v>
       </c>
       <c r="B131" t="s">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="C131" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>114</v>
+        <v>279</v>
       </c>
       <c r="B132" t="s">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="C132" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>115</v>
+        <v>36</v>
       </c>
       <c r="B133" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C133" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>116</v>
+        <v>378</v>
       </c>
       <c r="B134" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>117</v>
+        <v>379</v>
       </c>
       <c r="B135" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C135" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>118</v>
+        <v>275</v>
       </c>
       <c r="B136" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C136" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>277</v>
+        <v>37</v>
       </c>
       <c r="B137" t="s">
         <v>16</v>
       </c>
       <c r="C137" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="B138" t="s">
         <v>16</v>
       </c>
       <c r="C138" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="B139" t="s">
         <v>16</v>
       </c>
       <c r="C139" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>282</v>
+        <v>380</v>
       </c>
       <c r="B140" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C140" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>121</v>
+        <v>381</v>
       </c>
       <c r="B141" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C141" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>122</v>
+        <v>382</v>
       </c>
       <c r="B142" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C142" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>283</v>
+        <v>247</v>
       </c>
       <c r="B143" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C143" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="B144" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C144" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="B145" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C145" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="B146" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C146" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>125</v>
+        <v>40</v>
       </c>
       <c r="B147" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C147" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>126</v>
+        <v>383</v>
       </c>
       <c r="B148" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C148" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>127</v>
+        <v>384</v>
       </c>
       <c r="B149" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C149" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>128</v>
+        <v>385</v>
       </c>
       <c r="B150" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C150" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>129</v>
+        <v>386</v>
       </c>
       <c r="B151" t="s">
-        <v>130</v>
+        <v>13</v>
       </c>
       <c r="C151" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>131</v>
+        <v>387</v>
       </c>
       <c r="B152" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="C152" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>132</v>
+        <v>388</v>
       </c>
       <c r="B153" t="s">
         <v>7</v>
       </c>
       <c r="C153" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="B154" t="s">
         <v>7</v>
       </c>
       <c r="C154" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="B155" t="s">
         <v>7</v>
       </c>
       <c r="C155" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="B156" t="s">
         <v>7</v>
       </c>
       <c r="C156" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>136</v>
+        <v>42</v>
       </c>
       <c r="B157" t="s">
         <v>7</v>
       </c>
       <c r="C157" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>137</v>
+        <v>389</v>
       </c>
       <c r="B158" t="s">
         <v>7</v>
       </c>
       <c r="C158" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>138</v>
+        <v>43</v>
       </c>
       <c r="B159" t="s">
         <v>7</v>
       </c>
       <c r="C159" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="B160" t="s">
         <v>7</v>
       </c>
       <c r="C160" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="B161" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C161" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="B162" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C162" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>142</v>
+        <v>255</v>
       </c>
       <c r="B163" t="s">
         <v>7</v>
       </c>
       <c r="C163" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>143</v>
+        <v>255</v>
       </c>
       <c r="B164" t="s">
         <v>7</v>
       </c>
       <c r="C164" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="B165" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C165" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>145</v>
+        <v>47</v>
       </c>
       <c r="B166" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C166" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="B167" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="C167" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>147</v>
+        <v>244</v>
       </c>
       <c r="B168" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C168" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>148</v>
+        <v>390</v>
       </c>
       <c r="B169" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C169" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>149</v>
+        <v>284</v>
       </c>
       <c r="B170" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C170" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>150</v>
+        <v>391</v>
       </c>
       <c r="B171" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C171" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="B172" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C172" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="B173" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C173" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="B174" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="C174" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>154</v>
+        <v>392</v>
       </c>
       <c r="B175" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C175" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>155</v>
+        <v>393</v>
       </c>
       <c r="B176" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C176" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>156</v>
+        <v>394</v>
       </c>
       <c r="B177" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C177" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>157</v>
+        <v>395</v>
       </c>
       <c r="B178" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C178" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>158</v>
+        <v>53</v>
       </c>
       <c r="B179" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C179" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>159</v>
+        <v>396</v>
       </c>
       <c r="B180" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C180" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B181" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C181" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>160</v>
+        <v>54</v>
       </c>
       <c r="B182" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C182" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>161</v>
+        <v>397</v>
       </c>
       <c r="B183" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C183" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>162</v>
+        <v>398</v>
       </c>
       <c r="B184" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="C184" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>163</v>
+        <v>399</v>
       </c>
       <c r="B185" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C185" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>164</v>
+        <v>400</v>
       </c>
       <c r="B186" t="s">
-        <v>49</v>
+        <v>239</v>
       </c>
       <c r="C186" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>165</v>
+        <v>286</v>
       </c>
       <c r="B187" t="s">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="C187" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>243</v>
+        <v>401</v>
       </c>
       <c r="B188" t="s">
-        <v>7</v>
+        <v>239</v>
       </c>
       <c r="C188" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>166</v>
+        <v>402</v>
       </c>
       <c r="B189" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C189" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>167</v>
+        <v>403</v>
       </c>
       <c r="B190" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C190" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>168</v>
+        <v>404</v>
       </c>
       <c r="B191" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C191" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>169</v>
+        <v>405</v>
       </c>
       <c r="B192" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C192" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>170</v>
+        <v>406</v>
       </c>
       <c r="B193" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C193" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>171</v>
+        <v>55</v>
       </c>
       <c r="B194" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C194" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>172</v>
+        <v>407</v>
       </c>
       <c r="B195" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C195" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>173</v>
+        <v>270</v>
       </c>
       <c r="B196" t="s">
         <v>16</v>
       </c>
       <c r="C196" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>174</v>
+        <v>57</v>
       </c>
       <c r="B197" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C197" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>175</v>
+        <v>408</v>
       </c>
       <c r="B198" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C198" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>176</v>
+        <v>58</v>
       </c>
       <c r="B199" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="C199" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>177</v>
+        <v>409</v>
       </c>
       <c r="B200" t="s">
         <v>16</v>
       </c>
       <c r="C200" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>178</v>
+        <v>60</v>
       </c>
       <c r="B201" t="s">
         <v>16</v>
       </c>
       <c r="C201" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>179</v>
+        <v>61</v>
       </c>
       <c r="B202" t="s">
         <v>16</v>
       </c>
       <c r="C202" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>180</v>
+        <v>410</v>
       </c>
       <c r="B203" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C203" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>181</v>
+        <v>411</v>
       </c>
       <c r="B204" t="s">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="C204" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>182</v>
+        <v>412</v>
       </c>
       <c r="B205" t="s">
-        <v>16</v>
+        <v>310</v>
       </c>
       <c r="C205" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>183</v>
+        <v>413</v>
       </c>
       <c r="B206" t="s">
-        <v>16</v>
+        <v>310</v>
       </c>
       <c r="C206" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>184</v>
+        <v>414</v>
       </c>
       <c r="B207" t="s">
         <v>16</v>
       </c>
       <c r="C207" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>185</v>
+        <v>62</v>
       </c>
       <c r="B208" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C208" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>270</v>
+        <v>415</v>
       </c>
       <c r="B209" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C209" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>186</v>
+        <v>63</v>
       </c>
       <c r="B210" t="s">
         <v>16</v>
       </c>
       <c r="C210" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="B211" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="C211" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>188</v>
+        <v>416</v>
       </c>
       <c r="B212" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C212" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>189</v>
+        <v>417</v>
       </c>
       <c r="B213" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="C213" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>190</v>
+        <v>64</v>
       </c>
       <c r="B214" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="C214" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="B215" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="C215" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="B216" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C216" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>193</v>
+        <v>66</v>
       </c>
       <c r="B217" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C217" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>194</v>
+        <v>418</v>
       </c>
       <c r="B218" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C218" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>195</v>
+        <v>67</v>
       </c>
       <c r="B219" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C219" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>196</v>
+        <v>419</v>
       </c>
       <c r="B220" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C220" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>197</v>
+        <v>420</v>
       </c>
       <c r="B221" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C221" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>198</v>
+        <v>68</v>
       </c>
       <c r="B222" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C222" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>199</v>
+        <v>421</v>
       </c>
       <c r="B223" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C223" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>200</v>
+        <v>69</v>
       </c>
       <c r="B224" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C224" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>201</v>
+        <v>70</v>
       </c>
       <c r="B225" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C225" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>202</v>
+        <v>71</v>
       </c>
       <c r="B226" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C226" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>203</v>
+        <v>72</v>
       </c>
       <c r="B227" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C227" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>245</v>
+        <v>73</v>
       </c>
       <c r="B228" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C228" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="B229" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C229" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>204</v>
+        <v>423</v>
       </c>
       <c r="B230" t="s">
         <v>13</v>
       </c>
       <c r="C230" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>205</v>
+        <v>424</v>
       </c>
       <c r="B231" t="s">
         <v>13</v>
       </c>
       <c r="C231" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="B232" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C232" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>207</v>
+        <v>74</v>
       </c>
       <c r="B233" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C233" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>208</v>
+        <v>75</v>
       </c>
       <c r="B234" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C234" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>209</v>
+        <v>76</v>
       </c>
       <c r="B235" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C235" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="B236" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C236" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>211</v>
+        <v>78</v>
       </c>
       <c r="B237" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C237" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>212</v>
+        <v>79</v>
       </c>
       <c r="B238" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C238" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>213</v>
+        <v>80</v>
       </c>
       <c r="B239" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C239" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>214</v>
+        <v>272</v>
       </c>
       <c r="B240" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C240" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>215</v>
+        <v>425</v>
       </c>
       <c r="B241" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="C241" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>216</v>
+        <v>426</v>
       </c>
       <c r="B242" t="s">
-        <v>11</v>
+        <v>310</v>
       </c>
       <c r="C242" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>217</v>
+        <v>427</v>
       </c>
       <c r="B243" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C243" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="B244" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C244" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>219</v>
+        <v>428</v>
       </c>
       <c r="B245" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C245" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="B246" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C246" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>220</v>
+        <v>82</v>
       </c>
       <c r="B247" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C247" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>221</v>
+        <v>83</v>
       </c>
       <c r="B248" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C248" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>222</v>
+        <v>429</v>
       </c>
       <c r="B249" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C249" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>223</v>
+        <v>430</v>
       </c>
       <c r="B250" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C250" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>224</v>
+        <v>431</v>
       </c>
       <c r="B251" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="C251" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>225</v>
+        <v>432</v>
       </c>
       <c r="B252" t="s">
-        <v>49</v>
+        <v>310</v>
       </c>
       <c r="C252" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>226</v>
+        <v>84</v>
       </c>
       <c r="B253" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C253" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>227</v>
+        <v>85</v>
       </c>
       <c r="B254" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C254" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>228</v>
+        <v>86</v>
       </c>
       <c r="B255" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C255" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>229</v>
+        <v>433</v>
       </c>
       <c r="B256" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="C256" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>230</v>
+        <v>434</v>
       </c>
       <c r="B257" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="C257" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>231</v>
+        <v>87</v>
       </c>
       <c r="B258" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C258" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>232</v>
+        <v>435</v>
       </c>
       <c r="B259" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C259" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>233</v>
+        <v>436</v>
       </c>
       <c r="B260" t="s">
-        <v>7</v>
+        <v>310</v>
       </c>
       <c r="C260" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>253</v>
+        <v>437</v>
       </c>
       <c r="B261" t="s">
-        <v>13</v>
+        <v>310</v>
       </c>
       <c r="C261" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>234</v>
+        <v>438</v>
       </c>
       <c r="B262" t="s">
-        <v>4</v>
+        <v>310</v>
       </c>
       <c r="C262" t="s">
-        <v>235</v>
+        <v>56</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>236</v>
+        <v>439</v>
       </c>
       <c r="B263" t="s">
-        <v>4</v>
+        <v>310</v>
       </c>
       <c r="C263" t="s">
-        <v>235</v>
+        <v>56</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>237</v>
+        <v>88</v>
       </c>
       <c r="B264" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C264" t="s">
-        <v>235</v>
+        <v>56</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>238</v>
+        <v>440</v>
       </c>
       <c r="B265" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C265" t="s">
-        <v>235</v>
+        <v>56</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>239</v>
+        <v>89</v>
       </c>
       <c r="B266" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C266" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>240</v>
+        <v>89</v>
       </c>
       <c r="B267" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C267" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>241</v>
+        <v>441</v>
       </c>
       <c r="B268" t="s">
-        <v>242</v>
+        <v>7</v>
       </c>
       <c r="C268" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>287</v>
+        <v>442</v>
       </c>
       <c r="B269" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C269" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>288</v>
+        <v>443</v>
       </c>
       <c r="B270" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C270" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="B271" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C271" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>263</v>
+        <v>90</v>
       </c>
       <c r="B272" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="C272" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
+        <v>444</v>
+      </c>
+      <c r="B273" t="s">
+        <v>7</v>
+      </c>
+      <c r="C273" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>445</v>
+      </c>
+      <c r="B274" t="s">
+        <v>7</v>
+      </c>
+      <c r="C274" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>446</v>
+      </c>
+      <c r="B275" t="s">
+        <v>7</v>
+      </c>
+      <c r="C275" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>447</v>
+      </c>
+      <c r="B276" t="s">
+        <v>7</v>
+      </c>
+      <c r="C276" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>92</v>
+      </c>
+      <c r="B277" t="s">
+        <v>13</v>
+      </c>
+      <c r="C277" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>93</v>
+      </c>
+      <c r="B278" t="s">
+        <v>13</v>
+      </c>
+      <c r="C278" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>448</v>
+      </c>
+      <c r="B279" t="s">
+        <v>7</v>
+      </c>
+      <c r="C279" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>94</v>
+      </c>
+      <c r="B280" t="s">
+        <v>13</v>
+      </c>
+      <c r="C280" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>449</v>
+      </c>
+      <c r="B281" t="s">
+        <v>13</v>
+      </c>
+      <c r="C281" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>450</v>
+      </c>
+      <c r="B282" t="s">
+        <v>13</v>
+      </c>
+      <c r="C282" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>95</v>
+      </c>
+      <c r="B283" t="s">
+        <v>13</v>
+      </c>
+      <c r="C283" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>451</v>
+      </c>
+      <c r="B284" t="s">
+        <v>13</v>
+      </c>
+      <c r="C284" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>452</v>
+      </c>
+      <c r="B285" t="s">
+        <v>7</v>
+      </c>
+      <c r="C285" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>96</v>
+      </c>
+      <c r="B286" t="s">
+        <v>13</v>
+      </c>
+      <c r="C286" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>97</v>
+      </c>
+      <c r="B287" t="s">
+        <v>13</v>
+      </c>
+      <c r="C287" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>453</v>
+      </c>
+      <c r="B288" t="s">
+        <v>7</v>
+      </c>
+      <c r="C288" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>454</v>
+      </c>
+      <c r="B289" t="s">
+        <v>7</v>
+      </c>
+      <c r="C289" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>98</v>
+      </c>
+      <c r="B290" t="s">
+        <v>13</v>
+      </c>
+      <c r="C290" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>99</v>
+      </c>
+      <c r="B291" t="s">
+        <v>13</v>
+      </c>
+      <c r="C291" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>257</v>
+      </c>
+      <c r="B292" t="s">
+        <v>7</v>
+      </c>
+      <c r="C292" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>100</v>
+      </c>
+      <c r="B293" t="s">
+        <v>13</v>
+      </c>
+      <c r="C293" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>455</v>
+      </c>
+      <c r="B294" t="s">
+        <v>7</v>
+      </c>
+      <c r="C294" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>456</v>
+      </c>
+      <c r="B295" t="s">
+        <v>11</v>
+      </c>
+      <c r="C295" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>101</v>
+      </c>
+      <c r="B296" t="s">
+        <v>11</v>
+      </c>
+      <c r="C296" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>283</v>
+      </c>
+      <c r="B297" t="s">
+        <v>11</v>
+      </c>
+      <c r="C297" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>457</v>
+      </c>
+      <c r="B298" t="s">
+        <v>11</v>
+      </c>
+      <c r="C298" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>102</v>
+      </c>
+      <c r="B299" t="s">
+        <v>11</v>
+      </c>
+      <c r="C299" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>458</v>
+      </c>
+      <c r="B300" t="s">
+        <v>11</v>
+      </c>
+      <c r="C300" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>105</v>
+      </c>
+      <c r="B301" t="s">
+        <v>11</v>
+      </c>
+      <c r="C301" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>106</v>
+      </c>
+      <c r="B302" t="s">
+        <v>49</v>
+      </c>
+      <c r="C302" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>107</v>
+      </c>
+      <c r="B303" t="s">
+        <v>49</v>
+      </c>
+      <c r="C303" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>108</v>
+      </c>
+      <c r="B304" t="s">
+        <v>16</v>
+      </c>
+      <c r="C304" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>459</v>
+      </c>
+      <c r="B305" t="s">
+        <v>16</v>
+      </c>
+      <c r="C305" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>460</v>
+      </c>
+      <c r="B306" t="s">
+        <v>16</v>
+      </c>
+      <c r="C306" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>109</v>
+      </c>
+      <c r="B307" t="s">
+        <v>13</v>
+      </c>
+      <c r="C307" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>262</v>
+      </c>
+      <c r="B308" t="s">
+        <v>239</v>
+      </c>
+      <c r="C308" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>461</v>
+      </c>
+      <c r="B309" t="s">
+        <v>239</v>
+      </c>
+      <c r="C309" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>110</v>
+      </c>
+      <c r="B310" t="s">
+        <v>111</v>
+      </c>
+      <c r="C310" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>113</v>
+      </c>
+      <c r="B311" t="s">
+        <v>111</v>
+      </c>
+      <c r="C311" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>462</v>
+      </c>
+      <c r="B312" t="s">
+        <v>49</v>
+      </c>
+      <c r="C312" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>463</v>
+      </c>
+      <c r="B313" t="s">
+        <v>49</v>
+      </c>
+      <c r="C313" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>464</v>
+      </c>
+      <c r="B314" t="s">
+        <v>13</v>
+      </c>
+      <c r="C314" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>465</v>
+      </c>
+      <c r="B315" t="s">
+        <v>49</v>
+      </c>
+      <c r="C315" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>466</v>
+      </c>
+      <c r="B316" t="s">
+        <v>13</v>
+      </c>
+      <c r="C316" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>467</v>
+      </c>
+      <c r="B317" t="s">
+        <v>49</v>
+      </c>
+      <c r="C317" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>468</v>
+      </c>
+      <c r="B318" t="s">
+        <v>49</v>
+      </c>
+      <c r="C318" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>469</v>
+      </c>
+      <c r="B319" t="s">
+        <v>49</v>
+      </c>
+      <c r="C319" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>470</v>
+      </c>
+      <c r="B320" t="s">
+        <v>49</v>
+      </c>
+      <c r="C320" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>471</v>
+      </c>
+      <c r="B321" t="s">
+        <v>49</v>
+      </c>
+      <c r="C321" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>472</v>
+      </c>
+      <c r="B322" t="s">
+        <v>49</v>
+      </c>
+      <c r="C322" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>473</v>
+      </c>
+      <c r="B323" t="s">
+        <v>16</v>
+      </c>
+      <c r="C323" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>474</v>
+      </c>
+      <c r="B324" t="s">
+        <v>59</v>
+      </c>
+      <c r="C324" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>475</v>
+      </c>
+      <c r="B325" t="s">
+        <v>59</v>
+      </c>
+      <c r="C325" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>407</v>
+      </c>
+      <c r="B326" t="s">
+        <v>7</v>
+      </c>
+      <c r="C326" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>476</v>
+      </c>
+      <c r="B327" t="s">
+        <v>7</v>
+      </c>
+      <c r="C327" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>114</v>
+      </c>
+      <c r="B328" t="s">
+        <v>49</v>
+      </c>
+      <c r="C328" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>115</v>
+      </c>
+      <c r="B329" t="s">
+        <v>49</v>
+      </c>
+      <c r="C329" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>116</v>
+      </c>
+      <c r="B330" t="s">
+        <v>49</v>
+      </c>
+      <c r="C330" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>117</v>
+      </c>
+      <c r="B331" t="s">
+        <v>49</v>
+      </c>
+      <c r="C331" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>477</v>
+      </c>
+      <c r="B332" t="s">
+        <v>239</v>
+      </c>
+      <c r="C332" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>271</v>
+      </c>
+      <c r="B333" t="s">
+        <v>16</v>
+      </c>
+      <c r="C333" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>118</v>
+      </c>
+      <c r="B334" t="s">
+        <v>16</v>
+      </c>
+      <c r="C334" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>119</v>
+      </c>
+      <c r="B335" t="s">
+        <v>16</v>
+      </c>
+      <c r="C335" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>276</v>
+      </c>
+      <c r="B336" t="s">
+        <v>16</v>
+      </c>
+      <c r="C336" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>120</v>
+      </c>
+      <c r="B337" t="s">
+        <v>16</v>
+      </c>
+      <c r="C337" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>121</v>
+      </c>
+      <c r="B338" t="s">
+        <v>16</v>
+      </c>
+      <c r="C338" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>277</v>
+      </c>
+      <c r="B339" t="s">
+        <v>16</v>
+      </c>
+      <c r="C339" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>278</v>
+      </c>
+      <c r="B340" t="s">
+        <v>16</v>
+      </c>
+      <c r="C340" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>122</v>
+      </c>
+      <c r="B341" t="s">
+        <v>16</v>
+      </c>
+      <c r="C341" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>478</v>
+      </c>
+      <c r="B342" t="s">
+        <v>16</v>
+      </c>
+      <c r="C342" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>123</v>
+      </c>
+      <c r="B343" t="s">
+        <v>16</v>
+      </c>
+      <c r="C343" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>479</v>
+      </c>
+      <c r="B344" t="s">
+        <v>310</v>
+      </c>
+      <c r="C344" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>480</v>
+      </c>
+      <c r="B345" t="s">
+        <v>13</v>
+      </c>
+      <c r="C345" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>124</v>
+      </c>
+      <c r="B346" t="s">
+        <v>16</v>
+      </c>
+      <c r="C346" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>125</v>
+      </c>
+      <c r="B347" t="s">
+        <v>16</v>
+      </c>
+      <c r="C347" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>126</v>
+      </c>
+      <c r="B348" t="s">
+        <v>16</v>
+      </c>
+      <c r="C348" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>127</v>
+      </c>
+      <c r="B349" t="s">
+        <v>16</v>
+      </c>
+      <c r="C349" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>481</v>
+      </c>
+      <c r="B350" t="s">
+        <v>16</v>
+      </c>
+      <c r="C350" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>482</v>
+      </c>
+      <c r="B351" t="s">
+        <v>310</v>
+      </c>
+      <c r="C351" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>128</v>
+      </c>
+      <c r="B352" t="s">
+        <v>129</v>
+      </c>
+      <c r="C352" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>483</v>
+      </c>
+      <c r="B353" t="s">
+        <v>13</v>
+      </c>
+      <c r="C353" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>484</v>
+      </c>
+      <c r="B354" t="s">
+        <v>4</v>
+      </c>
+      <c r="C354" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>130</v>
+      </c>
+      <c r="B355" t="s">
+        <v>59</v>
+      </c>
+      <c r="C355" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>485</v>
+      </c>
+      <c r="B356" t="s">
+        <v>59</v>
+      </c>
+      <c r="C356" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>131</v>
+      </c>
+      <c r="B357" t="s">
+        <v>7</v>
+      </c>
+      <c r="C357" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A358" t="s">
+        <v>486</v>
+      </c>
+      <c r="B358" t="s">
+        <v>7</v>
+      </c>
+      <c r="C358" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A359" t="s">
+        <v>132</v>
+      </c>
+      <c r="B359" t="s">
+        <v>7</v>
+      </c>
+      <c r="C359" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A360" t="s">
+        <v>487</v>
+      </c>
+      <c r="B360" t="s">
+        <v>7</v>
+      </c>
+      <c r="C360" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A361" t="s">
+        <v>133</v>
+      </c>
+      <c r="B361" t="s">
+        <v>7</v>
+      </c>
+      <c r="C361" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A362" t="s">
+        <v>134</v>
+      </c>
+      <c r="B362" t="s">
+        <v>7</v>
+      </c>
+      <c r="C362" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A363" t="s">
+        <v>135</v>
+      </c>
+      <c r="B363" t="s">
+        <v>7</v>
+      </c>
+      <c r="C363" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A364" t="s">
+        <v>136</v>
+      </c>
+      <c r="B364" t="s">
+        <v>7</v>
+      </c>
+      <c r="C364" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>137</v>
+      </c>
+      <c r="B365" t="s">
+        <v>7</v>
+      </c>
+      <c r="C365" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A366" t="s">
+        <v>138</v>
+      </c>
+      <c r="B366" t="s">
+        <v>7</v>
+      </c>
+      <c r="C366" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
+        <v>488</v>
+      </c>
+      <c r="B367" t="s">
+        <v>7</v>
+      </c>
+      <c r="C367" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A368" t="s">
+        <v>489</v>
+      </c>
+      <c r="B368" t="s">
+        <v>7</v>
+      </c>
+      <c r="C368" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A369" t="s">
+        <v>139</v>
+      </c>
+      <c r="B369" t="s">
+        <v>7</v>
+      </c>
+      <c r="C369" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A370" t="s">
+        <v>140</v>
+      </c>
+      <c r="B370" t="s">
+        <v>7</v>
+      </c>
+      <c r="C370" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A371" t="s">
+        <v>141</v>
+      </c>
+      <c r="B371" t="s">
+        <v>7</v>
+      </c>
+      <c r="C371" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A372" t="s">
+        <v>142</v>
+      </c>
+      <c r="B372" t="s">
+        <v>7</v>
+      </c>
+      <c r="C372" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A373" t="s">
+        <v>143</v>
+      </c>
+      <c r="B373" t="s">
+        <v>7</v>
+      </c>
+      <c r="C373" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A374" t="s">
+        <v>144</v>
+      </c>
+      <c r="B374" t="s">
+        <v>7</v>
+      </c>
+      <c r="C374" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A375" t="s">
+        <v>145</v>
+      </c>
+      <c r="B375" t="s">
+        <v>7</v>
+      </c>
+      <c r="C375" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A376" t="s">
+        <v>146</v>
+      </c>
+      <c r="B376" t="s">
+        <v>7</v>
+      </c>
+      <c r="C376" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A377" t="s">
+        <v>147</v>
+      </c>
+      <c r="B377" t="s">
+        <v>7</v>
+      </c>
+      <c r="C377" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A378" t="s">
+        <v>148</v>
+      </c>
+      <c r="B378" t="s">
+        <v>7</v>
+      </c>
+      <c r="C378" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A379" t="s">
+        <v>149</v>
+      </c>
+      <c r="B379" t="s">
+        <v>7</v>
+      </c>
+      <c r="C379" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A380" t="s">
+        <v>150</v>
+      </c>
+      <c r="B380" t="s">
+        <v>7</v>
+      </c>
+      <c r="C380" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A381" t="s">
+        <v>151</v>
+      </c>
+      <c r="B381" t="s">
+        <v>7</v>
+      </c>
+      <c r="C381" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A382" t="s">
+        <v>152</v>
+      </c>
+      <c r="B382" t="s">
+        <v>7</v>
+      </c>
+      <c r="C382" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A383" t="s">
+        <v>153</v>
+      </c>
+      <c r="B383" t="s">
+        <v>7</v>
+      </c>
+      <c r="C383" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A384" t="s">
+        <v>154</v>
+      </c>
+      <c r="B384" t="s">
+        <v>7</v>
+      </c>
+      <c r="C384" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A385" t="s">
+        <v>155</v>
+      </c>
+      <c r="B385" t="s">
+        <v>7</v>
+      </c>
+      <c r="C385" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A386" t="s">
+        <v>156</v>
+      </c>
+      <c r="B386" t="s">
+        <v>7</v>
+      </c>
+      <c r="C386" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A387" t="s">
+        <v>157</v>
+      </c>
+      <c r="B387" t="s">
+        <v>7</v>
+      </c>
+      <c r="C387" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A388" t="s">
+        <v>158</v>
+      </c>
+      <c r="B388" t="s">
+        <v>7</v>
+      </c>
+      <c r="C388" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A389" t="s">
+        <v>258</v>
+      </c>
+      <c r="B389" t="s">
+        <v>49</v>
+      </c>
+      <c r="C389" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A390" t="s">
+        <v>159</v>
+      </c>
+      <c r="B390" t="s">
+        <v>49</v>
+      </c>
+      <c r="C390" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A391" t="s">
+        <v>160</v>
+      </c>
+      <c r="B391" t="s">
+        <v>49</v>
+      </c>
+      <c r="C391" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A392" t="s">
+        <v>161</v>
+      </c>
+      <c r="B392" t="s">
+        <v>49</v>
+      </c>
+      <c r="C392" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A393" t="s">
+        <v>162</v>
+      </c>
+      <c r="B393" t="s">
+        <v>49</v>
+      </c>
+      <c r="C393" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A394" t="s">
+        <v>163</v>
+      </c>
+      <c r="B394" t="s">
+        <v>49</v>
+      </c>
+      <c r="C394" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A395" t="s">
+        <v>164</v>
+      </c>
+      <c r="B395" t="s">
+        <v>49</v>
+      </c>
+      <c r="C395" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A396" t="s">
+        <v>240</v>
+      </c>
+      <c r="B396" t="s">
+        <v>7</v>
+      </c>
+      <c r="C396" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A397" t="s">
+        <v>490</v>
+      </c>
+      <c r="B397" t="s">
+        <v>59</v>
+      </c>
+      <c r="C397" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A398" t="s">
+        <v>165</v>
+      </c>
+      <c r="B398" t="s">
+        <v>16</v>
+      </c>
+      <c r="C398" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A399" t="s">
+        <v>165</v>
+      </c>
+      <c r="B399" t="s">
+        <v>16</v>
+      </c>
+      <c r="C399" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A400" t="s">
+        <v>166</v>
+      </c>
+      <c r="B400" t="s">
+        <v>16</v>
+      </c>
+      <c r="C400" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A401" t="s">
+        <v>167</v>
+      </c>
+      <c r="B401" t="s">
+        <v>16</v>
+      </c>
+      <c r="C401" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A402" t="s">
+        <v>168</v>
+      </c>
+      <c r="B402" t="s">
+        <v>16</v>
+      </c>
+      <c r="C402" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A403" t="s">
+        <v>169</v>
+      </c>
+      <c r="B403" t="s">
+        <v>16</v>
+      </c>
+      <c r="C403" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A404" t="s">
+        <v>170</v>
+      </c>
+      <c r="B404" t="s">
+        <v>16</v>
+      </c>
+      <c r="C404" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A405" t="s">
+        <v>171</v>
+      </c>
+      <c r="B405" t="s">
+        <v>16</v>
+      </c>
+      <c r="C405" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A406" t="s">
+        <v>172</v>
+      </c>
+      <c r="B406" t="s">
+        <v>16</v>
+      </c>
+      <c r="C406" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A407" t="s">
+        <v>173</v>
+      </c>
+      <c r="B407" t="s">
+        <v>16</v>
+      </c>
+      <c r="C407" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A408" t="s">
+        <v>174</v>
+      </c>
+      <c r="B408" t="s">
+        <v>16</v>
+      </c>
+      <c r="C408" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A409" t="s">
+        <v>175</v>
+      </c>
+      <c r="B409" t="s">
+        <v>16</v>
+      </c>
+      <c r="C409" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A410" t="s">
+        <v>176</v>
+      </c>
+      <c r="B410" t="s">
+        <v>16</v>
+      </c>
+      <c r="C410" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A411" t="s">
+        <v>177</v>
+      </c>
+      <c r="B411" t="s">
+        <v>16</v>
+      </c>
+      <c r="C411" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A412" t="s">
+        <v>178</v>
+      </c>
+      <c r="B412" t="s">
+        <v>16</v>
+      </c>
+      <c r="C412" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A413" t="s">
+        <v>179</v>
+      </c>
+      <c r="B413" t="s">
+        <v>16</v>
+      </c>
+      <c r="C413" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A414" t="s">
+        <v>180</v>
+      </c>
+      <c r="B414" t="s">
+        <v>16</v>
+      </c>
+      <c r="C414" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A415" t="s">
+        <v>181</v>
+      </c>
+      <c r="B415" t="s">
+        <v>16</v>
+      </c>
+      <c r="C415" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A416" t="s">
+        <v>491</v>
+      </c>
+      <c r="B416" t="s">
+        <v>16</v>
+      </c>
+      <c r="C416" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A417" t="s">
+        <v>492</v>
+      </c>
+      <c r="B417" t="s">
+        <v>16</v>
+      </c>
+      <c r="C417" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A418" t="s">
+        <v>493</v>
+      </c>
+      <c r="B418" t="s">
+        <v>16</v>
+      </c>
+      <c r="C418" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A419" t="s">
+        <v>182</v>
+      </c>
+      <c r="B419" t="s">
+        <v>16</v>
+      </c>
+      <c r="C419" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A420" t="s">
+        <v>183</v>
+      </c>
+      <c r="B420" t="s">
+        <v>16</v>
+      </c>
+      <c r="C420" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A421" t="s">
+        <v>494</v>
+      </c>
+      <c r="B421" t="s">
+        <v>16</v>
+      </c>
+      <c r="C421" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A422" t="s">
+        <v>495</v>
+      </c>
+      <c r="B422" t="s">
+        <v>16</v>
+      </c>
+      <c r="C422" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A423" t="s">
+        <v>496</v>
+      </c>
+      <c r="B423" t="s">
+        <v>497</v>
+      </c>
+      <c r="C423" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A424" t="s">
+        <v>498</v>
+      </c>
+      <c r="B424" t="s">
+        <v>4</v>
+      </c>
+      <c r="C424" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A425" t="s">
+        <v>499</v>
+      </c>
+      <c r="B425" t="s">
+        <v>16</v>
+      </c>
+      <c r="C425" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A426" t="s">
+        <v>500</v>
+      </c>
+      <c r="B426" t="s">
+        <v>13</v>
+      </c>
+      <c r="C426" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A427" t="s">
+        <v>501</v>
+      </c>
+      <c r="B427" t="s">
+        <v>4</v>
+      </c>
+      <c r="C427" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A428" t="s">
+        <v>184</v>
+      </c>
+      <c r="B428" t="s">
+        <v>4</v>
+      </c>
+      <c r="C428" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A429" t="s">
         <v>264</v>
       </c>
-      <c r="B273" t="s">
+      <c r="B429" t="s">
+        <v>16</v>
+      </c>
+      <c r="C429" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A430" t="s">
+        <v>185</v>
+      </c>
+      <c r="B430" t="s">
+        <v>16</v>
+      </c>
+      <c r="C430" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A431" t="s">
+        <v>186</v>
+      </c>
+      <c r="B431" t="s">
+        <v>59</v>
+      </c>
+      <c r="C431" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A432" t="s">
+        <v>187</v>
+      </c>
+      <c r="B432" t="s">
+        <v>59</v>
+      </c>
+      <c r="C432" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A433" t="s">
+        <v>188</v>
+      </c>
+      <c r="B433" t="s">
+        <v>59</v>
+      </c>
+      <c r="C433" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A434" t="s">
+        <v>189</v>
+      </c>
+      <c r="B434" t="s">
+        <v>59</v>
+      </c>
+      <c r="C434" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A435" t="s">
+        <v>502</v>
+      </c>
+      <c r="B435" t="s">
         <v>49</v>
       </c>
-      <c r="C273" t="s">
-        <v>105</v>
+      <c r="C435" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A436" t="s">
+        <v>190</v>
+      </c>
+      <c r="B436" t="s">
+        <v>49</v>
+      </c>
+      <c r="C436" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A437" t="s">
+        <v>503</v>
+      </c>
+      <c r="B437" t="s">
+        <v>129</v>
+      </c>
+      <c r="C437" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A438" t="s">
+        <v>504</v>
+      </c>
+      <c r="B438" t="s">
+        <v>129</v>
+      </c>
+      <c r="C438" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A439" t="s">
+        <v>505</v>
+      </c>
+      <c r="B439" t="s">
+        <v>4</v>
+      </c>
+      <c r="C439" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A440" t="s">
+        <v>506</v>
+      </c>
+      <c r="B440" t="s">
+        <v>129</v>
+      </c>
+      <c r="C440" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A441" t="s">
+        <v>507</v>
+      </c>
+      <c r="B441" t="s">
+        <v>310</v>
+      </c>
+      <c r="C441" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A442" t="s">
+        <v>191</v>
+      </c>
+      <c r="B442" t="s">
+        <v>16</v>
+      </c>
+      <c r="C442" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A443" t="s">
+        <v>192</v>
+      </c>
+      <c r="B443" t="s">
+        <v>16</v>
+      </c>
+      <c r="C443" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A444" t="s">
+        <v>193</v>
+      </c>
+      <c r="B444" t="s">
+        <v>16</v>
+      </c>
+      <c r="C444" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A445" t="s">
+        <v>194</v>
+      </c>
+      <c r="B445" t="s">
+        <v>16</v>
+      </c>
+      <c r="C445" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A446" t="s">
+        <v>195</v>
+      </c>
+      <c r="B446" t="s">
+        <v>16</v>
+      </c>
+      <c r="C446" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A447" t="s">
+        <v>196</v>
+      </c>
+      <c r="B447" t="s">
+        <v>16</v>
+      </c>
+      <c r="C447" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A448" t="s">
+        <v>196</v>
+      </c>
+      <c r="B448" t="s">
+        <v>16</v>
+      </c>
+      <c r="C448" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A449" t="s">
+        <v>197</v>
+      </c>
+      <c r="B449" t="s">
+        <v>16</v>
+      </c>
+      <c r="C449" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A450" t="s">
+        <v>198</v>
+      </c>
+      <c r="B450" t="s">
+        <v>13</v>
+      </c>
+      <c r="C450" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A451" t="s">
+        <v>199</v>
+      </c>
+      <c r="B451" t="s">
+        <v>13</v>
+      </c>
+      <c r="C451" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A452" t="s">
+        <v>200</v>
+      </c>
+      <c r="B452" t="s">
+        <v>13</v>
+      </c>
+      <c r="C452" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A453" t="s">
+        <v>508</v>
+      </c>
+      <c r="B453" t="s">
+        <v>13</v>
+      </c>
+      <c r="C453" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A454" t="s">
+        <v>201</v>
+      </c>
+      <c r="B454" t="s">
+        <v>13</v>
+      </c>
+      <c r="C454" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A455" t="s">
+        <v>202</v>
+      </c>
+      <c r="B455" t="s">
+        <v>13</v>
+      </c>
+      <c r="C455" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A456" t="s">
+        <v>509</v>
+      </c>
+      <c r="B456" t="s">
+        <v>13</v>
+      </c>
+      <c r="C456" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A457" t="s">
+        <v>510</v>
+      </c>
+      <c r="B457" t="s">
+        <v>7</v>
+      </c>
+      <c r="C457" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A458" t="s">
+        <v>511</v>
+      </c>
+      <c r="B458" t="s">
+        <v>7</v>
+      </c>
+      <c r="C458" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A459" t="s">
+        <v>512</v>
+      </c>
+      <c r="B459" t="s">
+        <v>7</v>
+      </c>
+      <c r="C459" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A460" t="s">
+        <v>242</v>
+      </c>
+      <c r="B460" t="s">
+        <v>13</v>
+      </c>
+      <c r="C460" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A461" t="s">
+        <v>241</v>
+      </c>
+      <c r="B461" t="s">
+        <v>13</v>
+      </c>
+      <c r="C461" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A462" t="s">
+        <v>203</v>
+      </c>
+      <c r="B462" t="s">
+        <v>13</v>
+      </c>
+      <c r="C462" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A463" t="s">
+        <v>204</v>
+      </c>
+      <c r="B463" t="s">
+        <v>13</v>
+      </c>
+      <c r="C463" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A464" t="s">
+        <v>205</v>
+      </c>
+      <c r="B464" t="s">
+        <v>13</v>
+      </c>
+      <c r="C464" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A465" t="s">
+        <v>206</v>
+      </c>
+      <c r="B465" t="s">
+        <v>13</v>
+      </c>
+      <c r="C465" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A466" t="s">
+        <v>207</v>
+      </c>
+      <c r="B466" t="s">
+        <v>13</v>
+      </c>
+      <c r="C466" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A467" t="s">
+        <v>208</v>
+      </c>
+      <c r="B467" t="s">
+        <v>13</v>
+      </c>
+      <c r="C467" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A468" t="s">
+        <v>209</v>
+      </c>
+      <c r="B468" t="s">
+        <v>13</v>
+      </c>
+      <c r="C468" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A469" t="s">
+        <v>513</v>
+      </c>
+      <c r="B469" t="s">
+        <v>13</v>
+      </c>
+      <c r="C469" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A470" t="s">
+        <v>210</v>
+      </c>
+      <c r="B470" t="s">
+        <v>13</v>
+      </c>
+      <c r="C470" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A471" t="s">
+        <v>514</v>
+      </c>
+      <c r="B471" t="s">
+        <v>13</v>
+      </c>
+      <c r="C471" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A472" t="s">
+        <v>211</v>
+      </c>
+      <c r="B472" t="s">
+        <v>13</v>
+      </c>
+      <c r="C472" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A473" t="s">
+        <v>515</v>
+      </c>
+      <c r="B473" t="s">
+        <v>13</v>
+      </c>
+      <c r="C473" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A474" t="s">
+        <v>516</v>
+      </c>
+      <c r="B474" t="s">
+        <v>13</v>
+      </c>
+      <c r="C474" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A475" t="s">
+        <v>517</v>
+      </c>
+      <c r="B475" t="s">
+        <v>7</v>
+      </c>
+      <c r="C475" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A476" t="s">
+        <v>212</v>
+      </c>
+      <c r="B476" t="s">
+        <v>11</v>
+      </c>
+      <c r="C476" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A477" t="s">
+        <v>213</v>
+      </c>
+      <c r="B477" t="s">
+        <v>11</v>
+      </c>
+      <c r="C477" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A478" t="s">
+        <v>214</v>
+      </c>
+      <c r="B478" t="s">
+        <v>11</v>
+      </c>
+      <c r="C478" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A479" t="s">
+        <v>215</v>
+      </c>
+      <c r="B479" t="s">
+        <v>11</v>
+      </c>
+      <c r="C479" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A480" t="s">
+        <v>216</v>
+      </c>
+      <c r="B480" t="s">
+        <v>11</v>
+      </c>
+      <c r="C480" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A481" t="s">
+        <v>217</v>
+      </c>
+      <c r="B481" t="s">
+        <v>11</v>
+      </c>
+      <c r="C481" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A482" t="s">
+        <v>218</v>
+      </c>
+      <c r="B482" t="s">
+        <v>11</v>
+      </c>
+      <c r="C482" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A483" t="s">
+        <v>285</v>
+      </c>
+      <c r="B483" t="s">
+        <v>11</v>
+      </c>
+      <c r="C483" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A484" t="s">
+        <v>518</v>
+      </c>
+      <c r="B484" t="s">
+        <v>11</v>
+      </c>
+      <c r="C484" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A485" t="s">
+        <v>519</v>
+      </c>
+      <c r="B485" t="s">
+        <v>11</v>
+      </c>
+      <c r="C485" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A486" t="s">
+        <v>520</v>
+      </c>
+      <c r="B486" t="s">
+        <v>11</v>
+      </c>
+      <c r="C486" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A487" t="s">
+        <v>219</v>
+      </c>
+      <c r="B487" t="s">
+        <v>11</v>
+      </c>
+      <c r="C487" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A488" t="s">
+        <v>220</v>
+      </c>
+      <c r="B488" t="s">
+        <v>11</v>
+      </c>
+      <c r="C488" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A489" t="s">
+        <v>221</v>
+      </c>
+      <c r="B489" t="s">
+        <v>11</v>
+      </c>
+      <c r="C489" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A490" t="s">
+        <v>222</v>
+      </c>
+      <c r="B490" t="s">
+        <v>11</v>
+      </c>
+      <c r="C490" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A491" t="s">
+        <v>521</v>
+      </c>
+      <c r="B491" t="s">
+        <v>49</v>
+      </c>
+      <c r="C491" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A492" t="s">
+        <v>223</v>
+      </c>
+      <c r="B492" t="s">
+        <v>49</v>
+      </c>
+      <c r="C492" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A493" t="s">
+        <v>224</v>
+      </c>
+      <c r="B493" t="s">
+        <v>49</v>
+      </c>
+      <c r="C493" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A494" t="s">
+        <v>225</v>
+      </c>
+      <c r="B494" t="s">
+        <v>49</v>
+      </c>
+      <c r="C494" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A495" t="s">
+        <v>226</v>
+      </c>
+      <c r="B495" t="s">
+        <v>49</v>
+      </c>
+      <c r="C495" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A496" t="s">
+        <v>227</v>
+      </c>
+      <c r="B496" t="s">
+        <v>49</v>
+      </c>
+      <c r="C496" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A497" t="s">
+        <v>228</v>
+      </c>
+      <c r="B497" t="s">
+        <v>49</v>
+      </c>
+      <c r="C497" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A498" t="s">
+        <v>229</v>
+      </c>
+      <c r="B498" t="s">
+        <v>49</v>
+      </c>
+      <c r="C498" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A499" t="s">
+        <v>522</v>
+      </c>
+      <c r="B499" t="s">
+        <v>49</v>
+      </c>
+      <c r="C499" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A500" t="s">
+        <v>523</v>
+      </c>
+      <c r="B500" t="s">
+        <v>49</v>
+      </c>
+      <c r="C500" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A501" t="s">
+        <v>524</v>
+      </c>
+      <c r="B501" t="s">
+        <v>49</v>
+      </c>
+      <c r="C501" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A502" t="s">
+        <v>525</v>
+      </c>
+      <c r="B502" t="s">
+        <v>16</v>
+      </c>
+      <c r="C502" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A503" t="s">
+        <v>526</v>
+      </c>
+      <c r="B503" t="s">
+        <v>16</v>
+      </c>
+      <c r="C503" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A504" t="s">
+        <v>527</v>
+      </c>
+      <c r="B504" t="s">
+        <v>16</v>
+      </c>
+      <c r="C504" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A505" t="s">
+        <v>528</v>
+      </c>
+      <c r="B505" t="s">
+        <v>16</v>
+      </c>
+      <c r="C505" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A506" t="s">
+        <v>230</v>
+      </c>
+      <c r="B506" t="s">
+        <v>7</v>
+      </c>
+      <c r="C506" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A507" t="s">
+        <v>250</v>
+      </c>
+      <c r="B507" t="s">
+        <v>13</v>
+      </c>
+      <c r="C507" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A508" t="s">
+        <v>231</v>
+      </c>
+      <c r="B508" t="s">
+        <v>4</v>
+      </c>
+      <c r="C508" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A509" t="s">
+        <v>233</v>
+      </c>
+      <c r="B509" t="s">
+        <v>4</v>
+      </c>
+      <c r="C509" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A510" t="s">
+        <v>234</v>
+      </c>
+      <c r="B510" t="s">
+        <v>4</v>
+      </c>
+      <c r="C510" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A511" t="s">
+        <v>235</v>
+      </c>
+      <c r="B511" t="s">
+        <v>11</v>
+      </c>
+      <c r="C511" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A512" t="s">
+        <v>236</v>
+      </c>
+      <c r="B512" t="s">
+        <v>13</v>
+      </c>
+      <c r="C512" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A513" t="s">
+        <v>237</v>
+      </c>
+      <c r="B513" t="s">
+        <v>13</v>
+      </c>
+      <c r="C513" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A514" t="s">
+        <v>238</v>
+      </c>
+      <c r="B514" t="s">
+        <v>239</v>
+      </c>
+      <c r="C514" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A515" t="s">
+        <v>281</v>
+      </c>
+      <c r="B515" t="s">
+        <v>11</v>
+      </c>
+      <c r="C515" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A516" t="s">
+        <v>282</v>
+      </c>
+      <c r="B516" t="s">
+        <v>11</v>
+      </c>
+      <c r="C516" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A517" t="s">
+        <v>103</v>
+      </c>
+      <c r="B517" t="s">
+        <v>11</v>
+      </c>
+      <c r="C517" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A518" t="s">
+        <v>259</v>
+      </c>
+      <c r="B518" t="s">
+        <v>49</v>
+      </c>
+      <c r="C518" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A519" t="s">
+        <v>260</v>
+      </c>
+      <c r="B519" t="s">
+        <v>49</v>
+      </c>
+      <c r="C519" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A520" t="s">
+        <v>529</v>
+      </c>
+      <c r="B520" t="s">
+        <v>49</v>
+      </c>
+      <c r="C520" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A521" t="s">
+        <v>531</v>
+      </c>
+      <c r="B521" t="s">
+        <v>59</v>
+      </c>
+      <c r="C521" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A522" t="s">
+        <v>532</v>
+      </c>
+      <c r="B522" t="s">
+        <v>49</v>
+      </c>
+      <c r="C522" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A523" t="s">
+        <v>533</v>
+      </c>
+      <c r="B523" t="s">
+        <v>49</v>
+      </c>
+      <c r="C523" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A524" t="s">
+        <v>534</v>
+      </c>
+      <c r="B524" t="s">
+        <v>13</v>
+      </c>
+      <c r="C524" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A525" t="s">
+        <v>535</v>
+      </c>
+      <c r="B525" t="s">
+        <v>13</v>
+      </c>
+      <c r="C525" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A526" t="s">
+        <v>536</v>
+      </c>
+      <c r="B526" t="s">
+        <v>13</v>
+      </c>
+      <c r="C526" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A527" t="s">
+        <v>537</v>
+      </c>
+      <c r="B527" t="s">
+        <v>497</v>
+      </c>
+      <c r="C527" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A528" t="s">
+        <v>538</v>
+      </c>
+      <c r="B528" t="s">
+        <v>497</v>
+      </c>
+      <c r="C528" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A529" t="s">
+        <v>539</v>
+      </c>
+      <c r="B529" t="s">
+        <v>7</v>
+      </c>
+      <c r="C529" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A530" t="s">
+        <v>540</v>
+      </c>
+      <c r="B530" t="s">
+        <v>4</v>
+      </c>
+      <c r="C530" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A531" t="s">
+        <v>541</v>
+      </c>
+      <c r="B531" t="s">
+        <v>497</v>
+      </c>
+      <c r="C531" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A532" t="s">
+        <v>542</v>
+      </c>
+      <c r="B532" t="s">
+        <v>59</v>
+      </c>
+      <c r="C532" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A533" t="s">
+        <v>543</v>
+      </c>
+      <c r="B533" t="s">
+        <v>59</v>
+      </c>
+      <c r="C533" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A534" t="s">
+        <v>544</v>
+      </c>
+      <c r="B534" t="s">
+        <v>16</v>
+      </c>
+      <c r="C534" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A535" t="s">
+        <v>545</v>
+      </c>
+      <c r="B535" t="s">
+        <v>16</v>
+      </c>
+      <c r="C535" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A536" t="s">
+        <v>546</v>
+      </c>
+      <c r="B536" t="s">
+        <v>13</v>
+      </c>
+      <c r="C536" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A537" t="s">
+        <v>547</v>
+      </c>
+      <c r="B537" t="s">
+        <v>7</v>
+      </c>
+      <c r="C537" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A538" t="s">
+        <v>548</v>
+      </c>
+      <c r="B538" t="s">
+        <v>7</v>
+      </c>
+      <c r="C538" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A539" t="s">
+        <v>549</v>
+      </c>
+      <c r="B539" t="s">
+        <v>11</v>
+      </c>
+      <c r="C539" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A540" t="s">
+        <v>550</v>
+      </c>
+      <c r="B540" t="s">
+        <v>16</v>
+      </c>
+      <c r="C540" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A541" t="s">
+        <v>551</v>
+      </c>
+      <c r="B541" t="s">
+        <v>16</v>
+      </c>
+      <c r="C541" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A542" t="s">
+        <v>552</v>
+      </c>
+      <c r="B542" t="s">
+        <v>59</v>
+      </c>
+      <c r="C542" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A543" t="s">
+        <v>552</v>
+      </c>
+      <c r="B543" t="s">
+        <v>59</v>
+      </c>
+      <c r="C543" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A544" t="s">
+        <v>553</v>
+      </c>
+      <c r="B544" t="s">
+        <v>16</v>
+      </c>
+      <c r="C544" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A545" t="s">
+        <v>554</v>
+      </c>
+      <c r="B545" t="s">
+        <v>49</v>
+      </c>
+      <c r="C545" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A546" t="s">
+        <v>555</v>
+      </c>
+      <c r="B546" t="s">
+        <v>49</v>
+      </c>
+      <c r="C546" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A547" t="s">
+        <v>556</v>
+      </c>
+      <c r="B547" t="s">
+        <v>16</v>
+      </c>
+      <c r="C547" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A548" t="s">
+        <v>557</v>
+      </c>
+      <c r="B548" t="s">
+        <v>239</v>
+      </c>
+      <c r="C548" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A549" t="s">
+        <v>558</v>
+      </c>
+      <c r="B549" t="s">
+        <v>129</v>
+      </c>
+      <c r="C549" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A550" t="s">
+        <v>559</v>
+      </c>
+      <c r="B550" t="s">
+        <v>111</v>
+      </c>
+      <c r="C550" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A551" t="s">
+        <v>560</v>
+      </c>
+      <c r="B551" t="s">
+        <v>4</v>
+      </c>
+      <c r="C551" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A552" t="s">
+        <v>561</v>
+      </c>
+      <c r="B552" t="s">
+        <v>13</v>
+      </c>
+      <c r="C552" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A553" t="s">
+        <v>562</v>
+      </c>
+      <c r="B553" t="s">
+        <v>11</v>
+      </c>
+      <c r="C553" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A554" t="s">
+        <v>563</v>
+      </c>
+      <c r="B554" t="s">
+        <v>310</v>
+      </c>
+      <c r="C554" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A555" t="s">
+        <v>564</v>
+      </c>
+      <c r="B555" t="s">
+        <v>565</v>
+      </c>
+      <c r="C555" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A556" t="s">
+        <v>566</v>
+      </c>
+      <c r="B556" t="s">
+        <v>13</v>
+      </c>
+      <c r="C556" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A557" t="s">
+        <v>567</v>
+      </c>
+      <c r="B557" t="s">
+        <v>13</v>
+      </c>
+      <c r="C557" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A558" t="s">
+        <v>568</v>
+      </c>
+      <c r="B558" t="s">
+        <v>13</v>
+      </c>
+      <c r="C558" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A559" t="s">
+        <v>569</v>
+      </c>
+      <c r="B559" t="s">
+        <v>13</v>
+      </c>
+      <c r="C559" t="s">
+        <v>530</v>
       </c>
     </row>
   </sheetData>

--- a/Vehicle Catalogue.xlsx
+++ b/Vehicle Catalogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samhi\Documents\My Games\Sprocket\Ostfront Tank Collection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1164B612-E385-4CF7-80AA-EB9772E2BEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536E3F5A-963C-41F0-B917-7258261C31FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{3FAC36FE-B102-4B04-8548-70F58966D145}"/>
+    <workbookView xWindow="8150" yWindow="2920" windowWidth="28800" windowHeight="15360" xr2:uid="{3FAC36FE-B102-4B04-8548-70F58966D145}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="558">
   <si>
     <t>Tank</t>
   </si>
@@ -167,15 +167,6 @@
     <t>SU-152</t>
   </si>
   <si>
-    <t>T29</t>
-  </si>
-  <si>
-    <t>T30</t>
-  </si>
-  <si>
-    <t>T34</t>
-  </si>
-  <si>
     <t>T-35</t>
   </si>
   <si>
@@ -188,9 +179,6 @@
     <t>Tiger 2P</t>
   </si>
   <si>
-    <t>TOG 2</t>
-  </si>
-  <si>
     <t>United Kingdom</t>
   </si>
   <si>
@@ -203,9 +191,6 @@
     <t>Vickers A1E1 Independent</t>
   </si>
   <si>
-    <t>VK 45.01 P</t>
-  </si>
-  <si>
     <t>VK 45.03</t>
   </si>
   <si>
@@ -428,12 +413,6 @@
     <t>Jagdpanzer IV/70(V)</t>
   </si>
   <si>
-    <t>LT vz. 35</t>
-  </si>
-  <si>
-    <t>Czechoslovakia</t>
-  </si>
-  <si>
     <t>M15 Contraereo</t>
   </si>
   <si>
@@ -665,9 +644,6 @@
     <t>T-34-76 (1941)E</t>
   </si>
   <si>
-    <t>T-34-76 (1942)</t>
-  </si>
-  <si>
     <t>T-34-76 (1943)</t>
   </si>
   <si>
@@ -857,9 +833,6 @@
     <t>E-10</t>
   </si>
   <si>
-    <t>E-25</t>
-  </si>
-  <si>
     <t>Panzerjäger Wanze</t>
   </si>
   <si>
@@ -1244,9 +1217,6 @@
     <t>Waffenträger auf Pz. IV</t>
   </si>
   <si>
-    <t>Wz.40</t>
-  </si>
-  <si>
     <t>4TP</t>
   </si>
   <si>
@@ -1280,9 +1250,6 @@
     <t>Kolohousenka</t>
   </si>
   <si>
-    <t>Lago M38</t>
-  </si>
-  <si>
     <t>Landsverk L-60</t>
   </si>
   <si>
@@ -1430,9 +1397,6 @@
     <t>25TP KSUST II</t>
   </si>
   <si>
-    <t>A24 Cavalier</t>
-  </si>
-  <si>
     <t>A24 Cruiser Mk VII Cavalier</t>
   </si>
   <si>
@@ -1448,12 +1412,6 @@
     <t>A7E3</t>
   </si>
   <si>
-    <t>AC 1 Sentinel</t>
-  </si>
-  <si>
-    <t>AC 4 Sentinel</t>
-  </si>
-  <si>
     <t>AT 2</t>
   </si>
   <si>
@@ -1553,9 +1511,6 @@
     <t>Sexton I</t>
   </si>
   <si>
-    <t>Škoda T 24</t>
-  </si>
-  <si>
     <t>Škoda T 25</t>
   </si>
   <si>
@@ -1752,6 +1707,15 @@
   </si>
   <si>
     <t>ZiS-6</t>
+  </si>
+  <si>
+    <t>VK 45.01 (P)</t>
+  </si>
+  <si>
+    <t>Czechia</t>
+  </si>
+  <si>
+    <t>Semovente da 90/53 M41M</t>
   </si>
 </sst>
 </file>
@@ -1806,7 +1770,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1814,16 +1778,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2159,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C50DCCC-8446-4FAC-BA76-D53F2D86B716}">
-  <dimension ref="A1:C559"/>
+  <dimension ref="A1:C542"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.81640625" customWidth="1"/>
@@ -2180,447 +2160,447 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B8" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C8" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B21" t="s">
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="B22" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="C22" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B24" t="s">
         <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="B26" t="s">
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B28" t="s">
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="B29" t="s">
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="B30" t="s">
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="B31" t="s">
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="B32" t="s">
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s">
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="B34" t="s">
         <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s">
         <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s">
         <v>7</v>
       </c>
       <c r="C36" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s">
         <v>7</v>
       </c>
       <c r="C37" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B40" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C40" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="B41" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C41" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B42" t="s">
         <v>16</v>
@@ -2664,10 +2644,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="B46" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C46" t="s">
         <v>8</v>
@@ -2708,263 +2688,263 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="B50" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="B51" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="B52" t="s">
         <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="B53" t="s">
         <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="B54" t="s">
         <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="B55" t="s">
         <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="B56" t="s">
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="B57" t="s">
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="B60" t="s">
         <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="B61" t="s">
         <v>4</v>
       </c>
       <c r="C61" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="B62" t="s">
         <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="B63" t="s">
         <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B64" t="s">
         <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="B65" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C65" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B66" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C66" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="B67" t="s">
         <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B68" t="s">
         <v>16</v>
       </c>
       <c r="C68" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B69" t="s">
         <v>16</v>
       </c>
       <c r="C69" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="B70" t="s">
         <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="B71" t="s">
         <v>7</v>
       </c>
       <c r="C71" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B73" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C73" t="s">
         <v>17</v>
@@ -2972,10 +2952,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B74" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C74" t="s">
         <v>17</v>
@@ -2983,7 +2963,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="B75" t="s">
         <v>4</v>
@@ -2994,10 +2974,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="B76" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C76" t="s">
         <v>17</v>
@@ -3005,10 +2985,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B77" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C77" t="s">
         <v>17</v>
@@ -3016,7 +2996,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B78" t="s">
         <v>4</v>
@@ -3027,10 +3007,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B79" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C79" t="s">
         <v>17</v>
@@ -3038,7 +3018,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B80" t="s">
         <v>11</v>
@@ -3049,10 +3029,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B81" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C81" t="s">
         <v>17</v>
@@ -3060,7 +3040,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="B82" t="s">
         <v>16</v>
@@ -3071,7 +3051,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B83" t="s">
         <v>16</v>
@@ -3104,10 +3084,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="B86" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C86" t="s">
         <v>17</v>
@@ -3115,7 +3095,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="B87" t="s">
         <v>16</v>
@@ -3126,7 +3106,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B88" t="s">
         <v>16</v>
@@ -3137,7 +3117,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="B89" t="s">
         <v>16</v>
@@ -3236,7 +3216,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -3247,7 +3227,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -3258,7 +3238,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="B100" t="s">
         <v>16</v>
@@ -3313,7 +3293,7 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B105" t="s">
         <v>13</v>
@@ -3324,7 +3304,7 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B106" t="s">
         <v>13</v>
@@ -3335,7 +3315,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B107" t="s">
         <v>13</v>
@@ -3346,7 +3326,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B108" t="s">
         <v>13</v>
@@ -3390,7 +3370,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B112" t="s">
         <v>13</v>
@@ -3423,7 +3403,7 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B115" t="s">
         <v>16</v>
@@ -3434,7 +3414,7 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B116" t="s">
         <v>13</v>
@@ -3445,7 +3425,7 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B117" t="s">
         <v>13</v>
@@ -3467,7 +3447,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B119" t="s">
         <v>13</v>
@@ -3478,7 +3458,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B120" t="s">
         <v>13</v>
@@ -3489,7 +3469,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B121" t="s">
         <v>13</v>
@@ -3500,7 +3480,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B122" t="s">
         <v>11</v>
@@ -3511,7 +3491,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B123" t="s">
         <v>16</v>
@@ -3522,7 +3502,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B124" t="s">
         <v>7</v>
@@ -3533,7 +3513,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="B125" t="s">
         <v>16</v>
@@ -3555,7 +3535,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B127" t="s">
         <v>16</v>
@@ -3566,7 +3546,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B128" t="s">
         <v>16</v>
@@ -3577,7 +3557,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B129" t="s">
         <v>13</v>
@@ -3588,7 +3568,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="B130" t="s">
         <v>16</v>
@@ -3599,7 +3579,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="B131" t="s">
         <v>16</v>
@@ -3610,7 +3590,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B132" t="s">
         <v>16</v>
@@ -3632,7 +3612,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B134" t="s">
         <v>13</v>
@@ -3643,7 +3623,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="B135" t="s">
         <v>13</v>
@@ -3654,7 +3634,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="B136" t="s">
         <v>16</v>
@@ -3698,7 +3678,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="B140" t="s">
         <v>13</v>
@@ -3709,7 +3689,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="B141" t="s">
         <v>13</v>
@@ -3720,7 +3700,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="B142" t="s">
         <v>13</v>
@@ -3731,7 +3711,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="B143" t="s">
         <v>13</v>
@@ -3742,7 +3722,7 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B144" t="s">
         <v>13</v>
@@ -3786,7 +3766,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="B148" t="s">
         <v>13</v>
@@ -3797,7 +3777,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B149" t="s">
         <v>13</v>
@@ -3808,7 +3788,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="B150" t="s">
         <v>7</v>
@@ -3819,7 +3799,7 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B151" t="s">
         <v>13</v>
@@ -3830,7 +3810,7 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="B152" t="s">
         <v>7</v>
@@ -3841,7 +3821,7 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B153" t="s">
         <v>7</v>
@@ -3852,7 +3832,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>41</v>
+        <v>380</v>
       </c>
       <c r="B154" t="s">
         <v>7</v>
@@ -3866,7 +3846,7 @@
         <v>41</v>
       </c>
       <c r="B155" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C155" t="s">
         <v>17</v>
@@ -3877,7 +3857,7 @@
         <v>42</v>
       </c>
       <c r="B156" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C156" t="s">
         <v>17</v>
@@ -3885,7 +3865,7 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>42</v>
+        <v>247</v>
       </c>
       <c r="B157" t="s">
         <v>7</v>
@@ -3896,10 +3876,10 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>389</v>
+        <v>43</v>
       </c>
       <c r="B158" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C158" t="s">
         <v>17</v>
@@ -3907,10 +3887,10 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B159" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C159" t="s">
         <v>17</v>
@@ -3918,10 +3898,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="B160" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
@@ -3929,10 +3909,10 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>44</v>
+        <v>381</v>
       </c>
       <c r="B161" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C161" t="s">
         <v>17</v>
@@ -3940,10 +3920,10 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>45</v>
+        <v>275</v>
       </c>
       <c r="B162" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C162" t="s">
         <v>17</v>
@@ -3951,10 +3931,10 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>255</v>
+        <v>382</v>
       </c>
       <c r="B163" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C163" t="s">
         <v>17</v>
@@ -3962,10 +3942,10 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>255</v>
+        <v>46</v>
       </c>
       <c r="B164" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C164" t="s">
         <v>17</v>
@@ -3973,10 +3953,10 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B165" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C165" t="s">
         <v>17</v>
@@ -3984,10 +3964,10 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B166" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C166" t="s">
         <v>17</v>
@@ -3995,10 +3975,10 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>48</v>
+        <v>383</v>
       </c>
       <c r="B167" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C167" t="s">
         <v>17</v>
@@ -4006,7 +3986,7 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>244</v>
+        <v>384</v>
       </c>
       <c r="B168" t="s">
         <v>16</v>
@@ -4017,10 +3997,10 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B169" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C169" t="s">
         <v>17</v>
@@ -4028,10 +4008,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>284</v>
+        <v>386</v>
       </c>
       <c r="B170" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C170" t="s">
         <v>17</v>
@@ -4039,10 +4019,10 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>391</v>
+        <v>555</v>
       </c>
       <c r="B171" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C171" t="s">
         <v>17</v>
@@ -4050,10 +4030,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>50</v>
+        <v>387</v>
       </c>
       <c r="B172" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C172" t="s">
         <v>17</v>
@@ -4061,10 +4041,10 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>51</v>
+        <v>257</v>
       </c>
       <c r="B173" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C173" t="s">
         <v>17</v>
@@ -4072,10 +4052,10 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B174" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C174" t="s">
         <v>17</v>
@@ -4083,7 +4063,7 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B175" t="s">
         <v>16</v>
@@ -4094,10 +4074,10 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B176" t="s">
-        <v>16</v>
+        <v>556</v>
       </c>
       <c r="C176" t="s">
         <v>17</v>
@@ -4105,7 +4085,7 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B177" t="s">
         <v>16</v>
@@ -4116,211 +4096,211 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>395</v>
+        <v>277</v>
       </c>
       <c r="B178" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="C178" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>53</v>
+        <v>391</v>
       </c>
       <c r="B179" t="s">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c r="C179" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B180" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C180" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>265</v>
+        <v>393</v>
       </c>
       <c r="B181" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C181" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>54</v>
+        <v>394</v>
       </c>
       <c r="B182" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C182" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B183" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C183" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B184" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="C184" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>399</v>
+        <v>50</v>
       </c>
       <c r="B185" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C185" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>400</v>
+        <v>262</v>
       </c>
       <c r="B186" t="s">
-        <v>239</v>
+        <v>16</v>
       </c>
       <c r="C186" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>286</v>
+        <v>52</v>
       </c>
       <c r="B187" t="s">
-        <v>111</v>
+        <v>4</v>
       </c>
       <c r="C187" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B188" t="s">
-        <v>239</v>
+        <v>4</v>
       </c>
       <c r="C188" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>402</v>
+        <v>53</v>
       </c>
       <c r="B189" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C189" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B190" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C190" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>404</v>
+        <v>55</v>
       </c>
       <c r="B191" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C191" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>405</v>
+        <v>56</v>
       </c>
       <c r="B192" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C192" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B193" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C193" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>55</v>
+        <v>401</v>
       </c>
       <c r="B194" t="s">
-        <v>4</v>
+        <v>556</v>
       </c>
       <c r="C194" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B195" t="s">
-        <v>7</v>
+        <v>301</v>
       </c>
       <c r="C195" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>270</v>
+        <v>403</v>
       </c>
       <c r="B196" t="s">
         <v>16</v>
       </c>
       <c r="C196" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
@@ -4328,21 +4308,21 @@
         <v>57</v>
       </c>
       <c r="B197" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C197" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B198" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C198" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
@@ -4350,98 +4330,98 @@
         <v>58</v>
       </c>
       <c r="B199" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C199" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>409</v>
+        <v>226</v>
       </c>
       <c r="B200" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C200" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>60</v>
+        <v>405</v>
       </c>
       <c r="B201" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C201" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>61</v>
+        <v>406</v>
       </c>
       <c r="B202" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C202" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>410</v>
+        <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="C203" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>411</v>
+        <v>60</v>
       </c>
       <c r="B204" t="s">
-        <v>129</v>
+        <v>7</v>
       </c>
       <c r="C204" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>412</v>
+        <v>248</v>
       </c>
       <c r="B205" t="s">
-        <v>310</v>
+        <v>7</v>
       </c>
       <c r="C205" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>413</v>
+        <v>61</v>
       </c>
       <c r="B206" t="s">
-        <v>310</v>
+        <v>7</v>
       </c>
       <c r="C206" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="B207" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C207" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
@@ -4449,307 +4429,307 @@
         <v>62</v>
       </c>
       <c r="B208" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B209" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="C209" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>63</v>
+        <v>409</v>
       </c>
       <c r="B210" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C210" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>234</v>
+        <v>63</v>
       </c>
       <c r="B211" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C211" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B212" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="C212" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>417</v>
+        <v>64</v>
       </c>
       <c r="B213" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C213" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B214" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C214" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B215" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C215" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>256</v>
+        <v>67</v>
       </c>
       <c r="B216" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C216" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B217" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C217" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="B218" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C218" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>67</v>
+        <v>412</v>
       </c>
       <c r="B219" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C219" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B220" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C220" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>420</v>
+        <v>232</v>
       </c>
       <c r="B221" t="s">
         <v>7</v>
       </c>
       <c r="C221" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A222" t="s">
-        <v>68</v>
+      <c r="A222" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="B222" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C222" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>421</v>
+        <v>70</v>
       </c>
       <c r="B223" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C223" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B224" t="s">
         <v>16</v>
       </c>
       <c r="C224" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B225" t="s">
         <v>16</v>
       </c>
       <c r="C225" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B226" t="s">
         <v>16</v>
       </c>
       <c r="C226" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B227" t="s">
         <v>16</v>
       </c>
       <c r="C227" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B228" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C228" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>422</v>
+        <v>263</v>
       </c>
       <c r="B229" t="s">
         <v>16</v>
       </c>
       <c r="C229" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="B230" t="s">
-        <v>13</v>
+        <v>556</v>
       </c>
       <c r="C230" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="B231" t="s">
-        <v>13</v>
+        <v>301</v>
       </c>
       <c r="C231" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>240</v>
+        <v>416</v>
       </c>
       <c r="B232" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C232" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B233" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C233" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>75</v>
+        <v>417</v>
       </c>
       <c r="B234" t="s">
         <v>16</v>
       </c>
       <c r="C234" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>76</v>
+        <v>261</v>
       </c>
       <c r="B235" t="s">
         <v>16</v>
       </c>
       <c r="C235" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
@@ -4757,10 +4737,10 @@
         <v>77</v>
       </c>
       <c r="B236" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C236" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
@@ -4768,76 +4748,76 @@
         <v>78</v>
       </c>
       <c r="B237" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C237" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>79</v>
+        <v>418</v>
       </c>
       <c r="B238" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C238" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>80</v>
+        <v>419</v>
       </c>
       <c r="B239" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C239" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>272</v>
+        <v>420</v>
       </c>
       <c r="B240" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C240" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B241" t="s">
-        <v>129</v>
+        <v>301</v>
       </c>
       <c r="C241" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="B242" t="s">
-        <v>310</v>
+        <v>16</v>
       </c>
       <c r="C242" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="B243" t="s">
         <v>16</v>
       </c>
       <c r="C243" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
@@ -4845,32 +4825,32 @@
         <v>81</v>
       </c>
       <c r="B244" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C244" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B245" t="s">
-        <v>16</v>
+        <v>556</v>
       </c>
       <c r="C245" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>269</v>
+        <v>423</v>
       </c>
       <c r="B246" t="s">
-        <v>16</v>
+        <v>556</v>
       </c>
       <c r="C246" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
@@ -4878,274 +4858,274 @@
         <v>82</v>
       </c>
       <c r="B247" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C247" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>83</v>
+        <v>424</v>
       </c>
       <c r="B248" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C248" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B249" t="s">
-        <v>4</v>
+        <v>301</v>
       </c>
       <c r="C249" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B250" t="s">
-        <v>4</v>
+        <v>301</v>
       </c>
       <c r="C250" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B251" t="s">
-        <v>4</v>
+        <v>301</v>
       </c>
       <c r="C251" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B252" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="C252" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B253" t="s">
         <v>16</v>
       </c>
       <c r="C253" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>85</v>
+        <v>429</v>
       </c>
       <c r="B254" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C254" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B255" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="C255" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>433</v>
+        <v>84</v>
       </c>
       <c r="B256" t="s">
-        <v>129</v>
+        <v>7</v>
       </c>
       <c r="C256" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B257" t="s">
-        <v>129</v>
+        <v>7</v>
       </c>
       <c r="C257" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>87</v>
+        <v>431</v>
       </c>
       <c r="B258" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C258" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B259" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C259" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>436</v>
+        <v>85</v>
       </c>
       <c r="B260" t="s">
-        <v>310</v>
+        <v>13</v>
       </c>
       <c r="C260" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>437</v>
+        <v>85</v>
       </c>
       <c r="B261" t="s">
-        <v>310</v>
+        <v>86</v>
       </c>
       <c r="C261" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B262" t="s">
-        <v>310</v>
+        <v>7</v>
       </c>
       <c r="C262" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B263" t="s">
-        <v>310</v>
+        <v>7</v>
       </c>
       <c r="C263" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>88</v>
+        <v>435</v>
       </c>
       <c r="B264" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C264" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B265" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C265" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B266" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C266" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B267" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C267" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B268" t="s">
         <v>7</v>
       </c>
       <c r="C268" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>442</v>
+        <v>89</v>
       </c>
       <c r="B269" t="s">
         <v>13</v>
       </c>
       <c r="C269" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B270" t="s">
         <v>13</v>
       </c>
       <c r="C270" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>90</v>
+        <v>439</v>
       </c>
       <c r="B271" t="s">
         <v>13</v>
       </c>
       <c r="C271" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
@@ -5153,87 +5133,87 @@
         <v>90</v>
       </c>
       <c r="B272" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="C272" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B273" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C273" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B274" t="s">
         <v>7</v>
       </c>
       <c r="C274" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>446</v>
+        <v>91</v>
       </c>
       <c r="B275" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C275" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>447</v>
+        <v>92</v>
       </c>
       <c r="B276" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C276" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>92</v>
+        <v>442</v>
       </c>
       <c r="B277" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C277" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>93</v>
+        <v>443</v>
       </c>
       <c r="B278" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C278" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>448</v>
+        <v>93</v>
       </c>
       <c r="B279" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C279" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
@@ -5244,3076 +5224,2889 @@
         <v>13</v>
       </c>
       <c r="C280" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>449</v>
+        <v>249</v>
       </c>
       <c r="B281" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C281" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>450</v>
+        <v>95</v>
       </c>
       <c r="B282" t="s">
         <v>13</v>
       </c>
       <c r="C282" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>95</v>
+        <v>444</v>
       </c>
       <c r="B283" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C283" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B284" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C284" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>452</v>
+        <v>96</v>
       </c>
       <c r="B285" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C285" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="B286" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C286" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>97</v>
+        <v>446</v>
       </c>
       <c r="B287" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C287" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>453</v>
+        <v>97</v>
       </c>
       <c r="B288" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C288" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="B289" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C289" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B290" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C290" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B291" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C291" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>257</v>
+        <v>102</v>
       </c>
       <c r="B292" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C292" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B293" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C293" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B294" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C294" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="B295" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C295" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B296" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C296" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="B297" t="s">
-        <v>11</v>
+        <v>231</v>
       </c>
       <c r="C297" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="B298" t="s">
-        <v>11</v>
+        <v>231</v>
       </c>
       <c r="C298" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B299" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="C299" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>458</v>
+        <v>108</v>
       </c>
       <c r="B300" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="C300" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>105</v>
+        <v>451</v>
       </c>
       <c r="B301" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C301" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>106</v>
+        <v>452</v>
       </c>
       <c r="B302" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C302" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>107</v>
+        <v>453</v>
       </c>
       <c r="B303" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C303" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>108</v>
+        <v>454</v>
       </c>
       <c r="B304" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C304" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B305" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C305" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B306" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C306" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>109</v>
+        <v>457</v>
       </c>
       <c r="B307" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C307" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>262</v>
+        <v>458</v>
       </c>
       <c r="B308" t="s">
-        <v>239</v>
+        <v>45</v>
       </c>
       <c r="C308" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B309" t="s">
-        <v>239</v>
+        <v>16</v>
       </c>
       <c r="C309" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>110</v>
+        <v>460</v>
       </c>
       <c r="B310" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="C310" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>113</v>
+        <v>461</v>
       </c>
       <c r="B311" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="C311" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>462</v>
+        <v>397</v>
       </c>
       <c r="B312" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="C312" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B313" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="C313" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>464</v>
+        <v>109</v>
       </c>
       <c r="B314" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C314" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>465</v>
+        <v>110</v>
       </c>
       <c r="B315" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C315" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>466</v>
+        <v>111</v>
       </c>
       <c r="B316" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C316" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>467</v>
+        <v>112</v>
       </c>
       <c r="B317" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C317" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B318" t="s">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c r="C318" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>469</v>
+        <v>113</v>
       </c>
       <c r="B319" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C319" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>470</v>
+        <v>114</v>
       </c>
       <c r="B320" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C320" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>471</v>
+        <v>267</v>
       </c>
       <c r="B321" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C321" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>472</v>
+        <v>115</v>
       </c>
       <c r="B322" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C322" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>473</v>
+        <v>116</v>
       </c>
       <c r="B323" t="s">
         <v>16</v>
       </c>
       <c r="C323" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>474</v>
+        <v>268</v>
       </c>
       <c r="B324" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C324" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>475</v>
+        <v>269</v>
       </c>
       <c r="B325" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C325" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>407</v>
+        <v>117</v>
       </c>
       <c r="B326" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C326" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="B327" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C327" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B328" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C328" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>115</v>
+        <v>465</v>
       </c>
       <c r="B329" t="s">
-        <v>49</v>
+        <v>301</v>
       </c>
       <c r="C329" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>116</v>
+        <v>466</v>
       </c>
       <c r="B330" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C330" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B331" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C331" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>477</v>
+        <v>120</v>
       </c>
       <c r="B332" t="s">
-        <v>239</v>
+        <v>16</v>
       </c>
       <c r="C332" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>271</v>
+        <v>121</v>
       </c>
       <c r="B333" t="s">
         <v>16</v>
       </c>
       <c r="C333" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B334" t="s">
         <v>16</v>
       </c>
       <c r="C334" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>119</v>
+        <v>467</v>
       </c>
       <c r="B335" t="s">
         <v>16</v>
       </c>
       <c r="C335" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>276</v>
+        <v>468</v>
       </c>
       <c r="B336" t="s">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c r="C336" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>120</v>
+        <v>469</v>
       </c>
       <c r="B337" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C337" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>121</v>
+        <v>470</v>
       </c>
       <c r="B338" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C338" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>277</v>
+        <v>123</v>
       </c>
       <c r="B339" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C339" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>278</v>
+        <v>471</v>
       </c>
       <c r="B340" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C340" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B341" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C341" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B342" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C342" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B343" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C343" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B344" t="s">
-        <v>310</v>
+        <v>7</v>
       </c>
       <c r="C344" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>480</v>
+        <v>126</v>
       </c>
       <c r="B345" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C345" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B346" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C346" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B347" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C347" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B348" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C348" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B349" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C349" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>481</v>
+        <v>131</v>
       </c>
       <c r="B350" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C350" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="B351" t="s">
-        <v>310</v>
+        <v>7</v>
       </c>
       <c r="C351" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>128</v>
+        <v>475</v>
       </c>
       <c r="B352" t="s">
-        <v>129</v>
+        <v>7</v>
       </c>
       <c r="C352" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>483</v>
+        <v>132</v>
       </c>
       <c r="B353" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C353" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>484</v>
+        <v>133</v>
       </c>
       <c r="B354" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C354" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B355" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="C355" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>485</v>
+        <v>135</v>
       </c>
       <c r="B356" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="C356" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B357" t="s">
         <v>7</v>
       </c>
       <c r="C357" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>486</v>
+        <v>137</v>
       </c>
       <c r="B358" t="s">
         <v>7</v>
       </c>
       <c r="C358" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B359" t="s">
         <v>7</v>
       </c>
       <c r="C359" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>487</v>
+        <v>139</v>
       </c>
       <c r="B360" t="s">
         <v>7</v>
       </c>
       <c r="C360" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B361" t="s">
         <v>7</v>
       </c>
       <c r="C361" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B362" t="s">
         <v>7</v>
       </c>
       <c r="C362" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B363" t="s">
         <v>7</v>
       </c>
       <c r="C363" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B364" t="s">
         <v>7</v>
       </c>
       <c r="C364" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B365" t="s">
         <v>7</v>
       </c>
       <c r="C365" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B366" t="s">
         <v>7</v>
       </c>
       <c r="C366" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>488</v>
+        <v>146</v>
       </c>
       <c r="B367" t="s">
         <v>7</v>
       </c>
       <c r="C367" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>489</v>
+        <v>147</v>
       </c>
       <c r="B368" t="s">
         <v>7</v>
       </c>
       <c r="C368" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B369" t="s">
         <v>7</v>
       </c>
       <c r="C369" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B370" t="s">
         <v>7</v>
       </c>
       <c r="C370" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B371" t="s">
         <v>7</v>
       </c>
       <c r="C371" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B372" t="s">
         <v>7</v>
       </c>
       <c r="C372" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>143</v>
+        <v>250</v>
       </c>
       <c r="B373" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C373" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B374" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C374" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B375" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C375" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B376" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C376" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B377" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C377" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B378" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C378" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B379" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C379" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>150</v>
+        <v>232</v>
       </c>
       <c r="B380" t="s">
         <v>7</v>
       </c>
       <c r="C380" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>151</v>
+        <v>476</v>
       </c>
       <c r="B381" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="C381" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B382" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C382" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B383" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C383" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B384" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C384" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B385" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C385" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B386" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C386" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B387" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C387" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B388" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C388" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>258</v>
+        <v>164</v>
       </c>
       <c r="B389" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C389" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B390" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C390" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B391" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C391" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B392" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C392" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B393" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C393" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B394" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C394" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B395" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C395" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>240</v>
+        <v>171</v>
       </c>
       <c r="B396" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C396" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>490</v>
+        <v>172</v>
       </c>
       <c r="B397" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C397" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B398" t="s">
         <v>16</v>
       </c>
       <c r="C398" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B399" t="s">
         <v>16</v>
       </c>
       <c r="C399" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>166</v>
+        <v>477</v>
       </c>
       <c r="B400" t="s">
         <v>16</v>
       </c>
       <c r="C400" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>167</v>
+        <v>478</v>
       </c>
       <c r="B401" t="s">
         <v>16</v>
       </c>
       <c r="C401" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>168</v>
+        <v>479</v>
       </c>
       <c r="B402" t="s">
         <v>16</v>
       </c>
       <c r="C402" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B403" t="s">
         <v>16</v>
       </c>
       <c r="C403" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B404" t="s">
         <v>16</v>
       </c>
       <c r="C404" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>171</v>
+        <v>480</v>
       </c>
       <c r="B405" t="s">
         <v>16</v>
       </c>
       <c r="C405" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>172</v>
+        <v>481</v>
       </c>
       <c r="B406" t="s">
         <v>16</v>
       </c>
       <c r="C406" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>173</v>
+        <v>482</v>
       </c>
       <c r="B407" t="s">
-        <v>16</v>
+        <v>483</v>
       </c>
       <c r="C407" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>174</v>
+        <v>484</v>
       </c>
       <c r="B408" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C408" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>175</v>
+        <v>485</v>
       </c>
       <c r="B409" t="s">
         <v>16</v>
       </c>
       <c r="C409" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>176</v>
+        <v>486</v>
       </c>
       <c r="B410" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C410" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>177</v>
+        <v>487</v>
       </c>
       <c r="B411" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C411" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B412" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C412" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>179</v>
+        <v>256</v>
       </c>
       <c r="B413" t="s">
         <v>16</v>
       </c>
       <c r="C413" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B414" t="s">
         <v>16</v>
       </c>
       <c r="C414" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B415" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C415" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>491</v>
+        <v>180</v>
       </c>
       <c r="B416" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C416" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>492</v>
+        <v>181</v>
       </c>
       <c r="B417" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C417" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>493</v>
+        <v>182</v>
       </c>
       <c r="B418" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C418" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>182</v>
+        <v>557</v>
       </c>
       <c r="B419" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C419" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>183</v>
+        <v>488</v>
       </c>
       <c r="B420" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C420" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>494</v>
+        <v>183</v>
       </c>
       <c r="B421" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C421" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B422" t="s">
-        <v>16</v>
+        <v>556</v>
       </c>
       <c r="C422" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B423" t="s">
-        <v>497</v>
+        <v>4</v>
       </c>
       <c r="C423" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="B424" t="s">
-        <v>4</v>
+        <v>556</v>
       </c>
       <c r="C424" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="B425" t="s">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c r="C425" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>500</v>
+        <v>184</v>
       </c>
       <c r="B426" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C426" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>501</v>
+        <v>185</v>
       </c>
       <c r="B427" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C427" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B428" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C428" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>264</v>
+        <v>187</v>
       </c>
       <c r="B429" t="s">
         <v>16</v>
       </c>
       <c r="C429" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B430" t="s">
         <v>16</v>
       </c>
       <c r="C430" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B431" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C431" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B432" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C432" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B433" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C433" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B434" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="C434" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>502</v>
+        <v>192</v>
       </c>
       <c r="B435" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C435" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B436" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C436" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="B437" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="C437" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>504</v>
+        <v>194</v>
       </c>
       <c r="B438" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="C438" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>505</v>
+        <v>195</v>
       </c>
       <c r="B439" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C439" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="B440" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="C440" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="B441" t="s">
-        <v>310</v>
+        <v>7</v>
       </c>
       <c r="C441" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>191</v>
+        <v>496</v>
       </c>
       <c r="B442" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C442" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>192</v>
+        <v>497</v>
       </c>
       <c r="B443" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C443" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
       <c r="B444" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C444" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="B445" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C445" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B446" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C446" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B447" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C447" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B448" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C448" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B449" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C449" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B450" t="s">
         <v>13</v>
       </c>
       <c r="C450" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B451" t="s">
         <v>13</v>
       </c>
       <c r="C451" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>200</v>
+        <v>498</v>
       </c>
       <c r="B452" t="s">
         <v>13</v>
       </c>
       <c r="C452" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>508</v>
+        <v>202</v>
       </c>
       <c r="B453" t="s">
         <v>13</v>
       </c>
       <c r="C453" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>201</v>
+        <v>499</v>
       </c>
       <c r="B454" t="s">
         <v>13</v>
       </c>
       <c r="C454" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B455" t="s">
         <v>13</v>
       </c>
       <c r="C455" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="B456" t="s">
         <v>13</v>
       </c>
       <c r="C456" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="B457" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C457" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="B458" t="s">
         <v>7</v>
       </c>
       <c r="C458" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>512</v>
+        <v>204</v>
       </c>
       <c r="B459" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C459" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>242</v>
+        <v>205</v>
       </c>
       <c r="B460" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C460" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>241</v>
+        <v>206</v>
       </c>
       <c r="B461" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C461" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B462" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C462" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B463" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C463" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B464" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C464" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B465" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C465" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>207</v>
+        <v>276</v>
       </c>
       <c r="B466" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C466" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>208</v>
+        <v>503</v>
       </c>
       <c r="B467" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C467" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>209</v>
+        <v>504</v>
       </c>
       <c r="B468" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C468" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="B469" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C469" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B470" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C470" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>514</v>
+        <v>212</v>
       </c>
       <c r="B471" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C471" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B472" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C472" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>515</v>
+        <v>214</v>
       </c>
       <c r="B473" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C473" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="B474" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C474" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>517</v>
+        <v>215</v>
       </c>
       <c r="B475" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C475" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B476" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C476" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B477" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C477" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B478" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C478" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B479" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C479" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B480" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C480" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B481" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C481" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>218</v>
+        <v>507</v>
       </c>
       <c r="B482" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C482" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>285</v>
+        <v>508</v>
       </c>
       <c r="B483" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C483" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="B484" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C484" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="B485" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C485" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="B486" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C486" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>219</v>
+        <v>512</v>
       </c>
       <c r="B487" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C487" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>220</v>
+        <v>513</v>
       </c>
       <c r="B488" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C488" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B489" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C489" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="B490" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C490" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>521</v>
+        <v>223</v>
       </c>
       <c r="B491" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="C491" t="s">
-        <v>112</v>
+        <v>224</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B492" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="C492" t="s">
-        <v>112</v>
+        <v>224</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
+        <v>226</v>
+      </c>
+      <c r="B493" t="s">
+        <v>4</v>
+      </c>
+      <c r="C493" t="s">
         <v>224</v>
-      </c>
-      <c r="B493" t="s">
-        <v>49</v>
-      </c>
-      <c r="C493" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B494" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="C494" t="s">
-        <v>112</v>
+        <v>224</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B495" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C495" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B496" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C496" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B497" t="s">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c r="C497" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>229</v>
+        <v>272</v>
       </c>
       <c r="B498" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="C498" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>522</v>
+        <v>273</v>
       </c>
       <c r="B499" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="C499" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>523</v>
+        <v>98</v>
       </c>
       <c r="B500" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="C500" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>524</v>
+        <v>251</v>
       </c>
       <c r="B501" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C501" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>525</v>
+        <v>252</v>
       </c>
       <c r="B502" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C502" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="B503" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C503" t="s">
-        <v>112</v>
+        <v>515</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="B504" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C504" t="s">
-        <v>112</v>
+        <v>515</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="B505" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C505" t="s">
-        <v>112</v>
+        <v>515</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>230</v>
+        <v>518</v>
       </c>
       <c r="B506" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C506" t="s">
-        <v>112</v>
+        <v>515</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>250</v>
+        <v>519</v>
       </c>
       <c r="B507" t="s">
         <v>13</v>
       </c>
       <c r="C507" t="s">
-        <v>112</v>
+        <v>515</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>231</v>
+        <v>520</v>
       </c>
       <c r="B508" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C508" t="s">
-        <v>232</v>
+        <v>515</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>233</v>
+        <v>521</v>
       </c>
       <c r="B509" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C509" t="s">
-        <v>232</v>
+        <v>515</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>234</v>
+        <v>522</v>
       </c>
       <c r="B510" t="s">
-        <v>4</v>
+        <v>483</v>
       </c>
       <c r="C510" t="s">
-        <v>232</v>
+        <v>515</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>235</v>
+        <v>523</v>
       </c>
       <c r="B511" t="s">
-        <v>11</v>
+        <v>483</v>
       </c>
       <c r="C511" t="s">
-        <v>232</v>
+        <v>515</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>236</v>
+        <v>524</v>
       </c>
       <c r="B512" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C512" t="s">
-        <v>104</v>
+        <v>515</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>237</v>
+        <v>525</v>
       </c>
       <c r="B513" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C513" t="s">
-        <v>104</v>
+        <v>515</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>238</v>
+        <v>526</v>
       </c>
       <c r="B514" t="s">
-        <v>239</v>
+        <v>483</v>
       </c>
       <c r="C514" t="s">
-        <v>104</v>
+        <v>515</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>281</v>
+        <v>527</v>
       </c>
       <c r="B515" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C515" t="s">
-        <v>104</v>
+        <v>515</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>282</v>
+        <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C516" t="s">
-        <v>104</v>
+        <v>515</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>103</v>
+        <v>529</v>
       </c>
       <c r="B517" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C517" t="s">
-        <v>104</v>
+        <v>515</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>259</v>
+        <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C518" t="s">
-        <v>104</v>
+        <v>515</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>260</v>
+        <v>531</v>
       </c>
       <c r="B519" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C519" t="s">
-        <v>104</v>
+        <v>515</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B520" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="C520" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B521" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="C521" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B522" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="C522" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B523" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C523" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B524" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C524" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B525" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C525" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B526" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C526" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B527" t="s">
-        <v>497</v>
+        <v>16</v>
       </c>
       <c r="C527" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B528" t="s">
-        <v>497</v>
+        <v>45</v>
       </c>
       <c r="C528" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B529" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C529" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B530" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C530" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B531" t="s">
-        <v>497</v>
+        <v>231</v>
       </c>
       <c r="C531" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B532" t="s">
-        <v>59</v>
+        <v>556</v>
       </c>
       <c r="C532" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B533" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="C533" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B534" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C534" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B535" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C535" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B536" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C536" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B537" t="s">
-        <v>7</v>
+        <v>301</v>
       </c>
       <c r="C537" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B538" t="s">
-        <v>7</v>
+        <v>550</v>
       </c>
       <c r="C538" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B539" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C539" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B540" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C540" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B541" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C541" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B542" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="C542" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A543" t="s">
-        <v>552</v>
-      </c>
-      <c r="B543" t="s">
-        <v>59</v>
-      </c>
-      <c r="C543" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A544" t="s">
-        <v>553</v>
-      </c>
-      <c r="B544" t="s">
-        <v>16</v>
-      </c>
-      <c r="C544" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A545" t="s">
-        <v>554</v>
-      </c>
-      <c r="B545" t="s">
-        <v>49</v>
-      </c>
-      <c r="C545" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A546" t="s">
-        <v>555</v>
-      </c>
-      <c r="B546" t="s">
-        <v>49</v>
-      </c>
-      <c r="C546" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A547" t="s">
-        <v>556</v>
-      </c>
-      <c r="B547" t="s">
-        <v>16</v>
-      </c>
-      <c r="C547" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A548" t="s">
-        <v>557</v>
-      </c>
-      <c r="B548" t="s">
-        <v>239</v>
-      </c>
-      <c r="C548" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A549" t="s">
-        <v>558</v>
-      </c>
-      <c r="B549" t="s">
-        <v>129</v>
-      </c>
-      <c r="C549" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A550" t="s">
-        <v>559</v>
-      </c>
-      <c r="B550" t="s">
-        <v>111</v>
-      </c>
-      <c r="C550" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A551" t="s">
-        <v>560</v>
-      </c>
-      <c r="B551" t="s">
-        <v>4</v>
-      </c>
-      <c r="C551" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A552" t="s">
-        <v>561</v>
-      </c>
-      <c r="B552" t="s">
-        <v>13</v>
-      </c>
-      <c r="C552" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A553" t="s">
-        <v>562</v>
-      </c>
-      <c r="B553" t="s">
-        <v>11</v>
-      </c>
-      <c r="C553" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A554" t="s">
-        <v>563</v>
-      </c>
-      <c r="B554" t="s">
-        <v>310</v>
-      </c>
-      <c r="C554" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A555" t="s">
-        <v>564</v>
-      </c>
-      <c r="B555" t="s">
-        <v>565</v>
-      </c>
-      <c r="C555" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A556" t="s">
-        <v>566</v>
-      </c>
-      <c r="B556" t="s">
-        <v>13</v>
-      </c>
-      <c r="C556" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A557" t="s">
-        <v>567</v>
-      </c>
-      <c r="B557" t="s">
-        <v>13</v>
-      </c>
-      <c r="C557" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A558" t="s">
-        <v>568</v>
-      </c>
-      <c r="B558" t="s">
-        <v>13</v>
-      </c>
-      <c r="C558" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A559" t="s">
-        <v>569</v>
-      </c>
-      <c r="B559" t="s">
-        <v>13</v>
-      </c>
-      <c r="C559" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>

--- a/Vehicle Catalogue.xlsx
+++ b/Vehicle Catalogue.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samhi\Documents\My Games\Sprocket\Ostfront Tank Collection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536E3F5A-963C-41F0-B917-7258261C31FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4217CB8-45D2-45A6-A14E-2B9145A2D5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8150" yWindow="2920" windowWidth="28800" windowHeight="15360" xr2:uid="{3FAC36FE-B102-4B04-8548-70F58966D145}"/>
+    <workbookView xWindow="11090" yWindow="6100" windowWidth="28800" windowHeight="15360" xr2:uid="{3FAC36FE-B102-4B04-8548-70F58966D145}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$273</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$271</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="555">
   <si>
     <t>Tank</t>
   </si>
@@ -1145,9 +1145,6 @@
     <t>O-Ho</t>
   </si>
   <si>
-    <t>Pawlack</t>
-  </si>
-  <si>
     <t>Porsche Tiger</t>
   </si>
   <si>
@@ -1247,9 +1244,6 @@
     <t>Harry Hopkins Mk 1 CS Alecto</t>
   </si>
   <si>
-    <t>Kolohousenka</t>
-  </si>
-  <si>
     <t>Landsverk L-60</t>
   </si>
   <si>
@@ -1437,9 +1431,6 @@
   </si>
   <si>
     <t>Grosstraktor</t>
-  </si>
-  <si>
-    <t>Ikv 72</t>
   </si>
   <si>
     <t>IT-3</t>
@@ -2139,7 +2130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C50DCCC-8446-4FAC-BA76-D53F2D86B716}">
-  <dimension ref="A1:C542"/>
+  <dimension ref="A1:C539"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.81640625" customWidth="1"/>
@@ -3505,7 +3496,7 @@
         <v>367</v>
       </c>
       <c r="B124" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C124" t="s">
         <v>17</v>
@@ -3513,10 +3504,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>368</v>
+        <v>35</v>
       </c>
       <c r="B125" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C125" t="s">
         <v>17</v>
@@ -3524,10 +3515,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>35</v>
+        <v>259</v>
       </c>
       <c r="B126" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C126" t="s">
         <v>17</v>
@@ -3535,7 +3526,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B127" t="s">
         <v>16</v>
@@ -3546,29 +3537,29 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="B128" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C128" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
-        <v>241</v>
+      <c r="A129" s="3" t="s">
+        <v>264</v>
       </c>
       <c r="B129" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C129" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A130" s="3" t="s">
-        <v>264</v>
+      <c r="A130" t="s">
+        <v>265</v>
       </c>
       <c r="B130" t="s">
         <v>16</v>
@@ -3579,7 +3570,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B131" t="s">
         <v>16</v>
@@ -3590,10 +3581,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>270</v>
+        <v>36</v>
       </c>
       <c r="B132" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C132" t="s">
         <v>17</v>
@@ -3601,7 +3592,7 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>36</v>
+        <v>368</v>
       </c>
       <c r="B133" t="s">
         <v>13</v>
@@ -3623,10 +3614,10 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>370</v>
+        <v>266</v>
       </c>
       <c r="B135" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C135" t="s">
         <v>17</v>
@@ -3634,7 +3625,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>266</v>
+        <v>37</v>
       </c>
       <c r="B136" t="s">
         <v>16</v>
@@ -3656,7 +3647,7 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B138" t="s">
         <v>16</v>
@@ -3667,10 +3658,10 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>38</v>
+        <v>370</v>
       </c>
       <c r="B139" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
@@ -3700,7 +3691,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>373</v>
+        <v>239</v>
       </c>
       <c r="B142" t="s">
         <v>13</v>
@@ -3711,7 +3702,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B143" t="s">
         <v>13</v>
@@ -3722,7 +3713,7 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>240</v>
+        <v>39</v>
       </c>
       <c r="B144" t="s">
         <v>13</v>
@@ -3744,7 +3735,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B146" t="s">
         <v>13</v>
@@ -3755,7 +3746,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>40</v>
+        <v>373</v>
       </c>
       <c r="B147" t="s">
         <v>13</v>
@@ -3780,7 +3771,7 @@
         <v>375</v>
       </c>
       <c r="B149" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C149" t="s">
         <v>17</v>
@@ -3791,7 +3782,7 @@
         <v>376</v>
       </c>
       <c r="B150" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C150" t="s">
         <v>17</v>
@@ -3802,7 +3793,7 @@
         <v>377</v>
       </c>
       <c r="B151" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -3832,10 +3823,10 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>380</v>
+        <v>41</v>
       </c>
       <c r="B154" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C154" t="s">
         <v>17</v>
@@ -3843,7 +3834,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B155" t="s">
         <v>13</v>
@@ -3854,10 +3845,10 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>42</v>
+        <v>247</v>
       </c>
       <c r="B156" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C156" t="s">
         <v>17</v>
@@ -3865,10 +3856,10 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="B157" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C157" t="s">
         <v>17</v>
@@ -3876,7 +3867,7 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B158" t="s">
         <v>16</v>
@@ -3887,7 +3878,7 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>44</v>
+        <v>236</v>
       </c>
       <c r="B159" t="s">
         <v>16</v>
@@ -3898,10 +3889,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>236</v>
+        <v>380</v>
       </c>
       <c r="B160" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
@@ -3909,7 +3900,7 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="B161" t="s">
         <v>11</v>
@@ -3920,7 +3911,7 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>275</v>
+        <v>381</v>
       </c>
       <c r="B162" t="s">
         <v>11</v>
@@ -3931,7 +3922,7 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>382</v>
+        <v>46</v>
       </c>
       <c r="B163" t="s">
         <v>11</v>
@@ -3942,7 +3933,7 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B164" t="s">
         <v>11</v>
@@ -3953,10 +3944,10 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B165" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C165" t="s">
         <v>17</v>
@@ -3964,10 +3955,10 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>48</v>
+        <v>382</v>
       </c>
       <c r="B166" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C166" t="s">
         <v>17</v>
@@ -4008,7 +3999,7 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>386</v>
+        <v>552</v>
       </c>
       <c r="B170" t="s">
         <v>16</v>
@@ -4019,7 +4010,7 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>555</v>
+        <v>386</v>
       </c>
       <c r="B171" t="s">
         <v>16</v>
@@ -4030,7 +4021,7 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>387</v>
+        <v>257</v>
       </c>
       <c r="B172" t="s">
         <v>16</v>
@@ -4041,7 +4032,7 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>257</v>
+        <v>49</v>
       </c>
       <c r="B173" t="s">
         <v>16</v>
@@ -4052,7 +4043,7 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>49</v>
+        <v>387</v>
       </c>
       <c r="B174" t="s">
         <v>16</v>
@@ -4066,7 +4057,7 @@
         <v>388</v>
       </c>
       <c r="B175" t="s">
-        <v>16</v>
+        <v>553</v>
       </c>
       <c r="C175" t="s">
         <v>17</v>
@@ -4077,7 +4068,7 @@
         <v>389</v>
       </c>
       <c r="B176" t="s">
-        <v>556</v>
+        <v>16</v>
       </c>
       <c r="C176" t="s">
         <v>17</v>
@@ -4085,21 +4076,21 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>390</v>
+        <v>277</v>
       </c>
       <c r="B177" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="C177" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>277</v>
+        <v>390</v>
       </c>
       <c r="B178" t="s">
-        <v>106</v>
+        <v>231</v>
       </c>
       <c r="C178" t="s">
         <v>51</v>
@@ -4110,7 +4101,7 @@
         <v>391</v>
       </c>
       <c r="B179" t="s">
-        <v>231</v>
+        <v>13</v>
       </c>
       <c r="C179" t="s">
         <v>51</v>
@@ -4121,7 +4112,7 @@
         <v>392</v>
       </c>
       <c r="B180" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C180" t="s">
         <v>51</v>
@@ -4143,7 +4134,7 @@
         <v>394</v>
       </c>
       <c r="B182" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C182" t="s">
         <v>51</v>
@@ -4162,10 +4153,10 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>396</v>
+        <v>50</v>
       </c>
       <c r="B184" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C184" t="s">
         <v>51</v>
@@ -4173,10 +4164,10 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>50</v>
+        <v>262</v>
       </c>
       <c r="B185" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C185" t="s">
         <v>51</v>
@@ -4184,10 +4175,10 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>262</v>
+        <v>52</v>
       </c>
       <c r="B186" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C186" t="s">
         <v>51</v>
@@ -4195,7 +4186,7 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>52</v>
+        <v>397</v>
       </c>
       <c r="B187" t="s">
         <v>4</v>
@@ -4206,10 +4197,10 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>398</v>
+        <v>53</v>
       </c>
       <c r="B188" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C188" t="s">
         <v>51</v>
@@ -4217,10 +4208,10 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>53</v>
+        <v>398</v>
       </c>
       <c r="B189" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C189" t="s">
         <v>51</v>
@@ -4228,7 +4219,7 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>399</v>
+        <v>55</v>
       </c>
       <c r="B190" t="s">
         <v>16</v>
@@ -4239,7 +4230,7 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B191" t="s">
         <v>16</v>
@@ -4250,10 +4241,10 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>56</v>
+        <v>399</v>
       </c>
       <c r="B192" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C192" t="s">
         <v>51</v>
@@ -4264,7 +4255,7 @@
         <v>400</v>
       </c>
       <c r="B193" t="s">
-        <v>45</v>
+        <v>301</v>
       </c>
       <c r="C193" t="s">
         <v>51</v>
@@ -4275,7 +4266,7 @@
         <v>401</v>
       </c>
       <c r="B194" t="s">
-        <v>556</v>
+        <v>16</v>
       </c>
       <c r="C194" t="s">
         <v>51</v>
@@ -4283,10 +4274,10 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>402</v>
+        <v>57</v>
       </c>
       <c r="B195" t="s">
-        <v>301</v>
+        <v>16</v>
       </c>
       <c r="C195" t="s">
         <v>51</v>
@@ -4294,10 +4285,10 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B196" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C196" t="s">
         <v>51</v>
@@ -4305,7 +4296,7 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B197" t="s">
         <v>16</v>
@@ -4316,10 +4307,10 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>404</v>
+        <v>226</v>
       </c>
       <c r="B198" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="C198" t="s">
         <v>51</v>
@@ -4327,10 +4318,10 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>58</v>
+        <v>403</v>
       </c>
       <c r="B199" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C199" t="s">
         <v>51</v>
@@ -4338,10 +4329,10 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>226</v>
+        <v>404</v>
       </c>
       <c r="B200" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C200" t="s">
         <v>51</v>
@@ -4349,10 +4340,10 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>405</v>
+        <v>59</v>
       </c>
       <c r="B201" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C201" t="s">
         <v>51</v>
@@ -4360,10 +4351,10 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>406</v>
+        <v>60</v>
       </c>
       <c r="B202" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C202" t="s">
         <v>51</v>
@@ -4371,7 +4362,7 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>59</v>
+        <v>248</v>
       </c>
       <c r="B203" t="s">
         <v>7</v>
@@ -4382,7 +4373,7 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B204" t="s">
         <v>7</v>
@@ -4393,7 +4384,7 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>248</v>
+        <v>405</v>
       </c>
       <c r="B205" t="s">
         <v>7</v>
@@ -4404,7 +4395,7 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B206" t="s">
         <v>7</v>
@@ -4415,7 +4406,7 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B207" t="s">
         <v>7</v>
@@ -4426,7 +4417,7 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>62</v>
+        <v>407</v>
       </c>
       <c r="B208" t="s">
         <v>7</v>
@@ -4437,7 +4428,7 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>408</v>
+        <v>63</v>
       </c>
       <c r="B209" t="s">
         <v>7</v>
@@ -4448,7 +4439,7 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B210" t="s">
         <v>7</v>
@@ -4459,10 +4450,10 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B211" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C211" t="s">
         <v>51</v>
@@ -4470,10 +4461,10 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>410</v>
+        <v>65</v>
       </c>
       <c r="B212" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C212" t="s">
         <v>51</v>
@@ -4481,7 +4472,7 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B213" t="s">
         <v>16</v>
@@ -4492,7 +4483,7 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B214" t="s">
         <v>16</v>
@@ -4503,10 +4494,10 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B215" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C215" t="s">
         <v>51</v>
@@ -4514,7 +4505,7 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>67</v>
+        <v>409</v>
       </c>
       <c r="B216" t="s">
         <v>16</v>
@@ -4525,10 +4516,10 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>68</v>
+        <v>410</v>
       </c>
       <c r="B217" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C217" t="s">
         <v>51</v>
@@ -4539,7 +4530,7 @@
         <v>411</v>
       </c>
       <c r="B218" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C218" t="s">
         <v>51</v>
@@ -4547,21 +4538,21 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>412</v>
+        <v>232</v>
       </c>
       <c r="B219" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C219" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A220" t="s">
-        <v>413</v>
+      <c r="A220" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="B220" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C220" t="s">
         <v>51</v>
@@ -4569,18 +4560,18 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>232</v>
+        <v>70</v>
       </c>
       <c r="B221" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C221" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A222" s="4" t="s">
-        <v>69</v>
+      <c r="A222" t="s">
+        <v>71</v>
       </c>
       <c r="B222" t="s">
         <v>16</v>
@@ -4591,7 +4582,7 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B223" t="s">
         <v>16</v>
@@ -4602,7 +4593,7 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B224" t="s">
         <v>16</v>
@@ -4613,7 +4604,7 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B225" t="s">
         <v>16</v>
@@ -4624,7 +4615,7 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B226" t="s">
         <v>16</v>
@@ -4635,7 +4626,7 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>74</v>
+        <v>263</v>
       </c>
       <c r="B227" t="s">
         <v>16</v>
@@ -4646,10 +4637,10 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>75</v>
+        <v>412</v>
       </c>
       <c r="B228" t="s">
-        <v>16</v>
+        <v>553</v>
       </c>
       <c r="C228" t="s">
         <v>51</v>
@@ -4657,10 +4648,10 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>263</v>
+        <v>413</v>
       </c>
       <c r="B229" t="s">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c r="C229" t="s">
         <v>51</v>
@@ -4671,7 +4662,7 @@
         <v>414</v>
       </c>
       <c r="B230" t="s">
-        <v>556</v>
+        <v>16</v>
       </c>
       <c r="C230" t="s">
         <v>51</v>
@@ -4679,10 +4670,10 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>415</v>
+        <v>76</v>
       </c>
       <c r="B231" t="s">
-        <v>301</v>
+        <v>4</v>
       </c>
       <c r="C231" t="s">
         <v>51</v>
@@ -4690,7 +4681,7 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B232" t="s">
         <v>16</v>
@@ -4701,10 +4692,10 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>76</v>
+        <v>261</v>
       </c>
       <c r="B233" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C233" t="s">
         <v>51</v>
@@ -4712,10 +4703,10 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>417</v>
+        <v>77</v>
       </c>
       <c r="B234" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C234" t="s">
         <v>51</v>
@@ -4723,10 +4714,10 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>261</v>
+        <v>78</v>
       </c>
       <c r="B235" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C235" t="s">
         <v>51</v>
@@ -4734,7 +4725,7 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>77</v>
+        <v>416</v>
       </c>
       <c r="B236" t="s">
         <v>4</v>
@@ -4745,10 +4736,10 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>78</v>
+        <v>417</v>
       </c>
       <c r="B237" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C237" t="s">
         <v>51</v>
@@ -4770,7 +4761,7 @@
         <v>419</v>
       </c>
       <c r="B239" t="s">
-        <v>4</v>
+        <v>301</v>
       </c>
       <c r="C239" t="s">
         <v>51</v>
@@ -4778,10 +4769,10 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>420</v>
+        <v>79</v>
       </c>
       <c r="B240" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C240" t="s">
         <v>51</v>
@@ -4789,10 +4780,10 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>421</v>
+        <v>80</v>
       </c>
       <c r="B241" t="s">
-        <v>301</v>
+        <v>16</v>
       </c>
       <c r="C241" t="s">
         <v>51</v>
@@ -4800,10 +4791,10 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B242" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C242" t="s">
         <v>51</v>
@@ -4811,10 +4802,10 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="B243" t="s">
-        <v>16</v>
+        <v>553</v>
       </c>
       <c r="C243" t="s">
         <v>51</v>
@@ -4822,10 +4813,10 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>81</v>
+        <v>421</v>
       </c>
       <c r="B244" t="s">
-        <v>54</v>
+        <v>553</v>
       </c>
       <c r="C244" t="s">
         <v>51</v>
@@ -4833,10 +4824,10 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>422</v>
+        <v>82</v>
       </c>
       <c r="B245" t="s">
-        <v>556</v>
+        <v>16</v>
       </c>
       <c r="C245" t="s">
         <v>51</v>
@@ -4844,10 +4835,10 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B246" t="s">
-        <v>556</v>
+        <v>16</v>
       </c>
       <c r="C246" t="s">
         <v>51</v>
@@ -4855,10 +4846,10 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="B247" t="s">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c r="C247" t="s">
         <v>51</v>
@@ -4869,7 +4860,7 @@
         <v>424</v>
       </c>
       <c r="B248" t="s">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c r="C248" t="s">
         <v>51</v>
@@ -4899,10 +4890,10 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>427</v>
+        <v>83</v>
       </c>
       <c r="B251" t="s">
-        <v>301</v>
+        <v>16</v>
       </c>
       <c r="C251" t="s">
         <v>51</v>
@@ -4910,10 +4901,10 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B252" t="s">
-        <v>301</v>
+        <v>13</v>
       </c>
       <c r="C252" t="s">
         <v>51</v>
@@ -4921,10 +4912,10 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B253" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C253" t="s">
         <v>51</v>
@@ -4932,10 +4923,10 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>429</v>
+        <v>84</v>
       </c>
       <c r="B254" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C254" t="s">
         <v>51</v>
@@ -4943,7 +4934,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>84</v>
+        <v>428</v>
       </c>
       <c r="B255" t="s">
         <v>7</v>
@@ -4954,10 +4945,10 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>84</v>
+        <v>429</v>
       </c>
       <c r="B256" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C256" t="s">
         <v>51</v>
@@ -4968,7 +4959,7 @@
         <v>430</v>
       </c>
       <c r="B257" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C257" t="s">
         <v>51</v>
@@ -4976,7 +4967,7 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>431</v>
+        <v>85</v>
       </c>
       <c r="B258" t="s">
         <v>13</v>
@@ -4987,10 +4978,10 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>432</v>
+        <v>85</v>
       </c>
       <c r="B259" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="C259" t="s">
         <v>51</v>
@@ -4998,10 +4989,10 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>85</v>
+        <v>431</v>
       </c>
       <c r="B260" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C260" t="s">
         <v>51</v>
@@ -5009,10 +5000,10 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>85</v>
+        <v>432</v>
       </c>
       <c r="B261" t="s">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="C261" t="s">
         <v>51</v>
@@ -5042,10 +5033,10 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>435</v>
+        <v>87</v>
       </c>
       <c r="B264" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C264" t="s">
         <v>51</v>
@@ -5053,10 +5044,10 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>436</v>
+        <v>88</v>
       </c>
       <c r="B265" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C265" t="s">
         <v>51</v>
@@ -5064,10 +5055,10 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>87</v>
+        <v>435</v>
       </c>
       <c r="B266" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C266" t="s">
         <v>51</v>
@@ -5075,7 +5066,7 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B267" t="s">
         <v>13</v>
@@ -5086,10 +5077,10 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B268" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C268" t="s">
         <v>51</v>
@@ -5097,7 +5088,7 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>89</v>
+        <v>437</v>
       </c>
       <c r="B269" t="s">
         <v>13</v>
@@ -5108,7 +5099,7 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>438</v>
+        <v>90</v>
       </c>
       <c r="B270" t="s">
         <v>13</v>
@@ -5119,7 +5110,7 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B271" t="s">
         <v>13</v>
@@ -5130,10 +5121,10 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>90</v>
+        <v>439</v>
       </c>
       <c r="B272" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C272" t="s">
         <v>51</v>
@@ -5141,7 +5132,7 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>440</v>
+        <v>91</v>
       </c>
       <c r="B273" t="s">
         <v>13</v>
@@ -5152,10 +5143,10 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>441</v>
+        <v>92</v>
       </c>
       <c r="B274" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C274" t="s">
         <v>51</v>
@@ -5163,10 +5154,10 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>91</v>
+        <v>440</v>
       </c>
       <c r="B275" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C275" t="s">
         <v>51</v>
@@ -5174,10 +5165,10 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>92</v>
+        <v>441</v>
       </c>
       <c r="B276" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C276" t="s">
         <v>51</v>
@@ -5185,10 +5176,10 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>442</v>
+        <v>93</v>
       </c>
       <c r="B277" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C277" t="s">
         <v>51</v>
@@ -5196,10 +5187,10 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>443</v>
+        <v>94</v>
       </c>
       <c r="B278" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C278" t="s">
         <v>51</v>
@@ -5207,10 +5198,10 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>93</v>
+        <v>249</v>
       </c>
       <c r="B279" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C279" t="s">
         <v>51</v>
@@ -5218,7 +5209,7 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B280" t="s">
         <v>13</v>
@@ -5229,7 +5220,7 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>249</v>
+        <v>442</v>
       </c>
       <c r="B281" t="s">
         <v>7</v>
@@ -5240,10 +5231,10 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>95</v>
+        <v>443</v>
       </c>
       <c r="B282" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C282" t="s">
         <v>51</v>
@@ -5251,10 +5242,10 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>444</v>
+        <v>96</v>
       </c>
       <c r="B283" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C283" t="s">
         <v>51</v>
@@ -5262,7 +5253,7 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>445</v>
+        <v>274</v>
       </c>
       <c r="B284" t="s">
         <v>11</v>
@@ -5273,7 +5264,7 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>96</v>
+        <v>444</v>
       </c>
       <c r="B285" t="s">
         <v>11</v>
@@ -5284,7 +5275,7 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>274</v>
+        <v>97</v>
       </c>
       <c r="B286" t="s">
         <v>11</v>
@@ -5295,7 +5286,7 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B287" t="s">
         <v>11</v>
@@ -5306,7 +5297,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B288" t="s">
         <v>11</v>
@@ -5317,10 +5308,10 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>447</v>
+        <v>101</v>
       </c>
       <c r="B289" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C289" t="s">
         <v>51</v>
@@ -5328,10 +5319,10 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B290" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C290" t="s">
         <v>51</v>
@@ -5339,10 +5330,10 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B291" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C291" t="s">
         <v>51</v>
@@ -5350,10 +5341,10 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>102</v>
+        <v>446</v>
       </c>
       <c r="B292" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C292" t="s">
         <v>51</v>
@@ -5361,7 +5352,7 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>103</v>
+        <v>447</v>
       </c>
       <c r="B293" t="s">
         <v>16</v>
@@ -5372,10 +5363,10 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>448</v>
+        <v>104</v>
       </c>
       <c r="B294" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C294" t="s">
         <v>51</v>
@@ -5383,32 +5374,32 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>449</v>
+        <v>254</v>
       </c>
       <c r="B295" t="s">
-        <v>16</v>
+        <v>231</v>
       </c>
       <c r="C295" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>104</v>
+        <v>448</v>
       </c>
       <c r="B296" t="s">
-        <v>13</v>
+        <v>231</v>
       </c>
       <c r="C296" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="B297" t="s">
-        <v>231</v>
+        <v>106</v>
       </c>
       <c r="C297" t="s">
         <v>107</v>
@@ -5416,10 +5407,10 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>450</v>
+        <v>108</v>
       </c>
       <c r="B298" t="s">
-        <v>231</v>
+        <v>106</v>
       </c>
       <c r="C298" t="s">
         <v>107</v>
@@ -5427,10 +5418,10 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>105</v>
+        <v>449</v>
       </c>
       <c r="B299" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="C299" t="s">
         <v>107</v>
@@ -5438,10 +5429,10 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>108</v>
+        <v>450</v>
       </c>
       <c r="B300" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="C300" t="s">
         <v>107</v>
@@ -5485,7 +5476,7 @@
         <v>454</v>
       </c>
       <c r="B304" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C304" t="s">
         <v>107</v>
@@ -5518,7 +5509,7 @@
         <v>457</v>
       </c>
       <c r="B307" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C307" t="s">
         <v>107</v>
@@ -5529,7 +5520,7 @@
         <v>458</v>
       </c>
       <c r="B308" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C308" t="s">
         <v>107</v>
@@ -5540,7 +5531,7 @@
         <v>459</v>
       </c>
       <c r="B309" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C309" t="s">
         <v>107</v>
@@ -5548,10 +5539,10 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>460</v>
+        <v>396</v>
       </c>
       <c r="B310" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C310" t="s">
         <v>107</v>
@@ -5559,10 +5550,10 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B311" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C311" t="s">
         <v>107</v>
@@ -5570,10 +5561,10 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>397</v>
+        <v>109</v>
       </c>
       <c r="B312" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C312" t="s">
         <v>107</v>
@@ -5581,10 +5572,10 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>462</v>
+        <v>110</v>
       </c>
       <c r="B313" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C313" t="s">
         <v>107</v>
@@ -5592,7 +5583,7 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B314" t="s">
         <v>45</v>
@@ -5603,7 +5594,7 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B315" t="s">
         <v>45</v>
@@ -5614,10 +5605,10 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>111</v>
+        <v>461</v>
       </c>
       <c r="B316" t="s">
-        <v>45</v>
+        <v>231</v>
       </c>
       <c r="C316" t="s">
         <v>107</v>
@@ -5625,10 +5616,10 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B317" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C317" t="s">
         <v>107</v>
@@ -5636,10 +5627,10 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>463</v>
+        <v>114</v>
       </c>
       <c r="B318" t="s">
-        <v>231</v>
+        <v>16</v>
       </c>
       <c r="C318" t="s">
         <v>107</v>
@@ -5647,7 +5638,7 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>113</v>
+        <v>267</v>
       </c>
       <c r="B319" t="s">
         <v>16</v>
@@ -5658,7 +5649,7 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B320" t="s">
         <v>16</v>
@@ -5669,7 +5660,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>267</v>
+        <v>116</v>
       </c>
       <c r="B321" t="s">
         <v>16</v>
@@ -5680,7 +5671,7 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>115</v>
+        <v>268</v>
       </c>
       <c r="B322" t="s">
         <v>16</v>
@@ -5691,7 +5682,7 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>116</v>
+        <v>269</v>
       </c>
       <c r="B323" t="s">
         <v>16</v>
@@ -5702,7 +5693,7 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>268</v>
+        <v>117</v>
       </c>
       <c r="B324" t="s">
         <v>16</v>
@@ -5713,7 +5704,7 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>269</v>
+        <v>462</v>
       </c>
       <c r="B325" t="s">
         <v>16</v>
@@ -5724,7 +5715,7 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B326" t="s">
         <v>16</v>
@@ -5735,10 +5726,10 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B327" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C327" t="s">
         <v>107</v>
@@ -5746,7 +5737,7 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B328" t="s">
         <v>16</v>
@@ -5757,10 +5748,10 @@
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>465</v>
+        <v>120</v>
       </c>
       <c r="B329" t="s">
-        <v>301</v>
+        <v>16</v>
       </c>
       <c r="C329" t="s">
         <v>107</v>
@@ -5768,10 +5759,10 @@
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>466</v>
+        <v>121</v>
       </c>
       <c r="B330" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C330" t="s">
         <v>107</v>
@@ -5779,7 +5770,7 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B331" t="s">
         <v>16</v>
@@ -5790,7 +5781,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>120</v>
+        <v>464</v>
       </c>
       <c r="B332" t="s">
         <v>16</v>
@@ -5801,10 +5792,10 @@
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>121</v>
+        <v>465</v>
       </c>
       <c r="B333" t="s">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c r="C333" t="s">
         <v>107</v>
@@ -5812,10 +5803,10 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>122</v>
+        <v>466</v>
       </c>
       <c r="B334" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C334" t="s">
         <v>107</v>
@@ -5826,7 +5817,7 @@
         <v>467</v>
       </c>
       <c r="B335" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C335" t="s">
         <v>107</v>
@@ -5834,10 +5825,10 @@
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>468</v>
+        <v>123</v>
       </c>
       <c r="B336" t="s">
-        <v>301</v>
+        <v>54</v>
       </c>
       <c r="C336" t="s">
         <v>107</v>
@@ -5845,10 +5836,10 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B337" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C337" t="s">
         <v>107</v>
@@ -5856,10 +5847,10 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>470</v>
+        <v>124</v>
       </c>
       <c r="B338" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C338" t="s">
         <v>107</v>
@@ -5867,10 +5858,10 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>123</v>
+        <v>469</v>
       </c>
       <c r="B339" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C339" t="s">
         <v>107</v>
@@ -5878,10 +5869,10 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>471</v>
+        <v>125</v>
       </c>
       <c r="B340" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C340" t="s">
         <v>107</v>
@@ -5889,7 +5880,7 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>124</v>
+        <v>470</v>
       </c>
       <c r="B341" t="s">
         <v>7</v>
@@ -5900,7 +5891,7 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>472</v>
+        <v>126</v>
       </c>
       <c r="B342" t="s">
         <v>7</v>
@@ -5911,7 +5902,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B343" t="s">
         <v>7</v>
@@ -5922,7 +5913,7 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>473</v>
+        <v>128</v>
       </c>
       <c r="B344" t="s">
         <v>7</v>
@@ -5933,7 +5924,7 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B345" t="s">
         <v>7</v>
@@ -5944,7 +5935,7 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B346" t="s">
         <v>7</v>
@@ -5955,7 +5946,7 @@
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B347" t="s">
         <v>7</v>
@@ -5966,7 +5957,7 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>129</v>
+        <v>471</v>
       </c>
       <c r="B348" t="s">
         <v>7</v>
@@ -5977,7 +5968,7 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>130</v>
+        <v>472</v>
       </c>
       <c r="B349" t="s">
         <v>7</v>
@@ -5988,7 +5979,7 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B350" t="s">
         <v>7</v>
@@ -5999,7 +5990,7 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>474</v>
+        <v>133</v>
       </c>
       <c r="B351" t="s">
         <v>7</v>
@@ -6010,7 +6001,7 @@
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>475</v>
+        <v>134</v>
       </c>
       <c r="B352" t="s">
         <v>7</v>
@@ -6021,7 +6012,7 @@
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B353" t="s">
         <v>7</v>
@@ -6032,7 +6023,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B354" t="s">
         <v>7</v>
@@ -6043,7 +6034,7 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B355" t="s">
         <v>7</v>
@@ -6054,7 +6045,7 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B356" t="s">
         <v>7</v>
@@ -6065,7 +6056,7 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B357" t="s">
         <v>7</v>
@@ -6076,7 +6067,7 @@
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B358" t="s">
         <v>7</v>
@@ -6087,7 +6078,7 @@
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B359" t="s">
         <v>7</v>
@@ -6098,7 +6089,7 @@
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B360" t="s">
         <v>7</v>
@@ -6109,7 +6100,7 @@
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B361" t="s">
         <v>7</v>
@@ -6120,7 +6111,7 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B362" t="s">
         <v>7</v>
@@ -6131,7 +6122,7 @@
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B363" t="s">
         <v>7</v>
@@ -6142,7 +6133,7 @@
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B364" t="s">
         <v>7</v>
@@ -6153,7 +6144,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B365" t="s">
         <v>7</v>
@@ -6164,7 +6155,7 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B366" t="s">
         <v>7</v>
@@ -6175,7 +6166,7 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B367" t="s">
         <v>7</v>
@@ -6186,7 +6177,7 @@
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B368" t="s">
         <v>7</v>
@@ -6197,7 +6188,7 @@
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B369" t="s">
         <v>7</v>
@@ -6208,10 +6199,10 @@
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>149</v>
+        <v>250</v>
       </c>
       <c r="B370" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C370" t="s">
         <v>107</v>
@@ -6219,10 +6210,10 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B371" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C371" t="s">
         <v>107</v>
@@ -6230,10 +6221,10 @@
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B372" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C372" t="s">
         <v>107</v>
@@ -6241,7 +6232,7 @@
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>250</v>
+        <v>154</v>
       </c>
       <c r="B373" t="s">
         <v>45</v>
@@ -6252,7 +6243,7 @@
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B374" t="s">
         <v>45</v>
@@ -6263,7 +6254,7 @@
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B375" t="s">
         <v>45</v>
@@ -6274,7 +6265,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B376" t="s">
         <v>45</v>
@@ -6285,10 +6276,10 @@
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>155</v>
+        <v>232</v>
       </c>
       <c r="B377" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C377" t="s">
         <v>107</v>
@@ -6296,10 +6287,10 @@
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>156</v>
+        <v>473</v>
       </c>
       <c r="B378" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C378" t="s">
         <v>107</v>
@@ -6307,10 +6298,10 @@
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B379" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C379" t="s">
         <v>107</v>
@@ -6318,10 +6309,10 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>232</v>
+        <v>158</v>
       </c>
       <c r="B380" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C380" t="s">
         <v>107</v>
@@ -6329,10 +6320,10 @@
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>476</v>
+        <v>159</v>
       </c>
       <c r="B381" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C381" t="s">
         <v>107</v>
@@ -6340,7 +6331,7 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B382" t="s">
         <v>16</v>
@@ -6351,7 +6342,7 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B383" t="s">
         <v>16</v>
@@ -6362,7 +6353,7 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B384" t="s">
         <v>16</v>
@@ -6373,7 +6364,7 @@
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B385" t="s">
         <v>16</v>
@@ -6384,7 +6375,7 @@
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B386" t="s">
         <v>16</v>
@@ -6395,7 +6386,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B387" t="s">
         <v>16</v>
@@ -6406,7 +6397,7 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B388" t="s">
         <v>16</v>
@@ -6417,7 +6408,7 @@
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B389" t="s">
         <v>16</v>
@@ -6428,7 +6419,7 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B390" t="s">
         <v>16</v>
@@ -6439,7 +6430,7 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B391" t="s">
         <v>16</v>
@@ -6450,7 +6441,7 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B392" t="s">
         <v>16</v>
@@ -6461,7 +6452,7 @@
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B393" t="s">
         <v>16</v>
@@ -6472,7 +6463,7 @@
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B394" t="s">
         <v>16</v>
@@ -6483,7 +6474,7 @@
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B395" t="s">
         <v>16</v>
@@ -6494,7 +6485,7 @@
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B396" t="s">
         <v>16</v>
@@ -6505,7 +6496,7 @@
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>172</v>
+        <v>474</v>
       </c>
       <c r="B397" t="s">
         <v>16</v>
@@ -6516,7 +6507,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>173</v>
+        <v>475</v>
       </c>
       <c r="B398" t="s">
         <v>16</v>
@@ -6527,7 +6518,7 @@
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>174</v>
+        <v>476</v>
       </c>
       <c r="B399" t="s">
         <v>16</v>
@@ -6538,7 +6529,7 @@
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>477</v>
+        <v>175</v>
       </c>
       <c r="B400" t="s">
         <v>16</v>
@@ -6549,7 +6540,7 @@
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>478</v>
+        <v>176</v>
       </c>
       <c r="B401" t="s">
         <v>16</v>
@@ -6560,7 +6551,7 @@
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B402" t="s">
         <v>16</v>
@@ -6571,7 +6562,7 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>175</v>
+        <v>478</v>
       </c>
       <c r="B403" t="s">
         <v>16</v>
@@ -6582,10 +6573,10 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>176</v>
+        <v>479</v>
       </c>
       <c r="B404" t="s">
-        <v>16</v>
+        <v>480</v>
       </c>
       <c r="C404" t="s">
         <v>107</v>
@@ -6593,10 +6584,10 @@
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B405" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C405" t="s">
         <v>107</v>
@@ -6604,7 +6595,7 @@
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B406" t="s">
         <v>16</v>
@@ -6615,10 +6606,10 @@
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B407" t="s">
-        <v>483</v>
+        <v>13</v>
       </c>
       <c r="C407" t="s">
         <v>107</v>
@@ -6637,10 +6628,10 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>485</v>
+        <v>177</v>
       </c>
       <c r="B409" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C409" t="s">
         <v>107</v>
@@ -6648,10 +6639,10 @@
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>486</v>
+        <v>256</v>
       </c>
       <c r="B410" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C410" t="s">
         <v>107</v>
@@ -6659,10 +6650,10 @@
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>487</v>
+        <v>178</v>
       </c>
       <c r="B411" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C411" t="s">
         <v>107</v>
@@ -6670,10 +6661,10 @@
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B412" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C412" t="s">
         <v>107</v>
@@ -6681,10 +6672,10 @@
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>256</v>
+        <v>180</v>
       </c>
       <c r="B413" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C413" t="s">
         <v>107</v>
@@ -6692,10 +6683,10 @@
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B414" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C414" t="s">
         <v>107</v>
@@ -6703,7 +6694,7 @@
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B415" t="s">
         <v>54</v>
@@ -6714,7 +6705,7 @@
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>180</v>
+        <v>554</v>
       </c>
       <c r="B416" t="s">
         <v>54</v>
@@ -6725,10 +6716,10 @@
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>181</v>
+        <v>485</v>
       </c>
       <c r="B417" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C417" t="s">
         <v>107</v>
@@ -6736,10 +6727,10 @@
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B418" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C418" t="s">
         <v>107</v>
@@ -6747,10 +6738,10 @@
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>557</v>
+        <v>486</v>
       </c>
       <c r="B419" t="s">
-        <v>54</v>
+        <v>553</v>
       </c>
       <c r="C419" t="s">
         <v>107</v>
@@ -6758,10 +6749,10 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B420" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="C420" t="s">
         <v>107</v>
@@ -6769,10 +6760,10 @@
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>183</v>
+        <v>488</v>
       </c>
       <c r="B421" t="s">
-        <v>45</v>
+        <v>553</v>
       </c>
       <c r="C421" t="s">
         <v>107</v>
@@ -6783,7 +6774,7 @@
         <v>489</v>
       </c>
       <c r="B422" t="s">
-        <v>556</v>
+        <v>301</v>
       </c>
       <c r="C422" t="s">
         <v>107</v>
@@ -6791,10 +6782,10 @@
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>490</v>
+        <v>184</v>
       </c>
       <c r="B423" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C423" t="s">
         <v>107</v>
@@ -6802,10 +6793,10 @@
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>491</v>
+        <v>185</v>
       </c>
       <c r="B424" t="s">
-        <v>556</v>
+        <v>16</v>
       </c>
       <c r="C424" t="s">
         <v>107</v>
@@ -6813,10 +6804,10 @@
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>492</v>
+        <v>186</v>
       </c>
       <c r="B425" t="s">
-        <v>301</v>
+        <v>16</v>
       </c>
       <c r="C425" t="s">
         <v>107</v>
@@ -6824,7 +6815,7 @@
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B426" t="s">
         <v>16</v>
@@ -6835,7 +6826,7 @@
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B427" t="s">
         <v>16</v>
@@ -6846,7 +6837,7 @@
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B428" t="s">
         <v>16</v>
@@ -6857,7 +6848,7 @@
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B429" t="s">
         <v>16</v>
@@ -6868,7 +6859,7 @@
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B430" t="s">
         <v>16</v>
@@ -6879,10 +6870,10 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B431" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C431" t="s">
         <v>107</v>
@@ -6890,10 +6881,10 @@
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B432" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C432" t="s">
         <v>107</v>
@@ -6901,10 +6892,10 @@
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B433" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C433" t="s">
         <v>107</v>
@@ -6912,7 +6903,7 @@
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>191</v>
+        <v>490</v>
       </c>
       <c r="B434" t="s">
         <v>13</v>
@@ -6923,7 +6914,7 @@
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B435" t="s">
         <v>13</v>
@@ -6934,7 +6925,7 @@
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B436" t="s">
         <v>13</v>
@@ -6945,7 +6936,7 @@
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B437" t="s">
         <v>13</v>
@@ -6956,10 +6947,10 @@
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>194</v>
+        <v>492</v>
       </c>
       <c r="B438" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C438" t="s">
         <v>107</v>
@@ -6967,10 +6958,10 @@
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>195</v>
+        <v>493</v>
       </c>
       <c r="B439" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C439" t="s">
         <v>107</v>
@@ -6981,7 +6972,7 @@
         <v>494</v>
       </c>
       <c r="B440" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C440" t="s">
         <v>107</v>
@@ -6989,10 +6980,10 @@
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>495</v>
+        <v>234</v>
       </c>
       <c r="B441" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C441" t="s">
         <v>107</v>
@@ -7000,10 +6991,10 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>496</v>
+        <v>233</v>
       </c>
       <c r="B442" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C442" t="s">
         <v>107</v>
@@ -7011,10 +7002,10 @@
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>497</v>
+        <v>196</v>
       </c>
       <c r="B443" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C443" t="s">
         <v>107</v>
@@ -7022,7 +7013,7 @@
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="B444" t="s">
         <v>13</v>
@@ -7033,7 +7024,7 @@
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="B445" t="s">
         <v>13</v>
@@ -7044,7 +7035,7 @@
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B446" t="s">
         <v>13</v>
@@ -7055,7 +7046,7 @@
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B447" t="s">
         <v>13</v>
@@ -7066,7 +7057,7 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B448" t="s">
         <v>13</v>
@@ -7077,7 +7068,7 @@
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>199</v>
+        <v>495</v>
       </c>
       <c r="B449" t="s">
         <v>13</v>
@@ -7088,7 +7079,7 @@
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B450" t="s">
         <v>13</v>
@@ -7099,7 +7090,7 @@
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>201</v>
+        <v>496</v>
       </c>
       <c r="B451" t="s">
         <v>13</v>
@@ -7110,7 +7101,7 @@
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>498</v>
+        <v>203</v>
       </c>
       <c r="B452" t="s">
         <v>13</v>
@@ -7121,7 +7112,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>202</v>
+        <v>497</v>
       </c>
       <c r="B453" t="s">
         <v>13</v>
@@ -7132,7 +7123,7 @@
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B454" t="s">
         <v>13</v>
@@ -7143,10 +7134,10 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>203</v>
+        <v>499</v>
       </c>
       <c r="B455" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C455" t="s">
         <v>107</v>
@@ -7154,10 +7145,10 @@
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>500</v>
+        <v>204</v>
       </c>
       <c r="B456" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C456" t="s">
         <v>107</v>
@@ -7165,10 +7156,10 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>501</v>
+        <v>205</v>
       </c>
       <c r="B457" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C457" t="s">
         <v>107</v>
@@ -7176,10 +7167,10 @@
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>502</v>
+        <v>206</v>
       </c>
       <c r="B458" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C458" t="s">
         <v>107</v>
@@ -7187,7 +7178,7 @@
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B459" t="s">
         <v>11</v>
@@ -7198,7 +7189,7 @@
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B460" t="s">
         <v>11</v>
@@ -7209,7 +7200,7 @@
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B461" t="s">
         <v>11</v>
@@ -7220,7 +7211,7 @@
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B462" t="s">
         <v>11</v>
@@ -7231,7 +7222,7 @@
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>208</v>
+        <v>276</v>
       </c>
       <c r="B463" t="s">
         <v>11</v>
@@ -7242,7 +7233,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>209</v>
+        <v>500</v>
       </c>
       <c r="B464" t="s">
         <v>11</v>
@@ -7253,7 +7244,7 @@
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>210</v>
+        <v>501</v>
       </c>
       <c r="B465" t="s">
         <v>11</v>
@@ -7264,7 +7255,7 @@
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>276</v>
+        <v>502</v>
       </c>
       <c r="B466" t="s">
         <v>11</v>
@@ -7275,7 +7266,7 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>503</v>
+        <v>211</v>
       </c>
       <c r="B467" t="s">
         <v>11</v>
@@ -7286,7 +7277,7 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>504</v>
+        <v>212</v>
       </c>
       <c r="B468" t="s">
         <v>11</v>
@@ -7297,7 +7288,7 @@
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>505</v>
+        <v>213</v>
       </c>
       <c r="B469" t="s">
         <v>11</v>
@@ -7308,7 +7299,7 @@
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B470" t="s">
         <v>11</v>
@@ -7319,10 +7310,10 @@
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>212</v>
+        <v>503</v>
       </c>
       <c r="B471" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C471" t="s">
         <v>107</v>
@@ -7330,10 +7321,10 @@
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B472" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C472" t="s">
         <v>107</v>
@@ -7341,10 +7332,10 @@
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B473" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C473" t="s">
         <v>107</v>
@@ -7352,7 +7343,7 @@
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>506</v>
+        <v>217</v>
       </c>
       <c r="B474" t="s">
         <v>45</v>
@@ -7363,7 +7354,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B475" t="s">
         <v>45</v>
@@ -7374,7 +7365,7 @@
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B476" t="s">
         <v>45</v>
@@ -7385,7 +7376,7 @@
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B477" t="s">
         <v>45</v>
@@ -7396,7 +7387,7 @@
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B478" t="s">
         <v>45</v>
@@ -7407,7 +7398,7 @@
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>219</v>
+        <v>504</v>
       </c>
       <c r="B479" t="s">
         <v>45</v>
@@ -7418,7 +7409,7 @@
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>220</v>
+        <v>505</v>
       </c>
       <c r="B480" t="s">
         <v>45</v>
@@ -7429,7 +7420,7 @@
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>221</v>
+        <v>506</v>
       </c>
       <c r="B481" t="s">
         <v>45</v>
@@ -7443,7 +7434,7 @@
         <v>507</v>
       </c>
       <c r="B482" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C482" t="s">
         <v>107</v>
@@ -7454,7 +7445,7 @@
         <v>508</v>
       </c>
       <c r="B483" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C483" t="s">
         <v>107</v>
@@ -7465,7 +7456,7 @@
         <v>509</v>
       </c>
       <c r="B484" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C484" t="s">
         <v>107</v>
@@ -7484,10 +7475,10 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>511</v>
+        <v>222</v>
       </c>
       <c r="B486" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C486" t="s">
         <v>107</v>
@@ -7495,10 +7486,10 @@
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>512</v>
+        <v>242</v>
       </c>
       <c r="B487" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C487" t="s">
         <v>107</v>
@@ -7506,43 +7497,43 @@
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>513</v>
+        <v>223</v>
       </c>
       <c r="B488" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C488" t="s">
-        <v>107</v>
+        <v>224</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B489" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C489" t="s">
-        <v>107</v>
+        <v>224</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="B490" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C490" t="s">
-        <v>107</v>
+        <v>224</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B491" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C491" t="s">
         <v>224</v>
@@ -7550,43 +7541,43 @@
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B492" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C492" t="s">
-        <v>224</v>
+        <v>99</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B493" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C493" t="s">
-        <v>224</v>
+        <v>99</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B494" t="s">
-        <v>11</v>
+        <v>231</v>
       </c>
       <c r="C494" t="s">
-        <v>224</v>
+        <v>99</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>228</v>
+        <v>272</v>
       </c>
       <c r="B495" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C495" t="s">
         <v>99</v>
@@ -7594,10 +7585,10 @@
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="B496" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C496" t="s">
         <v>99</v>
@@ -7605,10 +7596,10 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>230</v>
+        <v>98</v>
       </c>
       <c r="B497" t="s">
-        <v>231</v>
+        <v>11</v>
       </c>
       <c r="C497" t="s">
         <v>99</v>
@@ -7616,10 +7607,10 @@
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="B498" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C498" t="s">
         <v>99</v>
@@ -7627,10 +7618,10 @@
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="B499" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C499" t="s">
         <v>99</v>
@@ -7638,46 +7629,46 @@
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>98</v>
+        <v>511</v>
       </c>
       <c r="B500" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C500" t="s">
-        <v>99</v>
+        <v>512</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>251</v>
+        <v>513</v>
       </c>
       <c r="B501" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C501" t="s">
-        <v>99</v>
+        <v>512</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>252</v>
+        <v>514</v>
       </c>
       <c r="B502" t="s">
         <v>45</v>
       </c>
       <c r="C502" t="s">
-        <v>99</v>
+        <v>512</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B503" t="s">
         <v>45</v>
       </c>
       <c r="C503" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.35">
@@ -7685,10 +7676,10 @@
         <v>516</v>
       </c>
       <c r="B504" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C504" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.35">
@@ -7696,10 +7687,10 @@
         <v>517</v>
       </c>
       <c r="B505" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C505" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.35">
@@ -7707,10 +7698,10 @@
         <v>518</v>
       </c>
       <c r="B506" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C506" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.35">
@@ -7718,10 +7709,10 @@
         <v>519</v>
       </c>
       <c r="B507" t="s">
-        <v>13</v>
+        <v>480</v>
       </c>
       <c r="C507" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.35">
@@ -7729,10 +7720,10 @@
         <v>520</v>
       </c>
       <c r="B508" t="s">
-        <v>13</v>
+        <v>480</v>
       </c>
       <c r="C508" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.35">
@@ -7740,10 +7731,10 @@
         <v>521</v>
       </c>
       <c r="B509" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C509" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.35">
@@ -7751,10 +7742,10 @@
         <v>522</v>
       </c>
       <c r="B510" t="s">
-        <v>483</v>
+        <v>4</v>
       </c>
       <c r="C510" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.35">
@@ -7762,10 +7753,10 @@
         <v>523</v>
       </c>
       <c r="B511" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C511" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.35">
@@ -7773,10 +7764,10 @@
         <v>524</v>
       </c>
       <c r="B512" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="C512" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.35">
@@ -7784,10 +7775,10 @@
         <v>525</v>
       </c>
       <c r="B513" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C513" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.35">
@@ -7795,10 +7786,10 @@
         <v>526</v>
       </c>
       <c r="B514" t="s">
-        <v>483</v>
+        <v>16</v>
       </c>
       <c r="C514" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.35">
@@ -7806,10 +7797,10 @@
         <v>527</v>
       </c>
       <c r="B515" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C515" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.35">
@@ -7817,10 +7808,10 @@
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C516" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.35">
@@ -7828,10 +7819,10 @@
         <v>529</v>
       </c>
       <c r="B517" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C517" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.35">
@@ -7839,10 +7830,10 @@
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C518" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.35">
@@ -7850,10 +7841,10 @@
         <v>531</v>
       </c>
       <c r="B519" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C519" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.35">
@@ -7861,10 +7852,10 @@
         <v>532</v>
       </c>
       <c r="B520" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C520" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.35">
@@ -7872,10 +7863,10 @@
         <v>533</v>
       </c>
       <c r="B521" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C521" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.35">
@@ -7883,43 +7874,43 @@
         <v>534</v>
       </c>
       <c r="B522" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C522" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B523" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C523" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B524" t="s">
         <v>16</v>
       </c>
       <c r="C524" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B525" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C525" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.35">
@@ -7927,10 +7918,10 @@
         <v>537</v>
       </c>
       <c r="B526" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C526" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.35">
@@ -7941,7 +7932,7 @@
         <v>16</v>
       </c>
       <c r="C527" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.35">
@@ -7949,10 +7940,10 @@
         <v>539</v>
       </c>
       <c r="B528" t="s">
-        <v>45</v>
+        <v>231</v>
       </c>
       <c r="C528" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.35">
@@ -7960,10 +7951,10 @@
         <v>540</v>
       </c>
       <c r="B529" t="s">
-        <v>45</v>
+        <v>553</v>
       </c>
       <c r="C529" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.35">
@@ -7971,10 +7962,10 @@
         <v>541</v>
       </c>
       <c r="B530" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="C530" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.35">
@@ -7982,10 +7973,10 @@
         <v>542</v>
       </c>
       <c r="B531" t="s">
-        <v>231</v>
+        <v>4</v>
       </c>
       <c r="C531" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.35">
@@ -7993,10 +7984,10 @@
         <v>543</v>
       </c>
       <c r="B532" t="s">
-        <v>556</v>
+        <v>13</v>
       </c>
       <c r="C532" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.35">
@@ -8004,10 +7995,10 @@
         <v>544</v>
       </c>
       <c r="B533" t="s">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="C533" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.35">
@@ -8015,10 +8006,10 @@
         <v>545</v>
       </c>
       <c r="B534" t="s">
-        <v>4</v>
+        <v>301</v>
       </c>
       <c r="C534" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.35">
@@ -8026,43 +8017,43 @@
         <v>546</v>
       </c>
       <c r="B535" t="s">
-        <v>13</v>
+        <v>547</v>
       </c>
       <c r="C535" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B536" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C536" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B537" t="s">
-        <v>301</v>
+        <v>13</v>
       </c>
       <c r="C537" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B538" t="s">
-        <v>550</v>
+        <v>13</v>
       </c>
       <c r="C538" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.35">
@@ -8073,40 +8064,7 @@
         <v>13</v>
       </c>
       <c r="C539" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A540" t="s">
-        <v>552</v>
-      </c>
-      <c r="B540" t="s">
-        <v>13</v>
-      </c>
-      <c r="C540" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A541" t="s">
-        <v>553</v>
-      </c>
-      <c r="B541" t="s">
-        <v>13</v>
-      </c>
-      <c r="C541" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A542" t="s">
-        <v>554</v>
-      </c>
-      <c r="B542" t="s">
-        <v>13</v>
-      </c>
-      <c r="C542" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>

--- a/Vehicle Catalogue.xlsx
+++ b/Vehicle Catalogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samhi\Documents\My Games\Sprocket\Ostfront Tank Collection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4217CB8-45D2-45A6-A14E-2B9145A2D5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE965D25-0A67-4A23-9DE8-AF197B1F57B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11090" yWindow="6100" windowWidth="28800" windowHeight="15360" xr2:uid="{3FAC36FE-B102-4B04-8548-70F58966D145}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{3FAC36FE-B102-4B04-8548-70F58966D145}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="608">
   <si>
     <t>Tank</t>
   </si>
@@ -419,9 +419,6 @@
     <t>M1921 Medium Tank</t>
   </si>
   <si>
-    <t>M2 Medium Tank</t>
-  </si>
-  <si>
     <t>M4 Sherman I Hybrid</t>
   </si>
   <si>
@@ -773,12 +770,6 @@
     <t>ZSU-37</t>
   </si>
   <si>
-    <t>ZiS-22</t>
-  </si>
-  <si>
-    <t>Halftrack</t>
-  </si>
-  <si>
     <t>ISU-T</t>
   </si>
   <si>
@@ -1439,9 +1430,6 @@
     <t>Krupp-Steyr Waffenträger</t>
   </si>
   <si>
-    <t>Lago</t>
-  </si>
-  <si>
     <t>LTG</t>
   </si>
   <si>
@@ -1707,6 +1695,177 @@
   </si>
   <si>
     <t>Semovente da 90/53 M41M</t>
+  </si>
+  <si>
+    <t>AMD.35 (SA35)</t>
+  </si>
+  <si>
+    <t>DAF M39</t>
+  </si>
+  <si>
+    <t>KSP-76</t>
+  </si>
+  <si>
+    <t>Lvtdgb m/40</t>
+  </si>
+  <si>
+    <t>Pbil m/40</t>
+  </si>
+  <si>
+    <t>Sd.Kfz.221 (s.Pz.B.41)</t>
+  </si>
+  <si>
+    <t>T18E2</t>
+  </si>
+  <si>
+    <t>T55E1</t>
+  </si>
+  <si>
+    <t>T69 MGMC</t>
+  </si>
+  <si>
+    <t>Type 93 kokusan</t>
+  </si>
+  <si>
+    <t>Type 4 Chi-So</t>
+  </si>
+  <si>
+    <t>Type 98 So-Da</t>
+  </si>
+  <si>
+    <t>Char 2C Bis</t>
+  </si>
+  <si>
+    <t>Char B1 Ter</t>
+  </si>
+  <si>
+    <t>IS-152-2</t>
+  </si>
+  <si>
+    <t>IS-4 100</t>
+  </si>
+  <si>
+    <t>IS-4M</t>
+  </si>
+  <si>
+    <t>IS-7</t>
+  </si>
+  <si>
+    <t>KV-2 ZIS-6</t>
+  </si>
+  <si>
+    <t>KV-4B</t>
+  </si>
+  <si>
+    <t>M6A2E1</t>
+  </si>
+  <si>
+    <t>Pz.Bef.Wg.VI P</t>
+  </si>
+  <si>
+    <t>Pz.Kpfw. KV-2 754(r)</t>
+  </si>
+  <si>
+    <t>Sd.Kfz. 179 Bergepanther</t>
+  </si>
+  <si>
+    <t>T32E1</t>
+  </si>
+  <si>
+    <t>T-42</t>
+  </si>
+  <si>
+    <t>T92 HMC</t>
+  </si>
+  <si>
+    <t>T93 HMC</t>
+  </si>
+  <si>
+    <t>AMC.34 YR</t>
+  </si>
+  <si>
+    <t>LVT(A)(1</t>
+  </si>
+  <si>
+    <t>LVT(A)(1) (M24)</t>
+  </si>
+  <si>
+    <t>LVT(A)(4)</t>
+  </si>
+  <si>
+    <t>M18 90 mm</t>
+  </si>
+  <si>
+    <t>M2A2</t>
+  </si>
+  <si>
+    <t>Spj fm/43</t>
+  </si>
+  <si>
+    <t>T-50E</t>
+  </si>
+  <si>
+    <t>Type 2 Ka-Mi</t>
+  </si>
+  <si>
+    <t>Type 5 Ho-To</t>
+  </si>
+  <si>
+    <t>Type 92 HAC</t>
+  </si>
+  <si>
+    <t>Type 95 So-Ki</t>
+  </si>
+  <si>
+    <t>Type 98 Ta-Se</t>
+  </si>
+  <si>
+    <t>ZUT-37</t>
+  </si>
+  <si>
+    <t>M2A1 medium</t>
+  </si>
+  <si>
+    <t>M2A1 Medium Flamm</t>
+  </si>
+  <si>
+    <t>Matilda F-96</t>
+  </si>
+  <si>
+    <t>T-34-100</t>
+  </si>
+  <si>
+    <t>T-34-85 (1941) STZ</t>
+  </si>
+  <si>
+    <t>Type 3 Chi-Nu II</t>
+  </si>
+  <si>
+    <t>Type 3 Ka-Chi</t>
+  </si>
+  <si>
+    <t>Type 5 To-Ku</t>
+  </si>
+  <si>
+    <t>Type 89 SS-Ki</t>
+  </si>
+  <si>
+    <t>Type 97 Se-Ri</t>
+  </si>
+  <si>
+    <t>Type 97 Shi-Ki</t>
+  </si>
+  <si>
+    <t>Type 5 Na-To</t>
+  </si>
+  <si>
+    <t>SPM</t>
+  </si>
+  <si>
+    <t>Type 94</t>
+  </si>
+  <si>
+    <t>GMC T27 "Xylophone"</t>
   </si>
 </sst>
 </file>
@@ -2130,11 +2289,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C50DCCC-8446-4FAC-BA76-D53F2D86B716}">
-  <dimension ref="A1:C539"/>
+  <dimension ref="A1:C594"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.81640625" customWidth="1"/>
-    <col min="2" max="2" width="15.36328125" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" customWidth="1"/>
     <col min="3" max="3" width="15.54296875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2151,912 +2310,912 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B2" t="s">
         <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B3" t="s">
         <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>284</v>
+        <v>551</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B8" t="s">
-        <v>286</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>283</v>
       </c>
       <c r="C9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>288</v>
+        <v>552</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B11" t="s">
         <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B16" t="s">
         <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B17" t="s">
         <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B18" t="s">
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B21" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B22" t="s">
-        <v>301</v>
+        <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>302</v>
+        <v>553</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>298</v>
       </c>
       <c r="C25" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>305</v>
+        <v>554</v>
       </c>
       <c r="B26" t="s">
-        <v>4</v>
+        <v>298</v>
       </c>
       <c r="C26" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>310</v>
+        <v>555</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>298</v>
       </c>
       <c r="C31" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s">
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s">
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>318</v>
+        <v>556</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="B40" t="s">
-        <v>231</v>
+        <v>7</v>
       </c>
       <c r="C40" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="B41" t="s">
-        <v>231</v>
+        <v>7</v>
       </c>
       <c r="C41" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>271</v>
+        <v>312</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>5</v>
+        <v>276</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>3</v>
+        <v>313</v>
       </c>
       <c r="B43" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C43" t="s">
-        <v>5</v>
+        <v>276</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>557</v>
       </c>
       <c r="B44" t="s">
         <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>5</v>
+        <v>276</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>10</v>
+        <v>558</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C45" t="s">
-        <v>5</v>
+        <v>276</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>255</v>
+        <v>559</v>
       </c>
       <c r="B46" t="s">
-        <v>231</v>
+        <v>7</v>
       </c>
       <c r="C46" t="s">
-        <v>8</v>
+        <v>276</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>6</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>276</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>276</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>560</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>8</v>
+        <v>276</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>230</v>
       </c>
       <c r="C50" t="s">
-        <v>322</v>
+        <v>276</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B51" t="s">
-        <v>54</v>
+        <v>230</v>
       </c>
       <c r="C51" t="s">
-        <v>322</v>
+        <v>276</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>324</v>
+        <v>268</v>
       </c>
       <c r="B52" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>322</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>325</v>
+        <v>3</v>
       </c>
       <c r="B53" t="s">
         <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>322</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>326</v>
+        <v>9</v>
       </c>
       <c r="B54" t="s">
         <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>322</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>327</v>
+        <v>10</v>
       </c>
       <c r="B55" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C55" t="s">
-        <v>322</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>328</v>
+        <v>561</v>
       </c>
       <c r="B56" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C56" t="s">
-        <v>322</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>329</v>
+        <v>562</v>
       </c>
       <c r="B57" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C57" t="s">
-        <v>322</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>330</v>
+        <v>252</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="C58" t="s">
-        <v>322</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>331</v>
+        <v>6</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>322</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>332</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>322</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>333</v>
+        <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>322</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="B62" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="C62" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="B63" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="B64" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C64" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="B65" t="s">
-        <v>231</v>
+        <v>4</v>
       </c>
       <c r="C65" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="B66" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C66" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="B67" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C67" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="B68" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C69" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="B70" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="B71" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>243</v>
+        <v>329</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C72" t="s">
-        <v>244</v>
+        <v>319</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="B73" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="C73" t="s">
-        <v>17</v>
+        <v>319</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>246</v>
+        <v>331</v>
       </c>
       <c r="B74" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C74" t="s">
-        <v>17</v>
+        <v>319</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="B75" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C75" t="s">
-        <v>17</v>
+        <v>319</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="B76" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C76" t="s">
-        <v>17</v>
+        <v>319</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="B77" t="s">
-        <v>45</v>
+        <v>230</v>
       </c>
       <c r="C77" t="s">
-        <v>17</v>
+        <v>319</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="B78" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C78" t="s">
-        <v>17</v>
+        <v>319</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="B79" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>17</v>
+        <v>319</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="B80" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C80" t="s">
-        <v>17</v>
+        <v>319</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>253</v>
+        <v>338</v>
       </c>
       <c r="B81" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C81" t="s">
-        <v>17</v>
+        <v>319</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="B82" t="s">
         <v>16</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>319</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="B83" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C83" t="s">
-        <v>17</v>
+        <v>319</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>15</v>
+        <v>341</v>
       </c>
       <c r="B84" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C84" t="s">
         <v>17</v>
@@ -3064,10 +3223,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>18</v>
+        <v>243</v>
       </c>
       <c r="B85" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C85" t="s">
         <v>17</v>
@@ -3075,10 +3234,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="B86" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="C86" t="s">
         <v>17</v>
@@ -3086,10 +3245,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="B87" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C87" t="s">
         <v>17</v>
@@ -3097,10 +3256,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="B88" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C88" t="s">
         <v>17</v>
@@ -3108,10 +3267,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="B89" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C89" t="s">
         <v>17</v>
@@ -3119,10 +3278,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>19</v>
+        <v>346</v>
       </c>
       <c r="B90" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C90" t="s">
         <v>17</v>
@@ -3130,10 +3289,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>20</v>
+        <v>563</v>
       </c>
       <c r="B91" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C91" t="s">
         <v>17</v>
@@ -3141,10 +3300,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>21</v>
+        <v>564</v>
       </c>
       <c r="B92" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C92" t="s">
         <v>17</v>
@@ -3152,10 +3311,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>22</v>
+        <v>347</v>
       </c>
       <c r="B93" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C93" t="s">
         <v>17</v>
@@ -3163,10 +3322,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>23</v>
+        <v>250</v>
       </c>
       <c r="B94" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C94" t="s">
         <v>17</v>
@@ -3174,10 +3333,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>24</v>
+        <v>348</v>
       </c>
       <c r="B95" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C95" t="s">
         <v>17</v>
@@ -3185,10 +3344,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>25</v>
+        <v>349</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C96" t="s">
         <v>17</v>
@@ -3196,10 +3355,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C97" t="s">
         <v>17</v>
@@ -3207,10 +3366,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>237</v>
+        <v>18</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C98" t="s">
         <v>17</v>
@@ -3218,10 +3377,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>245</v>
+        <v>350</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C99" t="s">
         <v>17</v>
@@ -3229,7 +3388,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B100" t="s">
         <v>16</v>
@@ -3240,7 +3399,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>27</v>
+        <v>352</v>
       </c>
       <c r="B101" t="s">
         <v>16</v>
@@ -3251,10 +3410,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>28</v>
+        <v>353</v>
       </c>
       <c r="B102" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C102" t="s">
         <v>17</v>
@@ -3262,7 +3421,7 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>28</v>
+        <v>565</v>
       </c>
       <c r="B103" t="s">
         <v>13</v>
@@ -3273,7 +3432,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B104" t="s">
         <v>13</v>
@@ -3284,7 +3443,7 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>358</v>
+        <v>20</v>
       </c>
       <c r="B105" t="s">
         <v>13</v>
@@ -3294,8 +3453,8 @@
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A106" s="2" t="s">
-        <v>235</v>
+      <c r="A106" t="s">
+        <v>21</v>
       </c>
       <c r="B106" t="s">
         <v>13</v>
@@ -3306,7 +3465,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>235</v>
+        <v>22</v>
       </c>
       <c r="B107" t="s">
         <v>13</v>
@@ -3317,7 +3476,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>359</v>
+        <v>23</v>
       </c>
       <c r="B108" t="s">
         <v>13</v>
@@ -3328,7 +3487,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>30</v>
+        <v>566</v>
       </c>
       <c r="B109" t="s">
         <v>13</v>
@@ -3339,7 +3498,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>31</v>
+        <v>567</v>
       </c>
       <c r="B110" t="s">
         <v>13</v>
@@ -3350,7 +3509,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B111" t="s">
         <v>13</v>
@@ -3361,7 +3520,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>238</v>
+        <v>25</v>
       </c>
       <c r="B112" t="s">
         <v>13</v>
@@ -3372,10 +3531,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>33</v>
+        <v>568</v>
       </c>
       <c r="B113" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C113" t="s">
         <v>17</v>
@@ -3383,10 +3542,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B114" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C114" t="s">
         <v>17</v>
@@ -3394,10 +3553,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>360</v>
+        <v>236</v>
       </c>
       <c r="B115" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C115" t="s">
         <v>17</v>
@@ -3405,7 +3564,7 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>361</v>
+        <v>242</v>
       </c>
       <c r="B116" t="s">
         <v>13</v>
@@ -3416,10 +3575,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B117" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C117" t="s">
         <v>17</v>
@@ -3427,10 +3586,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B118" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C118" t="s">
         <v>17</v>
@@ -3438,7 +3597,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>363</v>
+        <v>28</v>
       </c>
       <c r="B119" t="s">
         <v>13</v>
@@ -3449,7 +3608,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>364</v>
+        <v>29</v>
       </c>
       <c r="B120" t="s">
         <v>13</v>
@@ -3460,7 +3619,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>365</v>
+        <v>569</v>
       </c>
       <c r="B121" t="s">
         <v>13</v>
@@ -3471,21 +3630,21 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="B122" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C122" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
-        <v>260</v>
+      <c r="A123" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="B123" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C123" t="s">
         <v>17</v>
@@ -3493,10 +3652,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>367</v>
+        <v>234</v>
       </c>
       <c r="B124" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C124" t="s">
         <v>17</v>
@@ -3504,7 +3663,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>35</v>
+        <v>356</v>
       </c>
       <c r="B125" t="s">
         <v>13</v>
@@ -3515,10 +3674,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>259</v>
+        <v>570</v>
       </c>
       <c r="B126" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C126" t="s">
         <v>17</v>
@@ -3526,10 +3685,10 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>258</v>
+        <v>30</v>
       </c>
       <c r="B127" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C127" t="s">
         <v>17</v>
@@ -3537,7 +3696,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>241</v>
+        <v>31</v>
       </c>
       <c r="B128" t="s">
         <v>13</v>
@@ -3547,11 +3706,11 @@
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A129" s="3" t="s">
-        <v>264</v>
+      <c r="A129" t="s">
+        <v>32</v>
       </c>
       <c r="B129" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C129" t="s">
         <v>17</v>
@@ -3559,10 +3718,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="B130" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C130" t="s">
         <v>17</v>
@@ -3570,7 +3729,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>270</v>
+        <v>33</v>
       </c>
       <c r="B131" t="s">
         <v>16</v>
@@ -3581,10 +3740,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B132" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C132" t="s">
         <v>17</v>
@@ -3592,10 +3751,10 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>368</v>
+        <v>571</v>
       </c>
       <c r="B133" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C133" t="s">
         <v>17</v>
@@ -3603,10 +3762,10 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="B134" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C134" t="s">
         <v>17</v>
@@ -3614,10 +3773,10 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>266</v>
+        <v>358</v>
       </c>
       <c r="B135" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C135" t="s">
         <v>17</v>
@@ -3625,10 +3784,10 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>37</v>
+        <v>359</v>
       </c>
       <c r="B136" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C136" t="s">
         <v>17</v>
@@ -3636,10 +3795,10 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B137" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C137" t="s">
         <v>17</v>
@@ -3647,10 +3806,10 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>38</v>
+        <v>360</v>
       </c>
       <c r="B138" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C138" t="s">
         <v>17</v>
@@ -3658,7 +3817,7 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B139" t="s">
         <v>13</v>
@@ -3669,7 +3828,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B140" t="s">
         <v>13</v>
@@ -3680,10 +3839,10 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B141" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
@@ -3691,10 +3850,10 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="B142" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C142" t="s">
         <v>17</v>
@@ -3702,10 +3861,10 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>240</v>
+        <v>364</v>
       </c>
       <c r="B143" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C143" t="s">
         <v>17</v>
@@ -3713,10 +3872,10 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>39</v>
+        <v>572</v>
       </c>
       <c r="B144" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
@@ -3724,7 +3883,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B145" t="s">
         <v>13</v>
@@ -3735,7 +3894,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>40</v>
+        <v>573</v>
       </c>
       <c r="B146" t="s">
         <v>13</v>
@@ -3746,10 +3905,10 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>373</v>
+        <v>256</v>
       </c>
       <c r="B147" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
@@ -3757,10 +3916,10 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>374</v>
+        <v>255</v>
       </c>
       <c r="B148" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
@@ -3768,21 +3927,21 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="B149" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C149" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
-        <v>376</v>
+      <c r="A150" s="3" t="s">
+        <v>261</v>
       </c>
       <c r="B150" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C150" t="s">
         <v>17</v>
@@ -3790,10 +3949,10 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>377</v>
+        <v>262</v>
       </c>
       <c r="B151" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -3801,10 +3960,10 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>378</v>
+        <v>267</v>
       </c>
       <c r="B152" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C152" t="s">
         <v>17</v>
@@ -3812,10 +3971,10 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>379</v>
+        <v>574</v>
       </c>
       <c r="B153" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C153" t="s">
         <v>17</v>
@@ -3823,7 +3982,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B154" t="s">
         <v>13</v>
@@ -3834,7 +3993,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>42</v>
+        <v>365</v>
       </c>
       <c r="B155" t="s">
         <v>13</v>
@@ -3845,10 +4004,10 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>247</v>
+        <v>366</v>
       </c>
       <c r="B156" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C156" t="s">
         <v>17</v>
@@ -3856,7 +4015,7 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>43</v>
+        <v>263</v>
       </c>
       <c r="B157" t="s">
         <v>16</v>
@@ -3867,7 +4026,7 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B158" t="s">
         <v>16</v>
@@ -3878,7 +4037,7 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>236</v>
+        <v>37</v>
       </c>
       <c r="B159" t="s">
         <v>16</v>
@@ -3889,10 +4048,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>380</v>
+        <v>38</v>
       </c>
       <c r="B160" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
@@ -3900,10 +4059,10 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>275</v>
+        <v>367</v>
       </c>
       <c r="B161" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C161" t="s">
         <v>17</v>
@@ -3911,10 +4070,10 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="B162" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C162" t="s">
         <v>17</v>
@@ -3922,10 +4081,10 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>46</v>
+        <v>369</v>
       </c>
       <c r="B163" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C163" t="s">
         <v>17</v>
@@ -3933,10 +4092,10 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>47</v>
+        <v>238</v>
       </c>
       <c r="B164" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C164" t="s">
         <v>17</v>
@@ -3944,10 +4103,10 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>48</v>
+        <v>239</v>
       </c>
       <c r="B165" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C165" t="s">
         <v>17</v>
@@ -3955,10 +4114,10 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>382</v>
+        <v>39</v>
       </c>
       <c r="B166" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C166" t="s">
         <v>17</v>
@@ -3966,10 +4125,10 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>383</v>
+        <v>39</v>
       </c>
       <c r="B167" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C167" t="s">
         <v>17</v>
@@ -3977,10 +4136,10 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>384</v>
+        <v>40</v>
       </c>
       <c r="B168" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C168" t="s">
         <v>17</v>
@@ -3988,10 +4147,10 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="B169" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C169" t="s">
         <v>17</v>
@@ -3999,10 +4158,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>552</v>
+        <v>371</v>
       </c>
       <c r="B170" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C170" t="s">
         <v>17</v>
@@ -4010,10 +4169,10 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="B171" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C171" t="s">
         <v>17</v>
@@ -4021,10 +4180,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>257</v>
+        <v>373</v>
       </c>
       <c r="B172" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C172" t="s">
         <v>17</v>
@@ -4032,10 +4191,10 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>49</v>
+        <v>374</v>
       </c>
       <c r="B173" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C173" t="s">
         <v>17</v>
@@ -4043,10 +4202,10 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="B174" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C174" t="s">
         <v>17</v>
@@ -4054,10 +4213,10 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="B175" t="s">
-        <v>553</v>
+        <v>7</v>
       </c>
       <c r="C175" t="s">
         <v>17</v>
@@ -4065,10 +4224,10 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>389</v>
+        <v>575</v>
       </c>
       <c r="B176" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C176" t="s">
         <v>17</v>
@@ -4076,296 +4235,296 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>277</v>
+        <v>41</v>
       </c>
       <c r="B177" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="C177" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>390</v>
+        <v>42</v>
       </c>
       <c r="B178" t="s">
-        <v>231</v>
+        <v>13</v>
       </c>
       <c r="C178" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>391</v>
+        <v>576</v>
       </c>
       <c r="B179" t="s">
         <v>13</v>
       </c>
       <c r="C179" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>392</v>
+        <v>577</v>
       </c>
       <c r="B180" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C180" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>393</v>
+        <v>578</v>
       </c>
       <c r="B181" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C181" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>394</v>
+        <v>244</v>
       </c>
       <c r="B182" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C182" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>395</v>
+        <v>43</v>
       </c>
       <c r="B183" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C183" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B184" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C184" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>262</v>
+        <v>235</v>
       </c>
       <c r="B185" t="s">
         <v>16</v>
       </c>
       <c r="C185" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>52</v>
+        <v>377</v>
       </c>
       <c r="B186" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C186" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="B187" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C187" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>53</v>
+        <v>378</v>
       </c>
       <c r="B188" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C188" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>398</v>
+        <v>46</v>
       </c>
       <c r="B189" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C189" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B190" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C190" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B191" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C191" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="B192" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C192" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="B193" t="s">
-        <v>301</v>
+        <v>16</v>
       </c>
       <c r="C193" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="B194" t="s">
         <v>16</v>
       </c>
       <c r="C194" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>57</v>
+        <v>382</v>
       </c>
       <c r="B195" t="s">
         <v>16</v>
       </c>
       <c r="C195" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>402</v>
+        <v>548</v>
       </c>
       <c r="B196" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C196" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>58</v>
+        <v>383</v>
       </c>
       <c r="B197" t="s">
         <v>16</v>
       </c>
       <c r="C197" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="B198" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C198" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>403</v>
+        <v>49</v>
       </c>
       <c r="B199" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C199" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="B200" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C200" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>59</v>
+        <v>385</v>
       </c>
       <c r="B201" t="s">
-        <v>7</v>
+        <v>549</v>
       </c>
       <c r="C201" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>60</v>
+        <v>386</v>
       </c>
       <c r="B202" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C202" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="B203" t="s">
-        <v>7</v>
+        <v>106</v>
       </c>
       <c r="C203" t="s">
         <v>51</v>
@@ -4373,10 +4532,10 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>61</v>
+        <v>387</v>
       </c>
       <c r="B204" t="s">
-        <v>7</v>
+        <v>230</v>
       </c>
       <c r="C204" t="s">
         <v>51</v>
@@ -4384,10 +4543,10 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="B205" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C205" t="s">
         <v>51</v>
@@ -4395,10 +4554,10 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>62</v>
+        <v>579</v>
       </c>
       <c r="B206" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C206" t="s">
         <v>51</v>
@@ -4406,10 +4565,10 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="B207" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C207" t="s">
         <v>51</v>
@@ -4417,10 +4576,10 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="B208" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C208" t="s">
         <v>51</v>
@@ -4428,10 +4587,10 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>63</v>
+        <v>391</v>
       </c>
       <c r="B209" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C209" t="s">
         <v>51</v>
@@ -4439,10 +4598,10 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="B210" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C210" t="s">
         <v>51</v>
@@ -4450,10 +4609,10 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="B211" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C211" t="s">
         <v>51</v>
@@ -4461,7 +4620,7 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>65</v>
+        <v>259</v>
       </c>
       <c r="B212" t="s">
         <v>16</v>
@@ -4472,10 +4631,10 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B213" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C213" t="s">
         <v>51</v>
@@ -4483,10 +4642,10 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>67</v>
+        <v>394</v>
       </c>
       <c r="B214" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C214" t="s">
         <v>51</v>
@@ -4494,10 +4653,10 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B215" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C215" t="s">
         <v>51</v>
@@ -4505,7 +4664,7 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="B216" t="s">
         <v>16</v>
@@ -4516,10 +4675,10 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>410</v>
+        <v>55</v>
       </c>
       <c r="B217" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C217" t="s">
         <v>51</v>
@@ -4527,10 +4686,10 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>411</v>
+        <v>56</v>
       </c>
       <c r="B218" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C218" t="s">
         <v>51</v>
@@ -4538,21 +4697,21 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>232</v>
+        <v>396</v>
       </c>
       <c r="B219" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C219" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A220" s="4" t="s">
-        <v>69</v>
+      <c r="A220" t="s">
+        <v>397</v>
       </c>
       <c r="B220" t="s">
-        <v>16</v>
+        <v>298</v>
       </c>
       <c r="C220" t="s">
         <v>51</v>
@@ -4560,7 +4719,7 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>70</v>
+        <v>398</v>
       </c>
       <c r="B221" t="s">
         <v>16</v>
@@ -4571,7 +4730,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B222" t="s">
         <v>16</v>
@@ -4582,10 +4741,10 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>72</v>
+        <v>399</v>
       </c>
       <c r="B223" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C223" t="s">
         <v>51</v>
@@ -4593,7 +4752,7 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="B224" t="s">
         <v>16</v>
@@ -4604,10 +4763,10 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>74</v>
+        <v>225</v>
       </c>
       <c r="B225" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C225" t="s">
         <v>51</v>
@@ -4615,10 +4774,10 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="B226" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C226" t="s">
         <v>51</v>
@@ -4626,10 +4785,10 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>263</v>
+        <v>401</v>
       </c>
       <c r="B227" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C227" t="s">
         <v>51</v>
@@ -4637,10 +4796,10 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>412</v>
+        <v>580</v>
       </c>
       <c r="B228" t="s">
-        <v>553</v>
+        <v>7</v>
       </c>
       <c r="C228" t="s">
         <v>51</v>
@@ -4648,10 +4807,10 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>413</v>
+        <v>581</v>
       </c>
       <c r="B229" t="s">
-        <v>301</v>
+        <v>7</v>
       </c>
       <c r="C229" t="s">
         <v>51</v>
@@ -4659,10 +4818,10 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>414</v>
+        <v>582</v>
       </c>
       <c r="B230" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C230" t="s">
         <v>51</v>
@@ -4670,10 +4829,10 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B231" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C231" t="s">
         <v>51</v>
@@ -4681,10 +4840,10 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>415</v>
+        <v>583</v>
       </c>
       <c r="B232" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C232" t="s">
         <v>51</v>
@@ -4692,10 +4851,10 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>261</v>
+        <v>60</v>
       </c>
       <c r="B233" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C233" t="s">
         <v>51</v>
@@ -4703,10 +4862,10 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>77</v>
+        <v>245</v>
       </c>
       <c r="B234" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C234" t="s">
         <v>51</v>
@@ -4714,10 +4873,10 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B235" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C235" t="s">
         <v>51</v>
@@ -4725,10 +4884,10 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>416</v>
+        <v>584</v>
       </c>
       <c r="B236" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C236" t="s">
         <v>51</v>
@@ -4736,10 +4895,10 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="B237" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C237" t="s">
         <v>51</v>
@@ -4747,10 +4906,10 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>418</v>
+        <v>62</v>
       </c>
       <c r="B238" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C238" t="s">
         <v>51</v>
@@ -4758,10 +4917,10 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="B239" t="s">
-        <v>301</v>
+        <v>7</v>
       </c>
       <c r="C239" t="s">
         <v>51</v>
@@ -4769,10 +4928,10 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>79</v>
+        <v>404</v>
       </c>
       <c r="B240" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C240" t="s">
         <v>51</v>
@@ -4780,10 +4939,10 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B241" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C241" t="s">
         <v>51</v>
@@ -4791,10 +4950,10 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>81</v>
+        <v>405</v>
       </c>
       <c r="B242" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C242" t="s">
         <v>51</v>
@@ -4802,10 +4961,10 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>420</v>
+        <v>64</v>
       </c>
       <c r="B243" t="s">
-        <v>553</v>
+        <v>16</v>
       </c>
       <c r="C243" t="s">
         <v>51</v>
@@ -4813,10 +4972,10 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>421</v>
+        <v>65</v>
       </c>
       <c r="B244" t="s">
-        <v>553</v>
+        <v>16</v>
       </c>
       <c r="C244" t="s">
         <v>51</v>
@@ -4824,7 +4983,7 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="B245" t="s">
         <v>16</v>
@@ -4835,7 +4994,7 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>422</v>
+        <v>67</v>
       </c>
       <c r="B246" t="s">
         <v>16</v>
@@ -4846,10 +5005,10 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>423</v>
+        <v>68</v>
       </c>
       <c r="B247" t="s">
-        <v>301</v>
+        <v>45</v>
       </c>
       <c r="C247" t="s">
         <v>51</v>
@@ -4857,10 +5016,10 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="B248" t="s">
-        <v>301</v>
+        <v>16</v>
       </c>
       <c r="C248" t="s">
         <v>51</v>
@@ -4868,10 +5027,10 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="B249" t="s">
-        <v>301</v>
+        <v>13</v>
       </c>
       <c r="C249" t="s">
         <v>51</v>
@@ -4879,10 +5038,10 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="B250" t="s">
-        <v>301</v>
+        <v>13</v>
       </c>
       <c r="C250" t="s">
         <v>51</v>
@@ -4890,10 +5049,10 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>83</v>
+        <v>231</v>
       </c>
       <c r="B251" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C251" t="s">
         <v>51</v>
@@ -4901,10 +5060,10 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>427</v>
+        <v>69</v>
       </c>
       <c r="B252" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C252" t="s">
         <v>51</v>
@@ -4912,10 +5071,10 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B253" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C253" t="s">
         <v>51</v>
@@ -4923,10 +5082,10 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="B254" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C254" t="s">
         <v>51</v>
@@ -4934,10 +5093,10 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>428</v>
+        <v>72</v>
       </c>
       <c r="B255" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C255" t="s">
         <v>51</v>
@@ -4945,10 +5104,10 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>429</v>
+        <v>73</v>
       </c>
       <c r="B256" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C256" t="s">
         <v>51</v>
@@ -4956,10 +5115,10 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>430</v>
+        <v>74</v>
       </c>
       <c r="B257" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C257" t="s">
         <v>51</v>
@@ -4967,10 +5126,10 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B258" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C258" t="s">
         <v>51</v>
@@ -4978,10 +5137,10 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>85</v>
+        <v>260</v>
       </c>
       <c r="B259" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="C259" t="s">
         <v>51</v>
@@ -4989,10 +5148,10 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>431</v>
+        <v>409</v>
       </c>
       <c r="B260" t="s">
-        <v>7</v>
+        <v>549</v>
       </c>
       <c r="C260" t="s">
         <v>51</v>
@@ -5000,10 +5159,10 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>432</v>
+        <v>410</v>
       </c>
       <c r="B261" t="s">
-        <v>7</v>
+        <v>298</v>
       </c>
       <c r="C261" t="s">
         <v>51</v>
@@ -5011,10 +5170,10 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="B262" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C262" t="s">
         <v>51</v>
@@ -5022,10 +5181,10 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>434</v>
+        <v>76</v>
       </c>
       <c r="B263" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C263" t="s">
         <v>51</v>
@@ -5033,10 +5192,10 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>87</v>
+        <v>412</v>
       </c>
       <c r="B264" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C264" t="s">
         <v>51</v>
@@ -5044,10 +5203,10 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>88</v>
+        <v>258</v>
       </c>
       <c r="B265" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C265" t="s">
         <v>51</v>
@@ -5055,10 +5214,10 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>435</v>
+        <v>77</v>
       </c>
       <c r="B266" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C266" t="s">
         <v>51</v>
@@ -5066,7 +5225,7 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B267" t="s">
         <v>13</v>
@@ -5077,10 +5236,10 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>436</v>
+        <v>413</v>
       </c>
       <c r="B268" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C268" t="s">
         <v>51</v>
@@ -5088,10 +5247,10 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>437</v>
+        <v>414</v>
       </c>
       <c r="B269" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C269" t="s">
         <v>51</v>
@@ -5099,10 +5258,10 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>90</v>
+        <v>415</v>
       </c>
       <c r="B270" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C270" t="s">
         <v>51</v>
@@ -5110,10 +5269,10 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>438</v>
+        <v>416</v>
       </c>
       <c r="B271" t="s">
-        <v>13</v>
+        <v>298</v>
       </c>
       <c r="C271" t="s">
         <v>51</v>
@@ -5121,10 +5280,10 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>439</v>
+        <v>79</v>
       </c>
       <c r="B272" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C272" t="s">
         <v>51</v>
@@ -5132,10 +5291,10 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B273" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C273" t="s">
         <v>51</v>
@@ -5143,10 +5302,10 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B274" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C274" t="s">
         <v>51</v>
@@ -5154,10 +5313,10 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>440</v>
+        <v>417</v>
       </c>
       <c r="B275" t="s">
-        <v>7</v>
+        <v>549</v>
       </c>
       <c r="C275" t="s">
         <v>51</v>
@@ -5165,10 +5324,10 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>441</v>
+        <v>418</v>
       </c>
       <c r="B276" t="s">
-        <v>7</v>
+        <v>549</v>
       </c>
       <c r="C276" t="s">
         <v>51</v>
@@ -5176,10 +5335,10 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>93</v>
+        <v>585</v>
       </c>
       <c r="B277" t="s">
-        <v>13</v>
+        <v>298</v>
       </c>
       <c r="C277" t="s">
         <v>51</v>
@@ -5187,10 +5346,10 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B278" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C278" t="s">
         <v>51</v>
@@ -5198,10 +5357,10 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>249</v>
+        <v>419</v>
       </c>
       <c r="B279" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C279" t="s">
         <v>51</v>
@@ -5209,10 +5368,10 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>95</v>
+        <v>420</v>
       </c>
       <c r="B280" t="s">
-        <v>13</v>
+        <v>298</v>
       </c>
       <c r="C280" t="s">
         <v>51</v>
@@ -5220,10 +5379,10 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>442</v>
+        <v>421</v>
       </c>
       <c r="B281" t="s">
-        <v>7</v>
+        <v>298</v>
       </c>
       <c r="C281" t="s">
         <v>51</v>
@@ -5231,10 +5390,10 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="B282" t="s">
-        <v>11</v>
+        <v>298</v>
       </c>
       <c r="C282" t="s">
         <v>51</v>
@@ -5242,10 +5401,10 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>96</v>
+        <v>423</v>
       </c>
       <c r="B283" t="s">
-        <v>11</v>
+        <v>298</v>
       </c>
       <c r="C283" t="s">
         <v>51</v>
@@ -5253,10 +5412,10 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>274</v>
+        <v>83</v>
       </c>
       <c r="B284" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C284" t="s">
         <v>51</v>
@@ -5264,10 +5423,10 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="B285" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C285" t="s">
         <v>51</v>
@@ -5275,10 +5434,10 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B286" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C286" t="s">
         <v>51</v>
@@ -5286,10 +5445,10 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>445</v>
+        <v>84</v>
       </c>
       <c r="B287" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C287" t="s">
         <v>51</v>
@@ -5297,10 +5456,10 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>100</v>
+        <v>425</v>
       </c>
       <c r="B288" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C288" t="s">
         <v>51</v>
@@ -5308,10 +5467,10 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>101</v>
+        <v>426</v>
       </c>
       <c r="B289" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C289" t="s">
         <v>51</v>
@@ -5319,10 +5478,10 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>102</v>
+        <v>427</v>
       </c>
       <c r="B290" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C290" t="s">
         <v>51</v>
@@ -5330,10 +5489,10 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="B291" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C291" t="s">
         <v>51</v>
@@ -5341,10 +5500,10 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>446</v>
+        <v>85</v>
       </c>
       <c r="B292" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="C292" t="s">
         <v>51</v>
@@ -5352,10 +5511,10 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="B293" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C293" t="s">
         <v>51</v>
@@ -5363,10 +5522,10 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>104</v>
+        <v>429</v>
       </c>
       <c r="B294" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C294" t="s">
         <v>51</v>
@@ -5374,461 +5533,461 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>254</v>
+        <v>430</v>
       </c>
       <c r="B295" t="s">
-        <v>231</v>
+        <v>7</v>
       </c>
       <c r="C295" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="B296" t="s">
-        <v>231</v>
+        <v>7</v>
       </c>
       <c r="C296" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="B297" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="C297" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="B298" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="C298" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="B299" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C299" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>450</v>
+        <v>89</v>
       </c>
       <c r="B300" t="s">
         <v>13</v>
       </c>
       <c r="C300" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="B301" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C301" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="B302" t="s">
         <v>13</v>
       </c>
       <c r="C302" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>453</v>
+        <v>90</v>
       </c>
       <c r="B303" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C303" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="B304" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C304" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>455</v>
+        <v>586</v>
       </c>
       <c r="B305" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C305" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="B306" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C306" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>457</v>
+        <v>91</v>
       </c>
       <c r="B307" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C307" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>458</v>
+        <v>92</v>
       </c>
       <c r="B308" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C308" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>459</v>
+        <v>437</v>
       </c>
       <c r="B309" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C309" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>396</v>
+        <v>438</v>
       </c>
       <c r="B310" t="s">
         <v>7</v>
       </c>
       <c r="C310" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>460</v>
+        <v>93</v>
       </c>
       <c r="B311" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C311" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="B312" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C312" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>110</v>
+        <v>246</v>
       </c>
       <c r="B313" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C313" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B314" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C314" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>112</v>
+        <v>439</v>
       </c>
       <c r="B315" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C315" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>461</v>
+        <v>440</v>
       </c>
       <c r="B316" t="s">
-        <v>231</v>
+        <v>11</v>
       </c>
       <c r="C316" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>113</v>
+        <v>587</v>
       </c>
       <c r="B317" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C317" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="B318" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C318" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B319" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C319" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>115</v>
+        <v>588</v>
       </c>
       <c r="B320" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C320" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>116</v>
+        <v>441</v>
       </c>
       <c r="B321" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C321" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>268</v>
+        <v>589</v>
       </c>
       <c r="B322" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C322" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>269</v>
+        <v>97</v>
       </c>
       <c r="B323" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C323" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>117</v>
+        <v>590</v>
       </c>
       <c r="B324" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C324" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>462</v>
+        <v>442</v>
       </c>
       <c r="B325" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C325" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="B326" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C326" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>463</v>
+        <v>591</v>
       </c>
       <c r="B327" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C327" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B328" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C328" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="B329" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C329" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="B330" t="s">
         <v>16</v>
       </c>
       <c r="C330" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>122</v>
+        <v>443</v>
       </c>
       <c r="B331" t="s">
         <v>16</v>
       </c>
       <c r="C331" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="B332" t="s">
         <v>16</v>
       </c>
       <c r="C332" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>465</v>
+        <v>104</v>
       </c>
       <c r="B333" t="s">
-        <v>301</v>
+        <v>13</v>
       </c>
       <c r="C333" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>466</v>
+        <v>241</v>
       </c>
       <c r="B334" t="s">
         <v>13</v>
       </c>
       <c r="C334" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>467</v>
+        <v>592</v>
       </c>
       <c r="B335" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C335" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>123</v>
+        <v>251</v>
       </c>
       <c r="B336" t="s">
-        <v>54</v>
+        <v>230</v>
       </c>
       <c r="C336" t="s">
         <v>107</v>
@@ -5836,10 +5995,10 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>468</v>
+        <v>445</v>
       </c>
       <c r="B337" t="s">
-        <v>54</v>
+        <v>230</v>
       </c>
       <c r="C337" t="s">
         <v>107</v>
@@ -5847,10 +6006,10 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="B338" t="s">
-        <v>7</v>
+        <v>106</v>
       </c>
       <c r="C338" t="s">
         <v>107</v>
@@ -5858,10 +6017,10 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>469</v>
+        <v>108</v>
       </c>
       <c r="B339" t="s">
-        <v>7</v>
+        <v>106</v>
       </c>
       <c r="C339" t="s">
         <v>107</v>
@@ -5869,10 +6028,10 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>125</v>
+        <v>446</v>
       </c>
       <c r="B340" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C340" t="s">
         <v>107</v>
@@ -5880,10 +6039,10 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>470</v>
+        <v>447</v>
       </c>
       <c r="B341" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C341" t="s">
         <v>107</v>
@@ -5891,10 +6050,10 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>126</v>
+        <v>448</v>
       </c>
       <c r="B342" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C342" t="s">
         <v>107</v>
@@ -5902,10 +6061,10 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>127</v>
+        <v>449</v>
       </c>
       <c r="B343" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C343" t="s">
         <v>107</v>
@@ -5913,10 +6072,10 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>128</v>
+        <v>450</v>
       </c>
       <c r="B344" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C344" t="s">
         <v>107</v>
@@ -5924,10 +6083,10 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>129</v>
+        <v>451</v>
       </c>
       <c r="B345" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C345" t="s">
         <v>107</v>
@@ -5935,10 +6094,10 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>130</v>
+        <v>452</v>
       </c>
       <c r="B346" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C346" t="s">
         <v>107</v>
@@ -5946,10 +6105,10 @@
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>131</v>
+        <v>453</v>
       </c>
       <c r="B347" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C347" t="s">
         <v>107</v>
@@ -5957,10 +6116,10 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>471</v>
+        <v>454</v>
       </c>
       <c r="B348" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C348" t="s">
         <v>107</v>
@@ -5968,10 +6127,10 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>472</v>
+        <v>455</v>
       </c>
       <c r="B349" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="C349" t="s">
         <v>107</v>
@@ -5979,10 +6138,10 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>132</v>
+        <v>456</v>
       </c>
       <c r="B350" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="C350" t="s">
         <v>107</v>
@@ -5990,7 +6149,7 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>133</v>
+        <v>393</v>
       </c>
       <c r="B351" t="s">
         <v>7</v>
@@ -6001,7 +6160,7 @@
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>134</v>
+        <v>457</v>
       </c>
       <c r="B352" t="s">
         <v>7</v>
@@ -6012,10 +6171,10 @@
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="B353" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C353" t="s">
         <v>107</v>
@@ -6023,10 +6182,10 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="B354" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C354" t="s">
         <v>107</v>
@@ -6034,10 +6193,10 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="B355" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C355" t="s">
         <v>107</v>
@@ -6045,10 +6204,10 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="B356" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C356" t="s">
         <v>107</v>
@@ -6056,10 +6215,10 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>139</v>
+        <v>458</v>
       </c>
       <c r="B357" t="s">
-        <v>7</v>
+        <v>230</v>
       </c>
       <c r="C357" t="s">
         <v>107</v>
@@ -6067,10 +6226,10 @@
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="B358" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C358" t="s">
         <v>107</v>
@@ -6078,10 +6237,10 @@
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="B359" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C359" t="s">
         <v>107</v>
@@ -6089,10 +6248,10 @@
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>142</v>
+        <v>264</v>
       </c>
       <c r="B360" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C360" t="s">
         <v>107</v>
@@ -6100,10 +6259,10 @@
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="B361" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C361" t="s">
         <v>107</v>
@@ -6111,21 +6270,21 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="B362" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C362" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A363" t="s">
-        <v>145</v>
+      <c r="A363" s="4" t="s">
+        <v>265</v>
       </c>
       <c r="B363" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C363" t="s">
         <v>107</v>
@@ -6133,10 +6292,10 @@
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>146</v>
+        <v>266</v>
       </c>
       <c r="B364" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C364" t="s">
         <v>107</v>
@@ -6144,10 +6303,10 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="B365" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C365" t="s">
         <v>107</v>
@@ -6155,10 +6314,10 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>148</v>
+        <v>459</v>
       </c>
       <c r="B366" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C366" t="s">
         <v>107</v>
@@ -6166,10 +6325,10 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="B367" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C367" t="s">
         <v>107</v>
@@ -6177,10 +6336,10 @@
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>150</v>
+        <v>460</v>
       </c>
       <c r="B368" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C368" t="s">
         <v>107</v>
@@ -6188,10 +6347,10 @@
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="B369" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C369" t="s">
         <v>107</v>
@@ -6199,10 +6358,10 @@
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="B370" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C370" t="s">
         <v>107</v>
@@ -6210,10 +6369,10 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="B371" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C371" t="s">
         <v>107</v>
@@ -6221,10 +6380,10 @@
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="B372" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C372" t="s">
         <v>107</v>
@@ -6232,10 +6391,10 @@
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>154</v>
+        <v>461</v>
       </c>
       <c r="B373" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C373" t="s">
         <v>107</v>
@@ -6243,10 +6402,10 @@
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>155</v>
+        <v>462</v>
       </c>
       <c r="B374" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C374" t="s">
         <v>107</v>
@@ -6254,10 +6413,10 @@
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>156</v>
+        <v>463</v>
       </c>
       <c r="B375" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="C375" t="s">
         <v>107</v>
@@ -6265,10 +6424,10 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="B376" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C376" t="s">
         <v>107</v>
@@ -6276,10 +6435,10 @@
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>232</v>
+        <v>464</v>
       </c>
       <c r="B377" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="C377" t="s">
         <v>107</v>
@@ -6287,10 +6446,10 @@
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>473</v>
+        <v>124</v>
       </c>
       <c r="B378" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C378" t="s">
         <v>107</v>
@@ -6298,10 +6457,10 @@
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>158</v>
+        <v>465</v>
       </c>
       <c r="B379" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C379" t="s">
         <v>107</v>
@@ -6309,10 +6468,10 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>158</v>
+        <v>593</v>
       </c>
       <c r="B380" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C380" t="s">
         <v>107</v>
@@ -6320,10 +6479,10 @@
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>159</v>
+        <v>594</v>
       </c>
       <c r="B381" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C381" t="s">
         <v>107</v>
@@ -6331,10 +6490,10 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>160</v>
+        <v>466</v>
       </c>
       <c r="B382" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C382" t="s">
         <v>107</v>
@@ -6342,10 +6501,10 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="B383" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C383" t="s">
         <v>107</v>
@@ -6353,10 +6512,10 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="B384" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C384" t="s">
         <v>107</v>
@@ -6364,10 +6523,10 @@
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="B385" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C385" t="s">
         <v>107</v>
@@ -6375,10 +6534,10 @@
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="B386" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C386" t="s">
         <v>107</v>
@@ -6386,10 +6545,10 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="B387" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C387" t="s">
         <v>107</v>
@@ -6397,10 +6556,10 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="B388" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C388" t="s">
         <v>107</v>
@@ -6408,10 +6567,10 @@
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>167</v>
+        <v>467</v>
       </c>
       <c r="B389" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C389" t="s">
         <v>107</v>
@@ -6419,10 +6578,10 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>168</v>
+        <v>468</v>
       </c>
       <c r="B390" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C390" t="s">
         <v>107</v>
@@ -6430,10 +6589,10 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="B391" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C391" t="s">
         <v>107</v>
@@ -6441,10 +6600,10 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="B392" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C392" t="s">
         <v>107</v>
@@ -6452,10 +6611,10 @@
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>171</v>
+        <v>133</v>
       </c>
       <c r="B393" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C393" t="s">
         <v>107</v>
@@ -6463,10 +6622,10 @@
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="B394" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C394" t="s">
         <v>107</v>
@@ -6474,10 +6633,10 @@
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="B395" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C395" t="s">
         <v>107</v>
@@ -6485,10 +6644,10 @@
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="B396" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C396" t="s">
         <v>107</v>
@@ -6496,10 +6655,10 @@
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>474</v>
+        <v>137</v>
       </c>
       <c r="B397" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C397" t="s">
         <v>107</v>
@@ -6507,10 +6666,10 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>475</v>
+        <v>138</v>
       </c>
       <c r="B398" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C398" t="s">
         <v>107</v>
@@ -6518,10 +6677,10 @@
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>476</v>
+        <v>139</v>
       </c>
       <c r="B399" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C399" t="s">
         <v>107</v>
@@ -6529,10 +6688,10 @@
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="B400" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C400" t="s">
         <v>107</v>
@@ -6540,10 +6699,10 @@
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="B401" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C401" t="s">
         <v>107</v>
@@ -6551,10 +6710,10 @@
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>477</v>
+        <v>142</v>
       </c>
       <c r="B402" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C402" t="s">
         <v>107</v>
@@ -6562,10 +6721,10 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>478</v>
+        <v>143</v>
       </c>
       <c r="B403" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C403" t="s">
         <v>107</v>
@@ -6573,10 +6732,10 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>479</v>
+        <v>144</v>
       </c>
       <c r="B404" t="s">
-        <v>480</v>
+        <v>7</v>
       </c>
       <c r="C404" t="s">
         <v>107</v>
@@ -6584,10 +6743,10 @@
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>481</v>
+        <v>145</v>
       </c>
       <c r="B405" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C405" t="s">
         <v>107</v>
@@ -6595,10 +6754,10 @@
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>482</v>
+        <v>146</v>
       </c>
       <c r="B406" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C406" t="s">
         <v>107</v>
@@ -6606,10 +6765,10 @@
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>483</v>
+        <v>147</v>
       </c>
       <c r="B407" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C407" t="s">
         <v>107</v>
@@ -6617,10 +6776,10 @@
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>484</v>
+        <v>148</v>
       </c>
       <c r="B408" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C408" t="s">
         <v>107</v>
@@ -6628,10 +6787,10 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="B409" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C409" t="s">
         <v>107</v>
@@ -6639,10 +6798,10 @@
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>256</v>
+        <v>150</v>
       </c>
       <c r="B410" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C410" t="s">
         <v>107</v>
@@ -6650,10 +6809,10 @@
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>178</v>
+        <v>595</v>
       </c>
       <c r="B411" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C411" t="s">
         <v>107</v>
@@ -6661,10 +6820,10 @@
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="B412" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C412" t="s">
         <v>107</v>
@@ -6672,10 +6831,10 @@
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="B413" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C413" t="s">
         <v>107</v>
@@ -6683,10 +6842,10 @@
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="B414" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C414" t="s">
         <v>107</v>
@@ -6694,10 +6853,10 @@
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="B415" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C415" t="s">
         <v>107</v>
@@ -6705,10 +6864,10 @@
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>554</v>
+        <v>154</v>
       </c>
       <c r="B416" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C416" t="s">
         <v>107</v>
@@ -6716,7 +6875,7 @@
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>485</v>
+        <v>155</v>
       </c>
       <c r="B417" t="s">
         <v>45</v>
@@ -6727,7 +6886,7 @@
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="B418" t="s">
         <v>45</v>
@@ -6738,10 +6897,10 @@
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>486</v>
+        <v>231</v>
       </c>
       <c r="B419" t="s">
-        <v>553</v>
+        <v>7</v>
       </c>
       <c r="C419" t="s">
         <v>107</v>
@@ -6749,10 +6908,10 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="B420" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C420" t="s">
         <v>107</v>
@@ -6760,10 +6919,10 @@
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>488</v>
+        <v>157</v>
       </c>
       <c r="B421" t="s">
-        <v>553</v>
+        <v>16</v>
       </c>
       <c r="C421" t="s">
         <v>107</v>
@@ -6771,10 +6930,10 @@
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>489</v>
+        <v>157</v>
       </c>
       <c r="B422" t="s">
-        <v>301</v>
+        <v>16</v>
       </c>
       <c r="C422" t="s">
         <v>107</v>
@@ -6782,7 +6941,7 @@
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="B423" t="s">
         <v>16</v>
@@ -6793,7 +6952,7 @@
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="B424" t="s">
         <v>16</v>
@@ -6804,7 +6963,7 @@
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="B425" t="s">
         <v>16</v>
@@ -6815,7 +6974,7 @@
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="B426" t="s">
         <v>16</v>
@@ -6826,7 +6985,7 @@
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="B427" t="s">
         <v>16</v>
@@ -6837,7 +6996,7 @@
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="B428" t="s">
         <v>16</v>
@@ -6848,7 +7007,7 @@
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="B429" t="s">
         <v>16</v>
@@ -6859,7 +7018,7 @@
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="B430" t="s">
         <v>16</v>
@@ -6870,10 +7029,10 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="B431" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C431" t="s">
         <v>107</v>
@@ -6881,10 +7040,10 @@
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="B432" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C432" t="s">
         <v>107</v>
@@ -6892,10 +7051,10 @@
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="B433" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C433" t="s">
         <v>107</v>
@@ -6903,10 +7062,10 @@
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>490</v>
+        <v>169</v>
       </c>
       <c r="B434" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C434" t="s">
         <v>107</v>
@@ -6914,10 +7073,10 @@
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="B435" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C435" t="s">
         <v>107</v>
@@ -6925,10 +7084,10 @@
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="B436" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C436" t="s">
         <v>107</v>
@@ -6936,10 +7095,10 @@
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>491</v>
+        <v>172</v>
       </c>
       <c r="B437" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C437" t="s">
         <v>107</v>
@@ -6947,10 +7106,10 @@
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>492</v>
+        <v>173</v>
       </c>
       <c r="B438" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C438" t="s">
         <v>107</v>
@@ -6958,10 +7117,10 @@
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="B439" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C439" t="s">
         <v>107</v>
@@ -6969,10 +7128,10 @@
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>494</v>
+        <v>471</v>
       </c>
       <c r="B440" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C440" t="s">
         <v>107</v>
@@ -6980,10 +7139,10 @@
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>234</v>
+        <v>472</v>
       </c>
       <c r="B441" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C441" t="s">
         <v>107</v>
@@ -6991,10 +7150,10 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>233</v>
+        <v>174</v>
       </c>
       <c r="B442" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C442" t="s">
         <v>107</v>
@@ -7002,10 +7161,10 @@
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="B443" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C443" t="s">
         <v>107</v>
@@ -7013,10 +7172,10 @@
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>197</v>
+        <v>473</v>
       </c>
       <c r="B444" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C444" t="s">
         <v>107</v>
@@ -7024,10 +7183,10 @@
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>198</v>
+        <v>474</v>
       </c>
       <c r="B445" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C445" t="s">
         <v>107</v>
@@ -7035,10 +7194,10 @@
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>199</v>
+        <v>475</v>
       </c>
       <c r="B446" t="s">
-        <v>13</v>
+        <v>476</v>
       </c>
       <c r="C446" t="s">
         <v>107</v>
@@ -7046,10 +7205,10 @@
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>200</v>
+        <v>477</v>
       </c>
       <c r="B447" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C447" t="s">
         <v>107</v>
@@ -7057,10 +7216,10 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>201</v>
+        <v>478</v>
       </c>
       <c r="B448" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C448" t="s">
         <v>107</v>
@@ -7068,7 +7227,7 @@
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="B449" t="s">
         <v>13</v>
@@ -7079,10 +7238,10 @@
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>202</v>
+        <v>480</v>
       </c>
       <c r="B450" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C450" t="s">
         <v>107</v>
@@ -7090,10 +7249,10 @@
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>496</v>
+        <v>176</v>
       </c>
       <c r="B451" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C451" t="s">
         <v>107</v>
@@ -7101,10 +7260,10 @@
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>203</v>
+        <v>253</v>
       </c>
       <c r="B452" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C452" t="s">
         <v>107</v>
@@ -7112,10 +7271,10 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>497</v>
+        <v>177</v>
       </c>
       <c r="B453" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C453" t="s">
         <v>107</v>
@@ -7123,10 +7282,10 @@
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>498</v>
+        <v>178</v>
       </c>
       <c r="B454" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C454" t="s">
         <v>107</v>
@@ -7134,10 +7293,10 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>499</v>
+        <v>179</v>
       </c>
       <c r="B455" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="C455" t="s">
         <v>107</v>
@@ -7145,10 +7304,10 @@
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="B456" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C456" t="s">
         <v>107</v>
@@ -7156,10 +7315,10 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="B457" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C457" t="s">
         <v>107</v>
@@ -7167,10 +7326,10 @@
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>206</v>
+        <v>550</v>
       </c>
       <c r="B458" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C458" t="s">
         <v>107</v>
@@ -7178,10 +7337,10 @@
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>207</v>
+        <v>481</v>
       </c>
       <c r="B459" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C459" t="s">
         <v>107</v>
@@ -7189,10 +7348,10 @@
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="B460" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C460" t="s">
         <v>107</v>
@@ -7200,10 +7359,10 @@
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>209</v>
+        <v>482</v>
       </c>
       <c r="B461" t="s">
-        <v>11</v>
+        <v>549</v>
       </c>
       <c r="C461" t="s">
         <v>107</v>
@@ -7211,10 +7370,10 @@
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>210</v>
+        <v>483</v>
       </c>
       <c r="B462" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C462" t="s">
         <v>107</v>
@@ -7222,10 +7381,10 @@
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>276</v>
+        <v>484</v>
       </c>
       <c r="B463" t="s">
-        <v>11</v>
+        <v>549</v>
       </c>
       <c r="C463" t="s">
         <v>107</v>
@@ -7233,10 +7392,10 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="B464" t="s">
-        <v>11</v>
+        <v>298</v>
       </c>
       <c r="C464" t="s">
         <v>107</v>
@@ -7244,10 +7403,10 @@
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>501</v>
+        <v>183</v>
       </c>
       <c r="B465" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C465" t="s">
         <v>107</v>
@@ -7255,10 +7414,10 @@
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>502</v>
+        <v>184</v>
       </c>
       <c r="B466" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C466" t="s">
         <v>107</v>
@@ -7266,10 +7425,10 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="B467" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C467" t="s">
         <v>107</v>
@@ -7277,10 +7436,10 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="B468" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C468" t="s">
         <v>107</v>
@@ -7288,10 +7447,10 @@
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="B469" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C469" t="s">
         <v>107</v>
@@ -7299,10 +7458,10 @@
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="B470" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C470" t="s">
         <v>107</v>
@@ -7310,10 +7469,10 @@
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>503</v>
+        <v>188</v>
       </c>
       <c r="B471" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C471" t="s">
         <v>107</v>
@@ -7321,10 +7480,10 @@
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="B472" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C472" t="s">
         <v>107</v>
@@ -7332,10 +7491,10 @@
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="B473" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C473" t="s">
         <v>107</v>
@@ -7343,10 +7502,10 @@
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="B474" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C474" t="s">
         <v>107</v>
@@ -7354,10 +7513,10 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="B475" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C475" t="s">
         <v>107</v>
@@ -7365,10 +7524,10 @@
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>219</v>
+        <v>486</v>
       </c>
       <c r="B476" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C476" t="s">
         <v>107</v>
@@ -7376,10 +7535,10 @@
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>220</v>
+        <v>193</v>
       </c>
       <c r="B477" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C477" t="s">
         <v>107</v>
@@ -7387,10 +7546,10 @@
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="B478" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C478" t="s">
         <v>107</v>
@@ -7398,10 +7557,10 @@
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="B479" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C479" t="s">
         <v>107</v>
@@ -7409,10 +7568,10 @@
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="B480" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C480" t="s">
         <v>107</v>
@@ -7420,10 +7579,10 @@
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
       <c r="B481" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C481" t="s">
         <v>107</v>
@@ -7431,10 +7590,10 @@
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
       <c r="B482" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C482" t="s">
         <v>107</v>
@@ -7442,10 +7601,10 @@
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>508</v>
+        <v>233</v>
       </c>
       <c r="B483" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C483" t="s">
         <v>107</v>
@@ -7453,10 +7612,10 @@
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>509</v>
+        <v>232</v>
       </c>
       <c r="B484" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C484" t="s">
         <v>107</v>
@@ -7464,10 +7623,10 @@
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>510</v>
+        <v>596</v>
       </c>
       <c r="B485" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C485" t="s">
         <v>107</v>
@@ -7475,10 +7634,10 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="B486" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C486" t="s">
         <v>107</v>
@@ -7486,7 +7645,7 @@
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>242</v>
+        <v>196</v>
       </c>
       <c r="B487" t="s">
         <v>13</v>
@@ -7497,574 +7656,1179 @@
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="B488" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C488" t="s">
-        <v>224</v>
+        <v>107</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="B489" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C489" t="s">
-        <v>224</v>
+        <v>107</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="B490" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C490" t="s">
-        <v>224</v>
+        <v>107</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>227</v>
+        <v>597</v>
       </c>
       <c r="B491" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C491" t="s">
-        <v>224</v>
+        <v>107</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="B492" t="s">
         <v>13</v>
       </c>
       <c r="C492" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>229</v>
+        <v>491</v>
       </c>
       <c r="B493" t="s">
         <v>13</v>
       </c>
       <c r="C493" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="B494" t="s">
-        <v>231</v>
+        <v>13</v>
       </c>
       <c r="C494" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>272</v>
+        <v>492</v>
       </c>
       <c r="B495" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C495" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>273</v>
+        <v>202</v>
       </c>
       <c r="B496" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C496" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>98</v>
+        <v>493</v>
       </c>
       <c r="B497" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C497" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>251</v>
+        <v>494</v>
       </c>
       <c r="B498" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C498" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>252</v>
+        <v>495</v>
       </c>
       <c r="B499" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C499" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>511</v>
+        <v>203</v>
       </c>
       <c r="B500" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="C500" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>513</v>
+        <v>204</v>
       </c>
       <c r="B501" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C501" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>514</v>
+        <v>205</v>
       </c>
       <c r="B502" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="C502" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>515</v>
+        <v>598</v>
       </c>
       <c r="B503" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="C503" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>516</v>
+        <v>206</v>
       </c>
       <c r="B504" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C504" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>517</v>
+        <v>207</v>
       </c>
       <c r="B505" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C505" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>518</v>
+        <v>599</v>
       </c>
       <c r="B506" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C506" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>519</v>
+        <v>208</v>
       </c>
       <c r="B507" t="s">
-        <v>480</v>
+        <v>11</v>
       </c>
       <c r="C507" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>520</v>
+        <v>209</v>
       </c>
       <c r="B508" t="s">
-        <v>480</v>
+        <v>11</v>
       </c>
       <c r="C508" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>521</v>
+        <v>273</v>
       </c>
       <c r="B509" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C509" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>522</v>
+        <v>496</v>
       </c>
       <c r="B510" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C510" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="B511" t="s">
-        <v>480</v>
+        <v>11</v>
       </c>
       <c r="C511" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>524</v>
+        <v>498</v>
       </c>
       <c r="B512" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C512" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>525</v>
+        <v>441</v>
       </c>
       <c r="B513" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C513" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>526</v>
+        <v>600</v>
       </c>
       <c r="B514" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C514" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>527</v>
+        <v>210</v>
       </c>
       <c r="B515" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C515" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>528</v>
+        <v>601</v>
       </c>
       <c r="B516" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C516" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>529</v>
+        <v>211</v>
       </c>
       <c r="B517" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C517" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>530</v>
+        <v>212</v>
       </c>
       <c r="B518" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C518" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>531</v>
+        <v>213</v>
       </c>
       <c r="B519" t="s">
         <v>11</v>
       </c>
       <c r="C519" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>532</v>
+        <v>602</v>
       </c>
       <c r="B520" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C520" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>533</v>
+        <v>603</v>
       </c>
       <c r="B521" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C521" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
       <c r="B522" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C522" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>534</v>
+        <v>214</v>
       </c>
       <c r="B523" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C523" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>535</v>
+        <v>215</v>
       </c>
       <c r="B524" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C524" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>536</v>
+        <v>216</v>
       </c>
       <c r="B525" t="s">
         <v>45</v>
       </c>
       <c r="C525" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>537</v>
+        <v>217</v>
       </c>
       <c r="B526" t="s">
         <v>45</v>
       </c>
       <c r="C526" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>538</v>
+        <v>218</v>
       </c>
       <c r="B527" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C527" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>539</v>
+        <v>219</v>
       </c>
       <c r="B528" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="C528" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>540</v>
+        <v>220</v>
       </c>
       <c r="B529" t="s">
-        <v>553</v>
+        <v>45</v>
       </c>
       <c r="C529" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>541</v>
+        <v>500</v>
       </c>
       <c r="B530" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="C530" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>542</v>
+        <v>501</v>
       </c>
       <c r="B531" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C531" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>543</v>
+        <v>502</v>
       </c>
       <c r="B532" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C532" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>544</v>
+        <v>503</v>
       </c>
       <c r="B533" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C533" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>545</v>
+        <v>504</v>
       </c>
       <c r="B534" t="s">
-        <v>301</v>
+        <v>16</v>
       </c>
       <c r="C534" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>546</v>
+        <v>505</v>
       </c>
       <c r="B535" t="s">
-        <v>547</v>
+        <v>16</v>
       </c>
       <c r="C535" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>548</v>
+        <v>506</v>
       </c>
       <c r="B536" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C536" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>549</v>
+        <v>221</v>
       </c>
       <c r="B537" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C537" t="s">
-        <v>512</v>
+        <v>107</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>550</v>
+        <v>222</v>
       </c>
       <c r="B538" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C538" t="s">
-        <v>512</v>
+        <v>223</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>551</v>
+        <v>224</v>
       </c>
       <c r="B539" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C539" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A540" t="s">
+        <v>225</v>
+      </c>
+      <c r="B540" t="s">
+        <v>4</v>
+      </c>
+      <c r="C540" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A541" t="s">
+        <v>226</v>
+      </c>
+      <c r="B541" t="s">
+        <v>11</v>
+      </c>
+      <c r="C541" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A542" t="s">
+        <v>604</v>
+      </c>
+      <c r="B542" t="s">
+        <v>11</v>
+      </c>
+      <c r="C542" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A543" t="s">
+        <v>226</v>
+      </c>
+      <c r="B543" t="s">
+        <v>11</v>
+      </c>
+      <c r="C543" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A544" t="s">
+        <v>227</v>
+      </c>
+      <c r="B544" t="s">
+        <v>13</v>
+      </c>
+      <c r="C544" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A545" t="s">
+        <v>228</v>
+      </c>
+      <c r="B545" t="s">
+        <v>13</v>
+      </c>
+      <c r="C545" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A546" t="s">
+        <v>229</v>
+      </c>
+      <c r="B546" t="s">
+        <v>230</v>
+      </c>
+      <c r="C546" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A547" t="s">
+        <v>269</v>
+      </c>
+      <c r="B547" t="s">
+        <v>11</v>
+      </c>
+      <c r="C547" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A548" t="s">
+        <v>606</v>
+      </c>
+      <c r="B548" t="s">
+        <v>11</v>
+      </c>
+      <c r="C548" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A549" t="s">
+        <v>270</v>
+      </c>
+      <c r="B549" t="s">
+        <v>11</v>
+      </c>
+      <c r="C549" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A550" t="s">
+        <v>98</v>
+      </c>
+      <c r="B550" t="s">
+        <v>11</v>
+      </c>
+      <c r="C550" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A551" t="s">
+        <v>98</v>
+      </c>
+      <c r="B551" t="s">
+        <v>11</v>
+      </c>
+      <c r="C551" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A552" t="s">
+        <v>248</v>
+      </c>
+      <c r="B552" t="s">
+        <v>45</v>
+      </c>
+      <c r="C552" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A553" t="s">
+        <v>249</v>
+      </c>
+      <c r="B553" t="s">
+        <v>45</v>
+      </c>
+      <c r="C553" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A554" t="s">
+        <v>507</v>
+      </c>
+      <c r="B554" t="s">
+        <v>45</v>
+      </c>
+      <c r="C554" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A555" t="s">
+        <v>509</v>
+      </c>
+      <c r="B555" t="s">
+        <v>54</v>
+      </c>
+      <c r="C555" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A556" t="s">
+        <v>510</v>
+      </c>
+      <c r="B556" t="s">
+        <v>45</v>
+      </c>
+      <c r="C556" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A557" t="s">
+        <v>511</v>
+      </c>
+      <c r="B557" t="s">
+        <v>45</v>
+      </c>
+      <c r="C557" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A558" t="s">
         <v>512</v>
+      </c>
+      <c r="B558" t="s">
+        <v>13</v>
+      </c>
+      <c r="C558" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A559" t="s">
+        <v>513</v>
+      </c>
+      <c r="B559" t="s">
+        <v>13</v>
+      </c>
+      <c r="C559" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A560" t="s">
+        <v>514</v>
+      </c>
+      <c r="B560" t="s">
+        <v>13</v>
+      </c>
+      <c r="C560" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A561" t="s">
+        <v>515</v>
+      </c>
+      <c r="B561" t="s">
+        <v>476</v>
+      </c>
+      <c r="C561" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A562" t="s">
+        <v>516</v>
+      </c>
+      <c r="B562" t="s">
+        <v>476</v>
+      </c>
+      <c r="C562" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A563" t="s">
+        <v>517</v>
+      </c>
+      <c r="B563" t="s">
+        <v>7</v>
+      </c>
+      <c r="C563" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A564" t="s">
+        <v>518</v>
+      </c>
+      <c r="B564" t="s">
+        <v>4</v>
+      </c>
+      <c r="C564" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A565" t="s">
+        <v>519</v>
+      </c>
+      <c r="B565" t="s">
+        <v>476</v>
+      </c>
+      <c r="C565" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A566" t="s">
+        <v>520</v>
+      </c>
+      <c r="B566" t="s">
+        <v>54</v>
+      </c>
+      <c r="C566" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A567" t="s">
+        <v>521</v>
+      </c>
+      <c r="B567" t="s">
+        <v>54</v>
+      </c>
+      <c r="C567" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A568" t="s">
+        <v>522</v>
+      </c>
+      <c r="B568" t="s">
+        <v>16</v>
+      </c>
+      <c r="C568" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A569" t="s">
+        <v>523</v>
+      </c>
+      <c r="B569" t="s">
+        <v>16</v>
+      </c>
+      <c r="C569" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A570" t="s">
+        <v>524</v>
+      </c>
+      <c r="B570" t="s">
+        <v>13</v>
+      </c>
+      <c r="C570" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A571" t="s">
+        <v>525</v>
+      </c>
+      <c r="B571" t="s">
+        <v>7</v>
+      </c>
+      <c r="C571" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A572" t="s">
+        <v>526</v>
+      </c>
+      <c r="B572" t="s">
+        <v>7</v>
+      </c>
+      <c r="C572" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A573" t="s">
+        <v>607</v>
+      </c>
+      <c r="B573" t="s">
+        <v>7</v>
+      </c>
+      <c r="C573" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A574" t="s">
+        <v>527</v>
+      </c>
+      <c r="B574" t="s">
+        <v>11</v>
+      </c>
+      <c r="C574" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A575" t="s">
+        <v>528</v>
+      </c>
+      <c r="B575" t="s">
+        <v>16</v>
+      </c>
+      <c r="C575" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A576" t="s">
+        <v>529</v>
+      </c>
+      <c r="B576" t="s">
+        <v>16</v>
+      </c>
+      <c r="C576" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A577" t="s">
+        <v>530</v>
+      </c>
+      <c r="B577" t="s">
+        <v>54</v>
+      </c>
+      <c r="C577" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A578" t="s">
+        <v>530</v>
+      </c>
+      <c r="B578" t="s">
+        <v>54</v>
+      </c>
+      <c r="C578" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A579" t="s">
+        <v>531</v>
+      </c>
+      <c r="B579" t="s">
+        <v>16</v>
+      </c>
+      <c r="C579" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A580" t="s">
+        <v>532</v>
+      </c>
+      <c r="B580" t="s">
+        <v>45</v>
+      </c>
+      <c r="C580" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A581" t="s">
+        <v>533</v>
+      </c>
+      <c r="B581" t="s">
+        <v>45</v>
+      </c>
+      <c r="C581" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A582" t="s">
+        <v>534</v>
+      </c>
+      <c r="B582" t="s">
+        <v>16</v>
+      </c>
+      <c r="C582" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A583" t="s">
+        <v>535</v>
+      </c>
+      <c r="B583" t="s">
+        <v>230</v>
+      </c>
+      <c r="C583" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A584" t="s">
+        <v>536</v>
+      </c>
+      <c r="B584" t="s">
+        <v>549</v>
+      </c>
+      <c r="C584" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A585" t="s">
+        <v>537</v>
+      </c>
+      <c r="B585" t="s">
+        <v>106</v>
+      </c>
+      <c r="C585" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A586" t="s">
+        <v>538</v>
+      </c>
+      <c r="B586" t="s">
+        <v>4</v>
+      </c>
+      <c r="C586" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A587" t="s">
+        <v>539</v>
+      </c>
+      <c r="B587" t="s">
+        <v>13</v>
+      </c>
+      <c r="C587" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A588" t="s">
+        <v>540</v>
+      </c>
+      <c r="B588" t="s">
+        <v>11</v>
+      </c>
+      <c r="C588" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A589" t="s">
+        <v>541</v>
+      </c>
+      <c r="B589" t="s">
+        <v>298</v>
+      </c>
+      <c r="C589" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A590" t="s">
+        <v>542</v>
+      </c>
+      <c r="B590" t="s">
+        <v>543</v>
+      </c>
+      <c r="C590" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A591" t="s">
+        <v>544</v>
+      </c>
+      <c r="B591" t="s">
+        <v>13</v>
+      </c>
+      <c r="C591" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A592" t="s">
+        <v>545</v>
+      </c>
+      <c r="B592" t="s">
+        <v>13</v>
+      </c>
+      <c r="C592" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A593" t="s">
+        <v>546</v>
+      </c>
+      <c r="B593" t="s">
+        <v>13</v>
+      </c>
+      <c r="C593" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A594" t="s">
+        <v>547</v>
+      </c>
+      <c r="B594" t="s">
+        <v>13</v>
+      </c>
+      <c r="C594" t="s">
+        <v>508</v>
       </c>
     </row>
   </sheetData>

--- a/Vehicle Catalogue.xlsx
+++ b/Vehicle Catalogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samhi\Documents\My Games\Sprocket\Ostfront Tank Collection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE965D25-0A67-4A23-9DE8-AF197B1F57B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B69875A6-CB63-4757-A8CC-ED78FEA593E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{3FAC36FE-B102-4B04-8548-70F58966D145}"/>
+    <workbookView xWindow="7600" yWindow="1710" windowWidth="28800" windowHeight="15360" xr2:uid="{3FAC36FE-B102-4B04-8548-70F58966D145}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="603">
   <si>
     <t>Tank</t>
   </si>
@@ -224,9 +224,6 @@
     <t>LVT-4 Water Buffalo</t>
   </si>
   <si>
-    <t>M18 Hellcat</t>
-  </si>
-  <si>
     <t>M24 Chaffee</t>
   </si>
   <si>
@@ -314,9 +311,6 @@
     <t>T-40</t>
   </si>
   <si>
-    <t>T-50</t>
-  </si>
-  <si>
     <t>T-60</t>
   </si>
   <si>
@@ -1088,9 +1082,6 @@
     <t>Chi-Se</t>
   </si>
   <si>
-    <t>Durchbruchswagen II</t>
-  </si>
-  <si>
     <t>E 75</t>
   </si>
   <si>
@@ -1235,9 +1226,6 @@
     <t>Harry Hopkins Mk 1 CS Alecto</t>
   </si>
   <si>
-    <t>Landsverk L-60</t>
-  </si>
-  <si>
     <t>Leichttraktor</t>
   </si>
   <si>
@@ -1274,9 +1262,6 @@
     <t>Panzerwagen 39</t>
   </si>
   <si>
-    <t>Pvlvv fm-42</t>
-  </si>
-  <si>
     <t>Pz.Kpfw. 38 n.A</t>
   </si>
   <si>
@@ -1304,18 +1289,6 @@
     <t>Straussler V-4-40</t>
   </si>
   <si>
-    <t>Strv m-21-29</t>
-  </si>
-  <si>
-    <t>Strv m-31</t>
-  </si>
-  <si>
-    <t>Strv m-38</t>
-  </si>
-  <si>
-    <t>Strv m-40L</t>
-  </si>
-  <si>
     <t>SU-18</t>
   </si>
   <si>
@@ -1490,18 +1463,12 @@
     <t>Sexton I</t>
   </si>
   <si>
-    <t>Škoda T 25</t>
-  </si>
-  <si>
     <t>SOMUA S35 CA</t>
   </si>
   <si>
     <t>ST vz. 39</t>
   </si>
   <si>
-    <t>Strv m-42</t>
-  </si>
-  <si>
     <t>SU-8</t>
   </si>
   <si>
@@ -1784,9 +1751,6 @@
     <t>AMC.34 YR</t>
   </si>
   <si>
-    <t>LVT(A)(1</t>
-  </si>
-  <si>
     <t>LVT(A)(1) (M24)</t>
   </si>
   <si>
@@ -1866,6 +1830,27 @@
   </si>
   <si>
     <t>GMC T27 "Xylophone"</t>
+  </si>
+  <si>
+    <t>LVT(A)(1)</t>
+  </si>
+  <si>
+    <t>Pvlvv fm/42</t>
+  </si>
+  <si>
+    <t>Sav M/43</t>
+  </si>
+  <si>
+    <t>Strv m/21-29</t>
+  </si>
+  <si>
+    <t>Strv m/31</t>
+  </si>
+  <si>
+    <t>Strv m/38</t>
+  </si>
+  <si>
+    <t>Strv m/40L</t>
   </si>
 </sst>
 </file>
@@ -2289,7 +2274,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C50DCCC-8446-4FAC-BA76-D53F2D86B716}">
-  <dimension ref="A1:C594"/>
+  <dimension ref="A1:C588"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.81640625" customWidth="1"/>
@@ -2310,557 +2295,557 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B9" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B11" t="s">
         <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B12" t="s">
         <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B13" t="s">
         <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B16" t="s">
         <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B17" t="s">
         <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B18" t="s">
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B19" t="s">
         <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B20" t="s">
         <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B21" t="s">
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B22" t="s">
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B25" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C25" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="B26" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C26" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B27" t="s">
         <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B28" t="s">
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s">
         <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="B31" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C31" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s">
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B33" t="s">
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s">
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s">
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B38" t="s">
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B40" t="s">
         <v>7</v>
       </c>
       <c r="C40" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s">
         <v>7</v>
       </c>
       <c r="C41" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s">
         <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B43" t="s">
         <v>7</v>
       </c>
       <c r="C43" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="B44" t="s">
         <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="B45" t="s">
         <v>7</v>
       </c>
       <c r="C45" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="B46" t="s">
         <v>7</v>
       </c>
       <c r="C46" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B47" t="s">
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B48" t="s">
         <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="B49" t="s">
         <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B50" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C50" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B51" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C51" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B52" t="s">
         <v>16</v>
@@ -2904,7 +2889,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B56" t="s">
         <v>11</v>
@@ -2915,7 +2900,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="B57" t="s">
         <v>11</v>
@@ -2926,10 +2911,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B58" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C58" t="s">
         <v>8</v>
@@ -2970,249 +2955,249 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B62" t="s">
         <v>54</v>
       </c>
       <c r="C62" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B63" t="s">
         <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B64" t="s">
         <v>4</v>
       </c>
       <c r="C64" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B65" t="s">
         <v>4</v>
       </c>
       <c r="C65" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B66" t="s">
         <v>7</v>
       </c>
       <c r="C66" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B67" t="s">
         <v>7</v>
       </c>
       <c r="C67" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B68" t="s">
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B69" t="s">
         <v>7</v>
       </c>
       <c r="C69" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B72" t="s">
         <v>16</v>
       </c>
       <c r="C72" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B73" t="s">
         <v>4</v>
       </c>
       <c r="C73" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B74" t="s">
         <v>7</v>
       </c>
       <c r="C74" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B75" t="s">
         <v>7</v>
       </c>
       <c r="C75" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B76" t="s">
         <v>7</v>
       </c>
       <c r="C76" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B77" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C77" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B78" t="s">
         <v>54</v>
       </c>
       <c r="C78" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B79" t="s">
         <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B80" t="s">
         <v>16</v>
       </c>
       <c r="C80" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B81" t="s">
         <v>16</v>
       </c>
       <c r="C81" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B82" t="s">
         <v>16</v>
       </c>
       <c r="C82" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B83" t="s">
         <v>7</v>
       </c>
       <c r="C83" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B84" t="s">
         <v>45</v>
@@ -3223,7 +3208,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B85" t="s">
         <v>45</v>
@@ -3234,7 +3219,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B86" t="s">
         <v>4</v>
@@ -3245,7 +3230,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B87" t="s">
         <v>45</v>
@@ -3256,7 +3241,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B88" t="s">
         <v>45</v>
@@ -3267,7 +3252,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B89" t="s">
         <v>4</v>
@@ -3278,7 +3263,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B90" t="s">
         <v>54</v>
@@ -3289,7 +3274,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="B91" t="s">
         <v>4</v>
@@ -3300,7 +3285,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="B92" t="s">
         <v>4</v>
@@ -3311,7 +3296,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B93" t="s">
         <v>11</v>
@@ -3322,7 +3307,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B94" t="s">
         <v>45</v>
@@ -3333,7 +3318,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B95" t="s">
         <v>16</v>
@@ -3344,7 +3329,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>349</v>
+        <v>15</v>
       </c>
       <c r="B96" t="s">
         <v>16</v>
@@ -3355,10 +3340,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B97" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C97" t="s">
         <v>17</v>
@@ -3366,10 +3351,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>18</v>
+        <v>347</v>
       </c>
       <c r="B98" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C98" t="s">
         <v>17</v>
@@ -3377,10 +3362,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B99" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C99" t="s">
         <v>17</v>
@@ -3388,7 +3373,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B100" t="s">
         <v>16</v>
@@ -3399,7 +3384,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B101" t="s">
         <v>16</v>
@@ -3410,10 +3395,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>353</v>
+        <v>554</v>
       </c>
       <c r="B102" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C102" t="s">
         <v>17</v>
@@ -3421,7 +3406,7 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>565</v>
+        <v>19</v>
       </c>
       <c r="B103" t="s">
         <v>13</v>
@@ -3432,7 +3417,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B104" t="s">
         <v>13</v>
@@ -3443,7 +3428,7 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B105" t="s">
         <v>13</v>
@@ -3454,7 +3439,7 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B106" t="s">
         <v>13</v>
@@ -3465,7 +3450,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B107" t="s">
         <v>13</v>
@@ -3476,7 +3461,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>23</v>
+        <v>555</v>
       </c>
       <c r="B108" t="s">
         <v>13</v>
@@ -3487,7 +3472,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="B109" t="s">
         <v>13</v>
@@ -3498,7 +3483,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>567</v>
+        <v>24</v>
       </c>
       <c r="B110" t="s">
         <v>13</v>
@@ -3509,7 +3494,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B111" t="s">
         <v>13</v>
@@ -3520,7 +3505,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>25</v>
+        <v>557</v>
       </c>
       <c r="B112" t="s">
         <v>13</v>
@@ -3531,7 +3516,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>568</v>
+        <v>26</v>
       </c>
       <c r="B113" t="s">
         <v>13</v>
@@ -3542,7 +3527,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>26</v>
+        <v>234</v>
       </c>
       <c r="B114" t="s">
         <v>13</v>
@@ -3553,7 +3538,7 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B115" t="s">
         <v>13</v>
@@ -3564,10 +3549,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>242</v>
+        <v>351</v>
       </c>
       <c r="B116" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C116" t="s">
         <v>17</v>
@@ -3575,7 +3560,7 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>354</v>
+        <v>27</v>
       </c>
       <c r="B117" t="s">
         <v>16</v>
@@ -3586,10 +3571,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B118" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C118" t="s">
         <v>17</v>
@@ -3597,7 +3582,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B119" t="s">
         <v>13</v>
@@ -3608,7 +3593,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>29</v>
+        <v>558</v>
       </c>
       <c r="B120" t="s">
         <v>13</v>
@@ -3619,7 +3604,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>569</v>
+        <v>352</v>
       </c>
       <c r="B121" t="s">
         <v>13</v>
@@ -3629,8 +3614,8 @@
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
-        <v>355</v>
+      <c r="A122" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="B122" t="s">
         <v>13</v>
@@ -3640,8 +3625,8 @@
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A123" s="2" t="s">
-        <v>234</v>
+      <c r="A123" t="s">
+        <v>232</v>
       </c>
       <c r="B123" t="s">
         <v>13</v>
@@ -3652,7 +3637,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>234</v>
+        <v>353</v>
       </c>
       <c r="B124" t="s">
         <v>13</v>
@@ -3663,7 +3648,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>356</v>
+        <v>559</v>
       </c>
       <c r="B125" t="s">
         <v>13</v>
@@ -3674,7 +3659,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>570</v>
+        <v>30</v>
       </c>
       <c r="B126" t="s">
         <v>13</v>
@@ -3685,7 +3670,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B127" t="s">
         <v>13</v>
@@ -3696,7 +3681,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B128" t="s">
         <v>13</v>
@@ -3707,7 +3692,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>32</v>
+        <v>235</v>
       </c>
       <c r="B129" t="s">
         <v>13</v>
@@ -3718,10 +3703,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>237</v>
+        <v>33</v>
       </c>
       <c r="B130" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C130" t="s">
         <v>17</v>
@@ -3740,10 +3725,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>33</v>
+        <v>560</v>
       </c>
       <c r="B132" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C132" t="s">
         <v>17</v>
@@ -3751,10 +3736,10 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>571</v>
+        <v>354</v>
       </c>
       <c r="B133" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C133" t="s">
         <v>17</v>
@@ -3762,10 +3747,10 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B134" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C134" t="s">
         <v>17</v>
@@ -3773,7 +3758,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B135" t="s">
         <v>13</v>
@@ -3784,7 +3769,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>359</v>
+        <v>34</v>
       </c>
       <c r="B136" t="s">
         <v>13</v>
@@ -3795,7 +3780,7 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>34</v>
+        <v>357</v>
       </c>
       <c r="B137" t="s">
         <v>13</v>
@@ -3806,7 +3791,7 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B138" t="s">
         <v>13</v>
@@ -3817,7 +3802,7 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B139" t="s">
         <v>13</v>
@@ -3828,10 +3813,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B140" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
@@ -3839,10 +3824,10 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>363</v>
+        <v>255</v>
       </c>
       <c r="B141" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
@@ -3850,7 +3835,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>257</v>
+        <v>361</v>
       </c>
       <c r="B142" t="s">
         <v>16</v>
@@ -3861,7 +3846,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>364</v>
+        <v>561</v>
       </c>
       <c r="B143" t="s">
         <v>16</v>
@@ -3872,10 +3857,10 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>572</v>
+        <v>35</v>
       </c>
       <c r="B144" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
@@ -3883,7 +3868,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>35</v>
+        <v>562</v>
       </c>
       <c r="B145" t="s">
         <v>13</v>
@@ -3894,10 +3879,10 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>573</v>
+        <v>254</v>
       </c>
       <c r="B146" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
@@ -3905,7 +3890,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B147" t="s">
         <v>16</v>
@@ -3916,29 +3901,29 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="B148" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>240</v>
+      <c r="A149" s="3" t="s">
+        <v>259</v>
       </c>
       <c r="B149" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C149" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A150" s="3" t="s">
-        <v>261</v>
+      <c r="A150" t="s">
+        <v>260</v>
       </c>
       <c r="B150" t="s">
         <v>16</v>
@@ -3949,7 +3934,7 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B151" t="s">
         <v>16</v>
@@ -3960,7 +3945,7 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>267</v>
+        <v>563</v>
       </c>
       <c r="B152" t="s">
         <v>16</v>
@@ -3971,10 +3956,10 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>574</v>
+        <v>36</v>
       </c>
       <c r="B153" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C153" t="s">
         <v>17</v>
@@ -3982,7 +3967,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>36</v>
+        <v>362</v>
       </c>
       <c r="B154" t="s">
         <v>13</v>
@@ -3993,7 +3978,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B155" t="s">
         <v>13</v>
@@ -4004,10 +3989,10 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>366</v>
+        <v>261</v>
       </c>
       <c r="B156" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C156" t="s">
         <v>17</v>
@@ -4015,7 +4000,7 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>263</v>
+        <v>37</v>
       </c>
       <c r="B157" t="s">
         <v>16</v>
@@ -4037,7 +4022,7 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B159" t="s">
         <v>16</v>
@@ -4048,10 +4033,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>38</v>
+        <v>364</v>
       </c>
       <c r="B160" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
@@ -4059,7 +4044,7 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B161" t="s">
         <v>13</v>
@@ -4070,7 +4055,7 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B162" t="s">
         <v>13</v>
@@ -4081,7 +4066,7 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>369</v>
+        <v>236</v>
       </c>
       <c r="B163" t="s">
         <v>13</v>
@@ -4092,7 +4077,7 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B164" t="s">
         <v>13</v>
@@ -4103,7 +4088,7 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>239</v>
+        <v>39</v>
       </c>
       <c r="B165" t="s">
         <v>13</v>
@@ -4125,7 +4110,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B167" t="s">
         <v>13</v>
@@ -4136,7 +4121,7 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>40</v>
+        <v>367</v>
       </c>
       <c r="B168" t="s">
         <v>13</v>
@@ -4147,7 +4132,7 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B169" t="s">
         <v>13</v>
@@ -4158,10 +4143,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B170" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C170" t="s">
         <v>17</v>
@@ -4169,10 +4154,10 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B171" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C171" t="s">
         <v>17</v>
@@ -4180,10 +4165,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B172" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C172" t="s">
         <v>17</v>
@@ -4191,7 +4176,7 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B173" t="s">
         <v>7</v>
@@ -4202,7 +4187,7 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B174" t="s">
         <v>7</v>
@@ -4213,7 +4198,7 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>376</v>
+        <v>564</v>
       </c>
       <c r="B175" t="s">
         <v>7</v>
@@ -4224,10 +4209,10 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>575</v>
+        <v>41</v>
       </c>
       <c r="B176" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C176" t="s">
         <v>17</v>
@@ -4235,7 +4220,7 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B177" t="s">
         <v>13</v>
@@ -4246,7 +4231,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>42</v>
+        <v>565</v>
       </c>
       <c r="B178" t="s">
         <v>13</v>
@@ -4257,10 +4242,10 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="B179" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C179" t="s">
         <v>17</v>
@@ -4268,7 +4253,7 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="B180" t="s">
         <v>7</v>
@@ -4279,7 +4264,7 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>578</v>
+        <v>242</v>
       </c>
       <c r="B181" t="s">
         <v>7</v>
@@ -4290,10 +4275,10 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>244</v>
+        <v>43</v>
       </c>
       <c r="B182" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C182" t="s">
         <v>17</v>
@@ -4301,7 +4286,7 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B183" t="s">
         <v>16</v>
@@ -4312,7 +4297,7 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>44</v>
+        <v>233</v>
       </c>
       <c r="B184" t="s">
         <v>16</v>
@@ -4323,10 +4308,10 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>235</v>
+        <v>374</v>
       </c>
       <c r="B185" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C185" t="s">
         <v>17</v>
@@ -4334,7 +4319,7 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>377</v>
+        <v>270</v>
       </c>
       <c r="B186" t="s">
         <v>11</v>
@@ -4345,7 +4330,7 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>272</v>
+        <v>375</v>
       </c>
       <c r="B187" t="s">
         <v>11</v>
@@ -4356,7 +4341,7 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>378</v>
+        <v>46</v>
       </c>
       <c r="B188" t="s">
         <v>11</v>
@@ -4367,7 +4352,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B189" t="s">
         <v>11</v>
@@ -4378,10 +4363,10 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B190" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C190" t="s">
         <v>17</v>
@@ -4389,10 +4374,10 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>48</v>
+        <v>376</v>
       </c>
       <c r="B191" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C191" t="s">
         <v>17</v>
@@ -4400,7 +4385,7 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B192" t="s">
         <v>16</v>
@@ -4411,7 +4396,7 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B193" t="s">
         <v>16</v>
@@ -4422,7 +4407,7 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B194" t="s">
         <v>16</v>
@@ -4433,7 +4418,7 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>382</v>
+        <v>537</v>
       </c>
       <c r="B195" t="s">
         <v>16</v>
@@ -4444,7 +4429,7 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>548</v>
+        <v>380</v>
       </c>
       <c r="B196" t="s">
         <v>16</v>
@@ -4455,7 +4440,7 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>383</v>
+        <v>252</v>
       </c>
       <c r="B197" t="s">
         <v>16</v>
@@ -4466,7 +4451,7 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>254</v>
+        <v>49</v>
       </c>
       <c r="B198" t="s">
         <v>16</v>
@@ -4477,7 +4462,7 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>49</v>
+        <v>381</v>
       </c>
       <c r="B199" t="s">
         <v>16</v>
@@ -4488,10 +4473,10 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B200" t="s">
-        <v>16</v>
+        <v>538</v>
       </c>
       <c r="C200" t="s">
         <v>17</v>
@@ -4499,10 +4484,10 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B201" t="s">
-        <v>549</v>
+        <v>16</v>
       </c>
       <c r="C201" t="s">
         <v>17</v>
@@ -4510,21 +4495,21 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>386</v>
+        <v>272</v>
       </c>
       <c r="B202" t="s">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="C202" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>274</v>
+        <v>384</v>
       </c>
       <c r="B203" t="s">
-        <v>106</v>
+        <v>228</v>
       </c>
       <c r="C203" t="s">
         <v>51</v>
@@ -4532,10 +4517,10 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B204" t="s">
-        <v>230</v>
+        <v>13</v>
       </c>
       <c r="C204" t="s">
         <v>51</v>
@@ -4543,10 +4528,10 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>388</v>
+        <v>568</v>
       </c>
       <c r="B205" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C205" t="s">
         <v>51</v>
@@ -4554,7 +4539,7 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>579</v>
+        <v>386</v>
       </c>
       <c r="B206" t="s">
         <v>4</v>
@@ -4565,7 +4550,7 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B207" t="s">
         <v>4</v>
@@ -4576,10 +4561,10 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B208" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C208" t="s">
         <v>51</v>
@@ -4587,7 +4572,7 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B209" t="s">
         <v>13</v>
@@ -4598,10 +4583,10 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>392</v>
+        <v>50</v>
       </c>
       <c r="B210" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C210" t="s">
         <v>51</v>
@@ -4609,10 +4594,10 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>50</v>
+        <v>257</v>
       </c>
       <c r="B211" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C211" t="s">
         <v>51</v>
@@ -4620,10 +4605,10 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>259</v>
+        <v>52</v>
       </c>
       <c r="B212" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C212" t="s">
         <v>51</v>
@@ -4631,7 +4616,7 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>52</v>
+        <v>391</v>
       </c>
       <c r="B213" t="s">
         <v>4</v>
@@ -4642,10 +4627,10 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>394</v>
+        <v>53</v>
       </c>
       <c r="B214" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C214" t="s">
         <v>51</v>
@@ -4653,10 +4638,10 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>53</v>
+        <v>392</v>
       </c>
       <c r="B215" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C215" t="s">
         <v>51</v>
@@ -4664,7 +4649,7 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>395</v>
+        <v>55</v>
       </c>
       <c r="B216" t="s">
         <v>16</v>
@@ -4675,7 +4660,7 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B217" t="s">
         <v>16</v>
@@ -4686,10 +4671,10 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>56</v>
+        <v>393</v>
       </c>
       <c r="B218" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C218" t="s">
         <v>51</v>
@@ -4697,10 +4682,10 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B219" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C219" t="s">
         <v>51</v>
@@ -4708,10 +4693,10 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>397</v>
+        <v>57</v>
       </c>
       <c r="B220" t="s">
-        <v>298</v>
+        <v>16</v>
       </c>
       <c r="C220" t="s">
         <v>51</v>
@@ -4719,10 +4704,10 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B221" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C221" t="s">
         <v>51</v>
@@ -4730,7 +4715,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B222" t="s">
         <v>16</v>
@@ -4741,10 +4726,10 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>399</v>
+        <v>223</v>
       </c>
       <c r="B223" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="C223" t="s">
         <v>51</v>
@@ -4752,10 +4737,10 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>58</v>
+        <v>396</v>
       </c>
       <c r="B224" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C224" t="s">
         <v>51</v>
@@ -4763,10 +4748,10 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>225</v>
+        <v>397</v>
       </c>
       <c r="B225" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C225" t="s">
         <v>51</v>
@@ -4774,10 +4759,10 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>400</v>
+        <v>596</v>
       </c>
       <c r="B226" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C226" t="s">
         <v>51</v>
@@ -4785,10 +4770,10 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>401</v>
+        <v>569</v>
       </c>
       <c r="B227" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C227" t="s">
         <v>51</v>
@@ -4796,7 +4781,7 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="B228" t="s">
         <v>7</v>
@@ -4807,7 +4792,7 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>581</v>
+        <v>59</v>
       </c>
       <c r="B229" t="s">
         <v>7</v>
@@ -4818,7 +4803,7 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="B230" t="s">
         <v>7</v>
@@ -4829,7 +4814,7 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>59</v>
+        <v>243</v>
       </c>
       <c r="B231" t="s">
         <v>7</v>
@@ -4840,7 +4825,7 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>583</v>
+        <v>60</v>
       </c>
       <c r="B232" t="s">
         <v>7</v>
@@ -4851,7 +4836,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>60</v>
+        <v>572</v>
       </c>
       <c r="B233" t="s">
         <v>7</v>
@@ -4862,7 +4847,7 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>245</v>
+        <v>398</v>
       </c>
       <c r="B234" t="s">
         <v>7</v>
@@ -4884,7 +4869,7 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>584</v>
+        <v>399</v>
       </c>
       <c r="B236" t="s">
         <v>7</v>
@@ -4895,7 +4880,7 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B237" t="s">
         <v>7</v>
@@ -4917,7 +4902,7 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B239" t="s">
         <v>7</v>
@@ -4928,10 +4913,10 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>404</v>
+        <v>63</v>
       </c>
       <c r="B240" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C240" t="s">
         <v>51</v>
@@ -4939,10 +4924,10 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B241" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C241" t="s">
         <v>51</v>
@@ -4950,10 +4935,10 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>405</v>
+        <v>65</v>
       </c>
       <c r="B242" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C242" t="s">
         <v>51</v>
@@ -4961,7 +4946,7 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B243" t="s">
         <v>16</v>
@@ -4972,10 +4957,10 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B244" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C244" t="s">
         <v>51</v>
@@ -4983,7 +4968,7 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>66</v>
+        <v>402</v>
       </c>
       <c r="B245" t="s">
         <v>16</v>
@@ -4994,10 +4979,10 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>67</v>
+        <v>403</v>
       </c>
       <c r="B246" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C246" t="s">
         <v>51</v>
@@ -5005,10 +4990,10 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>68</v>
+        <v>404</v>
       </c>
       <c r="B247" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C247" t="s">
         <v>51</v>
@@ -5016,10 +5001,10 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>406</v>
+        <v>229</v>
       </c>
       <c r="B248" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C248" t="s">
         <v>51</v>
@@ -5027,10 +5012,10 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>407</v>
+        <v>68</v>
       </c>
       <c r="B249" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C249" t="s">
         <v>51</v>
@@ -5038,10 +5023,10 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>408</v>
+        <v>69</v>
       </c>
       <c r="B250" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C250" t="s">
         <v>51</v>
@@ -5049,10 +5034,10 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>231</v>
+        <v>70</v>
       </c>
       <c r="B251" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C251" t="s">
         <v>51</v>
@@ -5060,7 +5045,7 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B252" t="s">
         <v>16</v>
@@ -5071,7 +5056,7 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B253" t="s">
         <v>16</v>
@@ -5082,7 +5067,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B254" t="s">
         <v>16</v>
@@ -5093,7 +5078,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B255" t="s">
         <v>16</v>
@@ -5104,7 +5089,7 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>73</v>
+        <v>258</v>
       </c>
       <c r="B256" t="s">
         <v>16</v>
@@ -5115,10 +5100,10 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>74</v>
+        <v>405</v>
       </c>
       <c r="B257" t="s">
-        <v>16</v>
+        <v>538</v>
       </c>
       <c r="C257" t="s">
         <v>51</v>
@@ -5126,10 +5111,10 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>75</v>
+        <v>597</v>
       </c>
       <c r="B258" t="s">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c r="C258" t="s">
         <v>51</v>
@@ -5137,7 +5122,7 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>260</v>
+        <v>406</v>
       </c>
       <c r="B259" t="s">
         <v>16</v>
@@ -5148,10 +5133,10 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>409</v>
+        <v>75</v>
       </c>
       <c r="B260" t="s">
-        <v>549</v>
+        <v>4</v>
       </c>
       <c r="C260" t="s">
         <v>51</v>
@@ -5159,10 +5144,10 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B261" t="s">
-        <v>298</v>
+        <v>16</v>
       </c>
       <c r="C261" t="s">
         <v>51</v>
@@ -5170,7 +5155,7 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>411</v>
+        <v>256</v>
       </c>
       <c r="B262" t="s">
         <v>16</v>
@@ -5192,10 +5177,10 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>412</v>
+        <v>77</v>
       </c>
       <c r="B264" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C264" t="s">
         <v>51</v>
@@ -5203,10 +5188,10 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>258</v>
+        <v>408</v>
       </c>
       <c r="B265" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C265" t="s">
         <v>51</v>
@@ -5214,7 +5199,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>77</v>
+        <v>409</v>
       </c>
       <c r="B266" t="s">
         <v>4</v>
@@ -5225,10 +5210,10 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="B267" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C267" t="s">
         <v>51</v>
@@ -5236,10 +5221,10 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>413</v>
+        <v>598</v>
       </c>
       <c r="B268" t="s">
-        <v>4</v>
+        <v>296</v>
       </c>
       <c r="C268" t="s">
         <v>51</v>
@@ -5247,10 +5232,10 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B269" t="s">
-        <v>4</v>
+        <v>296</v>
       </c>
       <c r="C269" t="s">
         <v>51</v>
@@ -5258,10 +5243,10 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>415</v>
+        <v>78</v>
       </c>
       <c r="B270" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C270" t="s">
         <v>51</v>
@@ -5269,10 +5254,10 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>416</v>
+        <v>79</v>
       </c>
       <c r="B271" t="s">
-        <v>298</v>
+        <v>16</v>
       </c>
       <c r="C271" t="s">
         <v>51</v>
@@ -5280,10 +5265,10 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B272" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C272" t="s">
         <v>51</v>
@@ -5291,10 +5276,10 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>80</v>
+        <v>412</v>
       </c>
       <c r="B273" t="s">
-        <v>16</v>
+        <v>538</v>
       </c>
       <c r="C273" t="s">
         <v>51</v>
@@ -5302,10 +5287,10 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>81</v>
+        <v>413</v>
       </c>
       <c r="B274" t="s">
-        <v>54</v>
+        <v>538</v>
       </c>
       <c r="C274" t="s">
         <v>51</v>
@@ -5313,10 +5298,10 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>417</v>
+        <v>573</v>
       </c>
       <c r="B275" t="s">
-        <v>549</v>
+        <v>296</v>
       </c>
       <c r="C275" t="s">
         <v>51</v>
@@ -5324,10 +5309,10 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="B276" t="s">
-        <v>549</v>
+        <v>16</v>
       </c>
       <c r="C276" t="s">
         <v>51</v>
@@ -5335,10 +5320,10 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>585</v>
+        <v>414</v>
       </c>
       <c r="B277" t="s">
-        <v>298</v>
+        <v>16</v>
       </c>
       <c r="C277" t="s">
         <v>51</v>
@@ -5346,10 +5331,10 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>82</v>
+        <v>599</v>
       </c>
       <c r="B278" t="s">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c r="C278" t="s">
         <v>51</v>
@@ -5357,10 +5342,10 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>419</v>
+        <v>600</v>
       </c>
       <c r="B279" t="s">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c r="C279" t="s">
         <v>51</v>
@@ -5368,10 +5353,10 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>420</v>
+        <v>601</v>
       </c>
       <c r="B280" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C280" t="s">
         <v>51</v>
@@ -5379,10 +5364,10 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>421</v>
+        <v>602</v>
       </c>
       <c r="B281" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C281" t="s">
         <v>51</v>
@@ -5390,10 +5375,10 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>422</v>
+        <v>82</v>
       </c>
       <c r="B282" t="s">
-        <v>298</v>
+        <v>16</v>
       </c>
       <c r="C282" t="s">
         <v>51</v>
@@ -5401,10 +5386,10 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="B283" t="s">
-        <v>298</v>
+        <v>13</v>
       </c>
       <c r="C283" t="s">
         <v>51</v>
@@ -5415,7 +5400,7 @@
         <v>83</v>
       </c>
       <c r="B284" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C284" t="s">
         <v>51</v>
@@ -5423,10 +5408,10 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B285" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C285" t="s">
         <v>51</v>
@@ -5434,10 +5419,10 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>84</v>
+        <v>417</v>
       </c>
       <c r="B286" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C286" t="s">
         <v>51</v>
@@ -5445,10 +5430,10 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>84</v>
+        <v>418</v>
       </c>
       <c r="B287" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C287" t="s">
         <v>51</v>
@@ -5456,10 +5441,10 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>425</v>
+        <v>84</v>
       </c>
       <c r="B288" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C288" t="s">
         <v>51</v>
@@ -5467,10 +5452,10 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>426</v>
+        <v>84</v>
       </c>
       <c r="B289" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C289" t="s">
         <v>51</v>
@@ -5478,10 +5463,10 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="B290" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C290" t="s">
         <v>51</v>
@@ -5489,10 +5474,10 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>85</v>
+        <v>420</v>
       </c>
       <c r="B291" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C291" t="s">
         <v>51</v>
@@ -5500,10 +5485,10 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>85</v>
+        <v>421</v>
       </c>
       <c r="B292" t="s">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="C292" t="s">
         <v>51</v>
@@ -5511,7 +5496,7 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B293" t="s">
         <v>7</v>
@@ -5522,10 +5507,10 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>429</v>
+        <v>86</v>
       </c>
       <c r="B294" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C294" t="s">
         <v>51</v>
@@ -5533,10 +5518,10 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>430</v>
+        <v>87</v>
       </c>
       <c r="B295" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C295" t="s">
         <v>51</v>
@@ -5544,7 +5529,7 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="B296" t="s">
         <v>7</v>
@@ -5555,7 +5540,7 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B297" t="s">
         <v>13</v>
@@ -5566,7 +5551,7 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>88</v>
+        <v>424</v>
       </c>
       <c r="B298" t="s">
         <v>13</v>
@@ -5577,10 +5562,10 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="B299" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C299" t="s">
         <v>51</v>
@@ -5588,7 +5573,7 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>89</v>
+        <v>426</v>
       </c>
       <c r="B300" t="s">
         <v>13</v>
@@ -5599,7 +5584,7 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>433</v>
+        <v>574</v>
       </c>
       <c r="B301" t="s">
         <v>13</v>
@@ -5610,10 +5595,10 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="B302" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C302" t="s">
         <v>51</v>
@@ -5621,7 +5606,7 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B303" t="s">
         <v>13</v>
@@ -5632,7 +5617,7 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>435</v>
+        <v>90</v>
       </c>
       <c r="B304" t="s">
         <v>13</v>
@@ -5643,10 +5628,10 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>586</v>
+        <v>428</v>
       </c>
       <c r="B305" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C305" t="s">
         <v>51</v>
@@ -5654,7 +5639,7 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="B306" t="s">
         <v>7</v>
@@ -5687,7 +5672,7 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>437</v>
+        <v>244</v>
       </c>
       <c r="B309" t="s">
         <v>7</v>
@@ -5698,10 +5683,10 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>438</v>
+        <v>93</v>
       </c>
       <c r="B310" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C310" t="s">
         <v>51</v>
@@ -5709,10 +5694,10 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>93</v>
+        <v>430</v>
       </c>
       <c r="B311" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C311" t="s">
         <v>51</v>
@@ -5720,10 +5705,10 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>94</v>
+        <v>431</v>
       </c>
       <c r="B312" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C312" t="s">
         <v>51</v>
@@ -5731,10 +5716,10 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>246</v>
+        <v>575</v>
       </c>
       <c r="B313" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C313" t="s">
         <v>51</v>
@@ -5742,10 +5727,10 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B314" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C314" t="s">
         <v>51</v>
@@ -5753,10 +5738,10 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>439</v>
+        <v>269</v>
       </c>
       <c r="B315" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C315" t="s">
         <v>51</v>
@@ -5764,7 +5749,7 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>440</v>
+        <v>576</v>
       </c>
       <c r="B316" t="s">
         <v>11</v>
@@ -5775,7 +5760,7 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>587</v>
+        <v>432</v>
       </c>
       <c r="B317" t="s">
         <v>11</v>
@@ -5786,7 +5771,7 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>96</v>
+        <v>577</v>
       </c>
       <c r="B318" t="s">
         <v>11</v>
@@ -5797,7 +5782,7 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>271</v>
+        <v>95</v>
       </c>
       <c r="B319" t="s">
         <v>11</v>
@@ -5808,7 +5793,7 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="B320" t="s">
         <v>11</v>
@@ -5819,7 +5804,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="B321" t="s">
         <v>11</v>
@@ -5830,7 +5815,7 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>589</v>
+        <v>98</v>
       </c>
       <c r="B322" t="s">
         <v>11</v>
@@ -5841,7 +5826,7 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>97</v>
+        <v>579</v>
       </c>
       <c r="B323" t="s">
         <v>11</v>
@@ -5852,10 +5837,10 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>590</v>
+        <v>99</v>
       </c>
       <c r="B324" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C324" t="s">
         <v>51</v>
@@ -5863,10 +5848,10 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>442</v>
+        <v>100</v>
       </c>
       <c r="B325" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C325" t="s">
         <v>51</v>
@@ -5874,10 +5859,10 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B326" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C326" t="s">
         <v>51</v>
@@ -5885,10 +5870,10 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>591</v>
+        <v>434</v>
       </c>
       <c r="B327" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C327" t="s">
         <v>51</v>
@@ -5896,10 +5881,10 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>101</v>
+        <v>435</v>
       </c>
       <c r="B328" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C328" t="s">
         <v>51</v>
@@ -5910,7 +5895,7 @@
         <v>102</v>
       </c>
       <c r="B329" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C329" t="s">
         <v>51</v>
@@ -5918,10 +5903,10 @@
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>103</v>
+        <v>239</v>
       </c>
       <c r="B330" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C330" t="s">
         <v>51</v>
@@ -5929,10 +5914,10 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>443</v>
+        <v>580</v>
       </c>
       <c r="B331" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C331" t="s">
         <v>51</v>
@@ -5940,310 +5925,310 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>444</v>
+        <v>249</v>
       </c>
       <c r="B332" t="s">
-        <v>16</v>
+        <v>228</v>
       </c>
       <c r="C332" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>104</v>
+        <v>436</v>
       </c>
       <c r="B333" t="s">
-        <v>13</v>
+        <v>228</v>
       </c>
       <c r="C333" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>241</v>
+        <v>103</v>
       </c>
       <c r="B334" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="C334" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>592</v>
+        <v>106</v>
       </c>
       <c r="B335" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="C335" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>251</v>
+        <v>437</v>
       </c>
       <c r="B336" t="s">
-        <v>230</v>
+        <v>45</v>
       </c>
       <c r="C336" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="B337" t="s">
-        <v>230</v>
+        <v>13</v>
       </c>
       <c r="C337" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>105</v>
+        <v>439</v>
       </c>
       <c r="B338" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="C338" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>108</v>
+        <v>440</v>
       </c>
       <c r="B339" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="C339" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B340" t="s">
         <v>45</v>
       </c>
       <c r="C340" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B341" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C341" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B342" t="s">
         <v>45</v>
       </c>
       <c r="C342" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B343" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C343" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B344" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C344" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="B345" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C345" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B346" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C346" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>453</v>
+        <v>390</v>
       </c>
       <c r="B347" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C347" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="B348" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C348" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>455</v>
+        <v>107</v>
       </c>
       <c r="B349" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C349" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>456</v>
+        <v>108</v>
       </c>
       <c r="B350" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C350" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>393</v>
+        <v>109</v>
       </c>
       <c r="B351" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C351" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>457</v>
+        <v>110</v>
       </c>
       <c r="B352" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C352" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>109</v>
+        <v>449</v>
       </c>
       <c r="B353" t="s">
-        <v>45</v>
+        <v>228</v>
       </c>
       <c r="C353" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B354" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C354" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B355" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C355" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>112</v>
+        <v>262</v>
       </c>
       <c r="B356" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C356" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>458</v>
+        <v>113</v>
       </c>
       <c r="B357" t="s">
-        <v>230</v>
+        <v>16</v>
       </c>
       <c r="C357" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B358" t="s">
         <v>16</v>
       </c>
       <c r="C358" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="B359" t="s">
         <v>16</v>
       </c>
       <c r="C359" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.35">
@@ -6254,7 +6239,7 @@
         <v>16</v>
       </c>
       <c r="C360" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.35">
@@ -6265,40 +6250,40 @@
         <v>16</v>
       </c>
       <c r="C361" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>116</v>
+        <v>450</v>
       </c>
       <c r="B362" t="s">
         <v>16</v>
       </c>
       <c r="C362" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A363" s="4" t="s">
-        <v>265</v>
+        <v>116</v>
       </c>
       <c r="B363" t="s">
         <v>16</v>
       </c>
       <c r="C363" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>266</v>
+        <v>451</v>
       </c>
       <c r="B364" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C364" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.35">
@@ -6309,238 +6294,238 @@
         <v>16</v>
       </c>
       <c r="C365" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>459</v>
+        <v>118</v>
       </c>
       <c r="B366" t="s">
         <v>16</v>
       </c>
       <c r="C366" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B367" t="s">
         <v>16</v>
       </c>
       <c r="C367" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>460</v>
+        <v>120</v>
       </c>
       <c r="B368" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C368" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>119</v>
+        <v>452</v>
       </c>
       <c r="B369" t="s">
         <v>16</v>
       </c>
       <c r="C369" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>120</v>
+        <v>453</v>
       </c>
       <c r="B370" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C370" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>121</v>
+        <v>454</v>
       </c>
       <c r="B371" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C371" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B372" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C372" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="B373" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C373" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>462</v>
+        <v>122</v>
       </c>
       <c r="B374" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C374" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="B375" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C375" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>123</v>
+        <v>581</v>
       </c>
       <c r="B376" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C376" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>464</v>
+        <v>582</v>
       </c>
       <c r="B377" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C377" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>124</v>
+        <v>457</v>
       </c>
       <c r="B378" t="s">
         <v>7</v>
       </c>
       <c r="C378" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>465</v>
+        <v>123</v>
       </c>
       <c r="B379" t="s">
         <v>7</v>
       </c>
       <c r="C379" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>593</v>
+        <v>124</v>
       </c>
       <c r="B380" t="s">
         <v>7</v>
       </c>
       <c r="C380" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>594</v>
+        <v>125</v>
       </c>
       <c r="B381" t="s">
         <v>7</v>
       </c>
       <c r="C381" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>466</v>
+        <v>126</v>
       </c>
       <c r="B382" t="s">
         <v>7</v>
       </c>
       <c r="C382" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B383" t="s">
         <v>7</v>
       </c>
       <c r="C383" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B384" t="s">
         <v>7</v>
       </c>
       <c r="C384" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>127</v>
+        <v>458</v>
       </c>
       <c r="B385" t="s">
         <v>7</v>
       </c>
       <c r="C385" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>128</v>
+        <v>459</v>
       </c>
       <c r="B386" t="s">
         <v>7</v>
       </c>
       <c r="C386" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.35">
@@ -6551,7 +6536,7 @@
         <v>7</v>
       </c>
       <c r="C387" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.35">
@@ -6562,227 +6547,227 @@
         <v>7</v>
       </c>
       <c r="C388" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>467</v>
+        <v>131</v>
       </c>
       <c r="B389" t="s">
         <v>7</v>
       </c>
       <c r="C389" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>468</v>
+        <v>132</v>
       </c>
       <c r="B390" t="s">
         <v>7</v>
       </c>
       <c r="C390" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B391" t="s">
         <v>7</v>
       </c>
       <c r="C391" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B392" t="s">
         <v>7</v>
       </c>
       <c r="C392" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B393" t="s">
         <v>7</v>
       </c>
       <c r="C393" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B394" t="s">
         <v>7</v>
       </c>
       <c r="C394" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B395" t="s">
         <v>7</v>
       </c>
       <c r="C395" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B396" t="s">
         <v>7</v>
       </c>
       <c r="C396" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B397" t="s">
         <v>7</v>
       </c>
       <c r="C397" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B398" t="s">
         <v>7</v>
       </c>
       <c r="C398" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B399" t="s">
         <v>7</v>
       </c>
       <c r="C399" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B400" t="s">
         <v>7</v>
       </c>
       <c r="C400" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B401" t="s">
         <v>7</v>
       </c>
       <c r="C401" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B402" t="s">
         <v>7</v>
       </c>
       <c r="C402" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B403" t="s">
         <v>7</v>
       </c>
       <c r="C403" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B404" t="s">
         <v>7</v>
       </c>
       <c r="C404" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B405" t="s">
         <v>7</v>
       </c>
       <c r="C405" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B406" t="s">
         <v>7</v>
       </c>
       <c r="C406" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>147</v>
+        <v>583</v>
       </c>
       <c r="B407" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C407" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>148</v>
+        <v>245</v>
       </c>
       <c r="B408" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C408" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.35">
@@ -6790,10 +6775,10 @@
         <v>149</v>
       </c>
       <c r="B409" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C409" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.35">
@@ -6801,76 +6786,76 @@
         <v>150</v>
       </c>
       <c r="B410" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C410" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>595</v>
+        <v>151</v>
       </c>
       <c r="B411" t="s">
         <v>45</v>
       </c>
       <c r="C411" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>247</v>
+        <v>152</v>
       </c>
       <c r="B412" t="s">
         <v>45</v>
       </c>
       <c r="C412" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B413" t="s">
         <v>45</v>
       </c>
       <c r="C413" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B414" t="s">
         <v>45</v>
       </c>
       <c r="C414" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>153</v>
+        <v>229</v>
       </c>
       <c r="B415" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C415" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>154</v>
+        <v>460</v>
       </c>
       <c r="B416" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C416" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.35">
@@ -6878,428 +6863,428 @@
         <v>155</v>
       </c>
       <c r="B417" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C417" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B418" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C418" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>231</v>
+        <v>156</v>
       </c>
       <c r="B419" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C419" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>469</v>
+        <v>157</v>
       </c>
       <c r="B420" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C420" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B421" t="s">
         <v>16</v>
       </c>
       <c r="C421" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B422" t="s">
         <v>16</v>
       </c>
       <c r="C422" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B423" t="s">
         <v>16</v>
       </c>
       <c r="C423" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B424" t="s">
         <v>16</v>
       </c>
       <c r="C424" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B425" t="s">
         <v>16</v>
       </c>
       <c r="C425" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B426" t="s">
         <v>16</v>
       </c>
       <c r="C426" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B427" t="s">
         <v>16</v>
       </c>
       <c r="C427" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B428" t="s">
         <v>16</v>
       </c>
       <c r="C428" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B429" t="s">
         <v>16</v>
       </c>
       <c r="C429" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B430" t="s">
         <v>16</v>
       </c>
       <c r="C430" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B431" t="s">
         <v>16</v>
       </c>
       <c r="C431" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B432" t="s">
         <v>16</v>
       </c>
       <c r="C432" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B433" t="s">
         <v>16</v>
       </c>
       <c r="C433" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B434" t="s">
         <v>16</v>
       </c>
       <c r="C434" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>170</v>
+        <v>461</v>
       </c>
       <c r="B435" t="s">
         <v>16</v>
       </c>
       <c r="C435" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>171</v>
+        <v>462</v>
       </c>
       <c r="B436" t="s">
         <v>16</v>
       </c>
       <c r="C436" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>172</v>
+        <v>463</v>
       </c>
       <c r="B437" t="s">
         <v>16</v>
       </c>
       <c r="C437" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B438" t="s">
         <v>16</v>
       </c>
       <c r="C438" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>470</v>
+        <v>173</v>
       </c>
       <c r="B439" t="s">
         <v>16</v>
       </c>
       <c r="C439" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="B440" t="s">
         <v>16</v>
       </c>
       <c r="C440" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="B441" t="s">
         <v>16</v>
       </c>
       <c r="C441" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>174</v>
+        <v>466</v>
       </c>
       <c r="B442" t="s">
-        <v>16</v>
+        <v>467</v>
       </c>
       <c r="C442" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>175</v>
+        <v>468</v>
       </c>
       <c r="B443" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C443" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B444" t="s">
         <v>16</v>
       </c>
       <c r="C444" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B445" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C445" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B446" t="s">
-        <v>476</v>
+        <v>4</v>
       </c>
       <c r="C446" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>477</v>
+        <v>174</v>
       </c>
       <c r="B447" t="s">
         <v>4</v>
       </c>
       <c r="C447" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>478</v>
+        <v>251</v>
       </c>
       <c r="B448" t="s">
         <v>16</v>
       </c>
       <c r="C448" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>479</v>
+        <v>175</v>
       </c>
       <c r="B449" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C449" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>480</v>
+        <v>176</v>
       </c>
       <c r="B450" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C450" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B451" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C451" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>253</v>
+        <v>178</v>
       </c>
       <c r="B452" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C452" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B453" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C453" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>178</v>
+        <v>539</v>
       </c>
       <c r="B454" t="s">
         <v>54</v>
       </c>
       <c r="C454" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>179</v>
+        <v>472</v>
       </c>
       <c r="B455" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C455" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.35">
@@ -7307,43 +7292,43 @@
         <v>180</v>
       </c>
       <c r="B456" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C456" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>181</v>
+        <v>473</v>
       </c>
       <c r="B457" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="C457" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>550</v>
+        <v>474</v>
       </c>
       <c r="B458" t="s">
-        <v>54</v>
+        <v>538</v>
       </c>
       <c r="C458" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>481</v>
+        <v>181</v>
       </c>
       <c r="B459" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C459" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.35">
@@ -7351,373 +7336,373 @@
         <v>182</v>
       </c>
       <c r="B460" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C460" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>482</v>
+        <v>183</v>
       </c>
       <c r="B461" t="s">
-        <v>549</v>
+        <v>16</v>
       </c>
       <c r="C461" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>483</v>
+        <v>184</v>
       </c>
       <c r="B462" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C462" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>484</v>
+        <v>185</v>
       </c>
       <c r="B463" t="s">
-        <v>549</v>
+        <v>16</v>
       </c>
       <c r="C463" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>485</v>
+        <v>186</v>
       </c>
       <c r="B464" t="s">
-        <v>298</v>
+        <v>16</v>
       </c>
       <c r="C464" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B465" t="s">
         <v>16</v>
       </c>
       <c r="C465" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B466" t="s">
         <v>16</v>
       </c>
       <c r="C466" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B467" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C467" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B468" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C468" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B469" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C469" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>188</v>
+        <v>475</v>
       </c>
       <c r="B470" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C470" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B471" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C471" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B472" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C472" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>190</v>
+        <v>476</v>
       </c>
       <c r="B473" t="s">
         <v>13</v>
       </c>
       <c r="C473" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>191</v>
+        <v>477</v>
       </c>
       <c r="B474" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C474" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>192</v>
+        <v>478</v>
       </c>
       <c r="B475" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C475" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="B476" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C476" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="B477" t="s">
         <v>13</v>
       </c>
       <c r="C477" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="B478" t="s">
         <v>13</v>
       </c>
       <c r="C478" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>487</v>
+        <v>584</v>
       </c>
       <c r="B479" t="s">
         <v>13</v>
       </c>
       <c r="C479" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>488</v>
+        <v>193</v>
       </c>
       <c r="B480" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C480" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>489</v>
+        <v>194</v>
       </c>
       <c r="B481" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C481" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>490</v>
+        <v>195</v>
       </c>
       <c r="B482" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C482" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="B483" t="s">
         <v>13</v>
       </c>
       <c r="C483" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="B484" t="s">
         <v>13</v>
       </c>
       <c r="C484" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="B485" t="s">
         <v>13</v>
       </c>
       <c r="C485" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B486" t="s">
         <v>13</v>
       </c>
       <c r="C486" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>196</v>
+        <v>480</v>
       </c>
       <c r="B487" t="s">
         <v>13</v>
       </c>
       <c r="C487" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B488" t="s">
         <v>13</v>
       </c>
       <c r="C488" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>198</v>
+        <v>481</v>
       </c>
       <c r="B489" t="s">
         <v>13</v>
       </c>
       <c r="C489" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B490" t="s">
         <v>13</v>
       </c>
       <c r="C490" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>597</v>
+        <v>482</v>
       </c>
       <c r="B491" t="s">
         <v>13</v>
       </c>
       <c r="C491" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>200</v>
+        <v>483</v>
       </c>
       <c r="B492" t="s">
         <v>13</v>
       </c>
       <c r="C492" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="B493" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C493" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.35">
@@ -7725,1114 +7710,1047 @@
         <v>201</v>
       </c>
       <c r="B494" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C494" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>492</v>
+        <v>202</v>
       </c>
       <c r="B495" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C495" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B496" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C496" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>493</v>
+        <v>586</v>
       </c>
       <c r="B497" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C497" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>494</v>
+        <v>204</v>
       </c>
       <c r="B498" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C498" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>495</v>
+        <v>205</v>
       </c>
       <c r="B499" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C499" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>203</v>
+        <v>587</v>
       </c>
       <c r="B500" t="s">
         <v>11</v>
       </c>
       <c r="C500" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B501" t="s">
         <v>11</v>
       </c>
       <c r="C501" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B502" t="s">
         <v>11</v>
       </c>
       <c r="C502" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>598</v>
+        <v>271</v>
       </c>
       <c r="B503" t="s">
         <v>11</v>
       </c>
       <c r="C503" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>206</v>
+        <v>485</v>
       </c>
       <c r="B504" t="s">
         <v>11</v>
       </c>
       <c r="C504" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>207</v>
+        <v>486</v>
       </c>
       <c r="B505" t="s">
         <v>11</v>
       </c>
       <c r="C505" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>599</v>
+        <v>487</v>
       </c>
       <c r="B506" t="s">
         <v>11</v>
       </c>
       <c r="C506" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>208</v>
+        <v>432</v>
       </c>
       <c r="B507" t="s">
         <v>11</v>
       </c>
       <c r="C507" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>209</v>
+        <v>588</v>
       </c>
       <c r="B508" t="s">
         <v>11</v>
       </c>
       <c r="C508" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>273</v>
+        <v>208</v>
       </c>
       <c r="B509" t="s">
         <v>11</v>
       </c>
       <c r="C509" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>496</v>
+        <v>589</v>
       </c>
       <c r="B510" t="s">
         <v>11</v>
       </c>
       <c r="C510" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>497</v>
+        <v>209</v>
       </c>
       <c r="B511" t="s">
         <v>11</v>
       </c>
       <c r="C511" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>498</v>
+        <v>210</v>
       </c>
       <c r="B512" t="s">
         <v>11</v>
       </c>
       <c r="C512" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>441</v>
+        <v>211</v>
       </c>
       <c r="B513" t="s">
         <v>11</v>
       </c>
       <c r="C513" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="B514" t="s">
         <v>11</v>
       </c>
       <c r="C514" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>210</v>
+        <v>591</v>
       </c>
       <c r="B515" t="s">
         <v>11</v>
       </c>
       <c r="C515" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>601</v>
+        <v>488</v>
       </c>
       <c r="B516" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C516" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B517" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C517" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B518" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C518" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B519" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C519" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>602</v>
+        <v>215</v>
       </c>
       <c r="B520" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C520" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>603</v>
+        <v>216</v>
       </c>
       <c r="B521" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C521" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>499</v>
+        <v>217</v>
       </c>
       <c r="B522" t="s">
         <v>45</v>
       </c>
       <c r="C522" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B523" t="s">
         <v>45</v>
       </c>
       <c r="C523" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>215</v>
+        <v>489</v>
       </c>
       <c r="B524" t="s">
         <v>45</v>
       </c>
       <c r="C524" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>216</v>
+        <v>490</v>
       </c>
       <c r="B525" t="s">
         <v>45</v>
       </c>
       <c r="C525" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>217</v>
+        <v>491</v>
       </c>
       <c r="B526" t="s">
         <v>45</v>
       </c>
       <c r="C526" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>218</v>
+        <v>492</v>
       </c>
       <c r="B527" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C527" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>219</v>
+        <v>493</v>
       </c>
       <c r="B528" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C528" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>220</v>
+        <v>494</v>
       </c>
       <c r="B529" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C529" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B530" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C530" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>501</v>
+        <v>219</v>
       </c>
       <c r="B531" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C531" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>502</v>
+        <v>220</v>
       </c>
       <c r="B532" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="C532" t="s">
-        <v>107</v>
+        <v>221</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>503</v>
+        <v>222</v>
       </c>
       <c r="B533" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C533" t="s">
-        <v>107</v>
+        <v>221</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>504</v>
+        <v>223</v>
       </c>
       <c r="B534" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C534" t="s">
-        <v>107</v>
+        <v>221</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>505</v>
+        <v>224</v>
       </c>
       <c r="B535" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C535" t="s">
-        <v>107</v>
+        <v>221</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>506</v>
+        <v>592</v>
       </c>
       <c r="B536" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C536" t="s">
-        <v>107</v>
+        <v>221</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B537" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C537" t="s">
-        <v>107</v>
+        <v>593</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B538" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C538" t="s">
-        <v>223</v>
+        <v>97</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B539" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C539" t="s">
-        <v>223</v>
+        <v>97</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B540" t="s">
-        <v>4</v>
+        <v>228</v>
       </c>
       <c r="C540" t="s">
-        <v>223</v>
+        <v>97</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="B541" t="s">
         <v>11</v>
       </c>
       <c r="C541" t="s">
-        <v>223</v>
+        <v>97</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="B542" t="s">
         <v>11</v>
       </c>
       <c r="C542" t="s">
-        <v>223</v>
+        <v>97</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>226</v>
+        <v>268</v>
       </c>
       <c r="B543" t="s">
         <v>11</v>
       </c>
       <c r="C543" t="s">
-        <v>605</v>
+        <v>97</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>227</v>
+        <v>96</v>
       </c>
       <c r="B544" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C544" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>228</v>
+        <v>96</v>
       </c>
       <c r="B545" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C545" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="B546" t="s">
-        <v>230</v>
+        <v>45</v>
       </c>
       <c r="C546" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="B547" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C547" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>606</v>
+        <v>496</v>
       </c>
       <c r="B548" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C548" t="s">
-        <v>99</v>
+        <v>497</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>270</v>
+        <v>498</v>
       </c>
       <c r="B549" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C549" t="s">
-        <v>99</v>
+        <v>497</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>98</v>
+        <v>499</v>
       </c>
       <c r="B550" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C550" t="s">
-        <v>99</v>
+        <v>497</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>98</v>
+        <v>500</v>
       </c>
       <c r="B551" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C551" t="s">
-        <v>99</v>
+        <v>497</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>248</v>
+        <v>501</v>
       </c>
       <c r="B552" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C552" t="s">
-        <v>99</v>
+        <v>497</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>249</v>
+        <v>502</v>
       </c>
       <c r="B553" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C553" t="s">
-        <v>99</v>
+        <v>497</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B554" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C554" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="B555" t="s">
-        <v>54</v>
+        <v>467</v>
       </c>
       <c r="C555" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="B556" t="s">
-        <v>45</v>
+        <v>467</v>
       </c>
       <c r="C556" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B557" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C557" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B558" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C558" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B559" t="s">
-        <v>13</v>
+        <v>467</v>
       </c>
       <c r="C559" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B560" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C560" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B561" t="s">
-        <v>476</v>
+        <v>54</v>
       </c>
       <c r="C561" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="B562" t="s">
-        <v>476</v>
+        <v>16</v>
       </c>
       <c r="C562" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="B563" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C563" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B564" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C564" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="B565" t="s">
-        <v>476</v>
+        <v>7</v>
       </c>
       <c r="C565" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B566" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C566" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>521</v>
+        <v>595</v>
       </c>
       <c r="B567" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C567" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="B568" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C568" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B569" t="s">
         <v>16</v>
       </c>
       <c r="C569" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="B570" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C570" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="B571" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="C571" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="B572" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="C572" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>607</v>
+        <v>520</v>
       </c>
       <c r="B573" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C573" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="B574" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C574" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B575" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C575" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="B576" t="s">
         <v>16</v>
       </c>
       <c r="C576" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="B577" t="s">
-        <v>54</v>
+        <v>228</v>
       </c>
       <c r="C577" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B578" t="s">
-        <v>54</v>
+        <v>538</v>
       </c>
       <c r="C578" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="B579" t="s">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="C579" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="B580" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="C580" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B581" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C581" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="B582" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C582" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B583" t="s">
-        <v>230</v>
+        <v>296</v>
       </c>
       <c r="C583" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="B584" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="C584" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B585" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="C585" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="B586" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C586" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B587" t="s">
         <v>13</v>
       </c>
       <c r="C587" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B588" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C588" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A589" t="s">
-        <v>541</v>
-      </c>
-      <c r="B589" t="s">
-        <v>298</v>
-      </c>
-      <c r="C589" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A590" t="s">
-        <v>542</v>
-      </c>
-      <c r="B590" t="s">
-        <v>543</v>
-      </c>
-      <c r="C590" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A591" t="s">
-        <v>544</v>
-      </c>
-      <c r="B591" t="s">
-        <v>13</v>
-      </c>
-      <c r="C591" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A592" t="s">
-        <v>545</v>
-      </c>
-      <c r="B592" t="s">
-        <v>13</v>
-      </c>
-      <c r="C592" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A593" t="s">
-        <v>546</v>
-      </c>
-      <c r="B593" t="s">
-        <v>13</v>
-      </c>
-      <c r="C593" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A594" t="s">
-        <v>547</v>
-      </c>
-      <c r="B594" t="s">
-        <v>13</v>
-      </c>
-      <c r="C594" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C273" xr:uid="{4C50DCCC-8446-4FAC-BA76-D53F2D86B716}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C273">
     <sortCondition ref="C1:C273"/>
   </sortState>

--- a/Vehicle Catalogue.xlsx
+++ b/Vehicle Catalogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samhi\Documents\My Games\Sprocket\Ostfront Tank Collection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B69875A6-CB63-4757-A8CC-ED78FEA593E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D928BE8-D5E3-4994-9876-5CE18958A5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7600" yWindow="1710" windowWidth="28800" windowHeight="15360" xr2:uid="{3FAC36FE-B102-4B04-8548-70F58966D145}"/>
+    <workbookView xWindow="9600" yWindow="3180" windowWidth="28800" windowHeight="15360" xr2:uid="{3FAC36FE-B102-4B04-8548-70F58966D145}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Vehicle Catalogue.xlsx
+++ b/Vehicle Catalogue.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samhi\Documents\My Games\Sprocket\Ostfront Tank Collection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D928BE8-D5E3-4994-9876-5CE18958A5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1578C9-9583-4464-8FC8-D56E7976A68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9600" yWindow="3180" windowWidth="28800" windowHeight="15360" xr2:uid="{3FAC36FE-B102-4B04-8548-70F58966D145}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{3FAC36FE-B102-4B04-8548-70F58966D145}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$271</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$585</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="600">
   <si>
     <t>Tank</t>
   </si>
@@ -638,9 +638,6 @@
     <t>T-34-76 (1943)</t>
   </si>
   <si>
-    <t>T-34-85 (1944)</t>
-  </si>
-  <si>
     <t>T-44</t>
   </si>
   <si>
@@ -1082,9 +1079,6 @@
     <t>Chi-Se</t>
   </si>
   <si>
-    <t>E 75</t>
-  </si>
-  <si>
     <t>FV201 (A45)</t>
   </si>
   <si>
@@ -1337,9 +1331,6 @@
     <t>T82</t>
   </si>
   <si>
-    <t>Type 1 Ho-Ni II</t>
-  </si>
-  <si>
     <t>Type 5 Ke-Ho</t>
   </si>
   <si>
@@ -1700,9 +1691,6 @@
     <t>Type 98 So-Da</t>
   </si>
   <si>
-    <t>Char 2C Bis</t>
-  </si>
-  <si>
     <t>Char B1 Ter</t>
   </si>
   <si>
@@ -1851,6 +1839,9 @@
   </si>
   <si>
     <t>Strv m/40L</t>
+  </si>
+  <si>
+    <t>E-50</t>
   </si>
 </sst>
 </file>
@@ -2274,7 +2265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C50DCCC-8446-4FAC-BA76-D53F2D86B716}">
-  <dimension ref="A1:C588"/>
+  <dimension ref="A1:C585"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.81640625" customWidth="1"/>
@@ -2295,557 +2286,557 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B2" t="s">
         <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B3" t="s">
         <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>279</v>
+      </c>
+      <c r="B9" t="s">
         <v>280</v>
       </c>
-      <c r="B9" t="s">
-        <v>281</v>
-      </c>
       <c r="C9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B11" t="s">
         <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B12" t="s">
         <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B13" t="s">
         <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B16" t="s">
         <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B17" t="s">
         <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B18" t="s">
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B19" t="s">
         <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B20" t="s">
         <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B21" t="s">
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B22" t="s">
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>294</v>
+      </c>
+      <c r="B25" t="s">
         <v>295</v>
       </c>
-      <c r="B25" t="s">
-        <v>296</v>
-      </c>
       <c r="C25" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C26" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B27" t="s">
         <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B28" t="s">
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B29" t="s">
         <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B31" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C31" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B32" t="s">
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B33" t="s">
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s">
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s">
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s">
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B40" t="s">
         <v>7</v>
       </c>
       <c r="C40" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B41" t="s">
         <v>7</v>
       </c>
       <c r="C41" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s">
         <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B43" t="s">
         <v>7</v>
       </c>
       <c r="C43" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B44" t="s">
         <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B45" t="s">
         <v>7</v>
       </c>
       <c r="C45" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B46" t="s">
         <v>7</v>
       </c>
       <c r="C46" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B47" t="s">
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B48" t="s">
         <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B49" t="s">
         <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C50" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B51" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C51" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B52" t="s">
         <v>16</v>
@@ -2889,7 +2880,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B56" t="s">
         <v>11</v>
@@ -2900,7 +2891,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B57" t="s">
         <v>11</v>
@@ -2911,10 +2902,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B58" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C58" t="s">
         <v>8</v>
@@ -2955,249 +2946,249 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B62" t="s">
         <v>54</v>
       </c>
       <c r="C62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B63" t="s">
         <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B64" t="s">
         <v>4</v>
       </c>
       <c r="C64" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B65" t="s">
         <v>4</v>
       </c>
       <c r="C65" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B66" t="s">
         <v>7</v>
       </c>
       <c r="C66" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B67" t="s">
         <v>7</v>
       </c>
       <c r="C67" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B68" t="s">
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B69" t="s">
         <v>7</v>
       </c>
       <c r="C69" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B72" t="s">
         <v>16</v>
       </c>
       <c r="C72" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B73" t="s">
         <v>4</v>
       </c>
       <c r="C73" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B74" t="s">
         <v>7</v>
       </c>
       <c r="C74" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B75" t="s">
         <v>7</v>
       </c>
       <c r="C75" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B76" t="s">
         <v>7</v>
       </c>
       <c r="C76" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B77" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C77" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B78" t="s">
         <v>54</v>
       </c>
       <c r="C78" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B79" t="s">
         <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B80" t="s">
         <v>16</v>
       </c>
       <c r="C80" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B81" t="s">
         <v>16</v>
       </c>
       <c r="C81" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B82" t="s">
         <v>16</v>
       </c>
       <c r="C82" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B83" t="s">
         <v>7</v>
       </c>
       <c r="C83" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B84" t="s">
         <v>45</v>
@@ -3208,7 +3199,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B85" t="s">
         <v>45</v>
@@ -3219,7 +3210,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B86" t="s">
         <v>4</v>
@@ -3230,7 +3221,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B87" t="s">
         <v>45</v>
@@ -3241,7 +3232,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B88" t="s">
         <v>45</v>
@@ -3252,7 +3243,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B89" t="s">
         <v>4</v>
@@ -3263,7 +3254,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B90" t="s">
         <v>54</v>
@@ -3274,7 +3265,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B91" t="s">
         <v>4</v>
@@ -3285,10 +3276,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>553</v>
+        <v>344</v>
       </c>
       <c r="B92" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C92" t="s">
         <v>17</v>
@@ -3296,10 +3287,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>345</v>
+        <v>247</v>
       </c>
       <c r="B93" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C93" t="s">
         <v>17</v>
@@ -3307,10 +3298,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>248</v>
+        <v>15</v>
       </c>
       <c r="B94" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C94" t="s">
         <v>17</v>
@@ -3318,10 +3309,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>346</v>
+        <v>18</v>
       </c>
       <c r="B95" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C95" t="s">
         <v>17</v>
@@ -3329,10 +3320,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>15</v>
+        <v>345</v>
       </c>
       <c r="B96" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C96" t="s">
         <v>17</v>
@@ -3340,10 +3331,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>18</v>
+        <v>346</v>
       </c>
       <c r="B97" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C97" t="s">
         <v>17</v>
@@ -3354,7 +3345,7 @@
         <v>347</v>
       </c>
       <c r="B98" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C98" t="s">
         <v>17</v>
@@ -3373,10 +3364,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>349</v>
+        <v>550</v>
       </c>
       <c r="B100" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C100" t="s">
         <v>17</v>
@@ -3384,10 +3375,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>350</v>
+        <v>19</v>
       </c>
       <c r="B101" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C101" t="s">
         <v>17</v>
@@ -3395,7 +3386,7 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>554</v>
+        <v>20</v>
       </c>
       <c r="B102" t="s">
         <v>13</v>
@@ -3406,7 +3397,7 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B103" t="s">
         <v>13</v>
@@ -3417,7 +3408,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B104" t="s">
         <v>13</v>
@@ -3428,7 +3419,7 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B105" t="s">
         <v>13</v>
@@ -3439,7 +3430,7 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>22</v>
+        <v>551</v>
       </c>
       <c r="B106" t="s">
         <v>13</v>
@@ -3450,7 +3441,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>23</v>
+        <v>552</v>
       </c>
       <c r="B107" t="s">
         <v>13</v>
@@ -3461,7 +3452,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>555</v>
+        <v>24</v>
       </c>
       <c r="B108" t="s">
         <v>13</v>
@@ -3472,7 +3463,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>556</v>
+        <v>25</v>
       </c>
       <c r="B109" t="s">
         <v>13</v>
@@ -3483,7 +3474,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>24</v>
+        <v>553</v>
       </c>
       <c r="B110" t="s">
         <v>13</v>
@@ -3494,7 +3485,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B111" t="s">
         <v>13</v>
@@ -3505,7 +3496,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>557</v>
+        <v>233</v>
       </c>
       <c r="B112" t="s">
         <v>13</v>
@@ -3516,7 +3507,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>26</v>
+        <v>239</v>
       </c>
       <c r="B113" t="s">
         <v>13</v>
@@ -3527,10 +3518,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>234</v>
+        <v>349</v>
       </c>
       <c r="B114" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C114" t="s">
         <v>17</v>
@@ -3538,10 +3529,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>240</v>
+        <v>27</v>
       </c>
       <c r="B115" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C115" t="s">
         <v>17</v>
@@ -3549,10 +3540,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>351</v>
+        <v>28</v>
       </c>
       <c r="B116" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C116" t="s">
         <v>17</v>
@@ -3560,10 +3551,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B117" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C117" t="s">
         <v>17</v>
@@ -3571,7 +3562,7 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>28</v>
+        <v>554</v>
       </c>
       <c r="B118" t="s">
         <v>13</v>
@@ -3582,7 +3573,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>29</v>
+        <v>350</v>
       </c>
       <c r="B119" t="s">
         <v>13</v>
@@ -3592,8 +3583,8 @@
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>558</v>
+      <c r="A120" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="B120" t="s">
         <v>13</v>
@@ -3604,7 +3595,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>352</v>
+        <v>231</v>
       </c>
       <c r="B121" t="s">
         <v>13</v>
@@ -3614,8 +3605,8 @@
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A122" s="2" t="s">
-        <v>232</v>
+      <c r="A122" t="s">
+        <v>351</v>
       </c>
       <c r="B122" t="s">
         <v>13</v>
@@ -3626,7 +3617,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>232</v>
+        <v>555</v>
       </c>
       <c r="B123" t="s">
         <v>13</v>
@@ -3637,7 +3628,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>353</v>
+        <v>30</v>
       </c>
       <c r="B124" t="s">
         <v>13</v>
@@ -3648,7 +3639,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>559</v>
+        <v>31</v>
       </c>
       <c r="B125" t="s">
         <v>13</v>
@@ -3659,7 +3650,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B126" t="s">
         <v>13</v>
@@ -3670,7 +3661,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>31</v>
+        <v>234</v>
       </c>
       <c r="B127" t="s">
         <v>13</v>
@@ -3681,10 +3672,10 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B128" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C128" t="s">
         <v>17</v>
@@ -3692,10 +3683,10 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>235</v>
+        <v>33</v>
       </c>
       <c r="B129" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C129" t="s">
         <v>17</v>
@@ -3703,10 +3694,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>33</v>
+        <v>556</v>
       </c>
       <c r="B130" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C130" t="s">
         <v>17</v>
@@ -3714,7 +3705,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
       <c r="B131" t="s">
         <v>16</v>
@@ -3725,10 +3716,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>560</v>
+        <v>353</v>
       </c>
       <c r="B132" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C132" t="s">
         <v>17</v>
@@ -3739,7 +3730,7 @@
         <v>354</v>
       </c>
       <c r="B133" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C133" t="s">
         <v>17</v>
@@ -3747,7 +3738,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>355</v>
+        <v>34</v>
       </c>
       <c r="B134" t="s">
         <v>13</v>
@@ -3758,7 +3749,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B135" t="s">
         <v>13</v>
@@ -3769,7 +3760,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>34</v>
+        <v>356</v>
       </c>
       <c r="B136" t="s">
         <v>13</v>
@@ -3794,7 +3785,7 @@
         <v>358</v>
       </c>
       <c r="B138" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C138" t="s">
         <v>17</v>
@@ -3802,10 +3793,10 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>359</v>
+        <v>254</v>
       </c>
       <c r="B139" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
@@ -3813,10 +3804,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B140" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
@@ -3824,7 +3815,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>255</v>
+        <v>557</v>
       </c>
       <c r="B141" t="s">
         <v>16</v>
@@ -3835,10 +3826,10 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>361</v>
+        <v>35</v>
       </c>
       <c r="B142" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C142" t="s">
         <v>17</v>
@@ -3846,10 +3837,10 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B143" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C143" t="s">
         <v>17</v>
@@ -3857,10 +3848,10 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>35</v>
+        <v>253</v>
       </c>
       <c r="B144" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
@@ -3868,10 +3859,10 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>562</v>
+        <v>252</v>
       </c>
       <c r="B145" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
@@ -3879,18 +3870,18 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="B146" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
-        <v>253</v>
+      <c r="A147" s="3" t="s">
+        <v>258</v>
       </c>
       <c r="B147" t="s">
         <v>16</v>
@@ -3901,18 +3892,18 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="B148" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A149" s="3" t="s">
-        <v>259</v>
+      <c r="A149" t="s">
+        <v>264</v>
       </c>
       <c r="B149" t="s">
         <v>16</v>
@@ -3923,7 +3914,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>260</v>
+        <v>559</v>
       </c>
       <c r="B150" t="s">
         <v>16</v>
@@ -3934,10 +3925,10 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>265</v>
+        <v>36</v>
       </c>
       <c r="B151" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C151" t="s">
         <v>17</v>
@@ -3945,10 +3936,10 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>563</v>
+        <v>360</v>
       </c>
       <c r="B152" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C152" t="s">
         <v>17</v>
@@ -3956,7 +3947,7 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>36</v>
+        <v>361</v>
       </c>
       <c r="B153" t="s">
         <v>13</v>
@@ -3967,10 +3958,10 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>362</v>
+        <v>260</v>
       </c>
       <c r="B154" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C154" t="s">
         <v>17</v>
@@ -3978,10 +3969,10 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>363</v>
+        <v>37</v>
       </c>
       <c r="B155" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C155" t="s">
         <v>17</v>
@@ -3989,7 +3980,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>261</v>
+        <v>37</v>
       </c>
       <c r="B156" t="s">
         <v>16</v>
@@ -4000,7 +3991,7 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B157" t="s">
         <v>16</v>
@@ -4011,10 +4002,10 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>37</v>
+        <v>362</v>
       </c>
       <c r="B158" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C158" t="s">
         <v>17</v>
@@ -4022,10 +4013,10 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>38</v>
+        <v>363</v>
       </c>
       <c r="B159" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C159" t="s">
         <v>17</v>
@@ -4044,7 +4035,7 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>365</v>
+        <v>235</v>
       </c>
       <c r="B161" t="s">
         <v>13</v>
@@ -4055,7 +4046,7 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>366</v>
+        <v>236</v>
       </c>
       <c r="B162" t="s">
         <v>13</v>
@@ -4066,7 +4057,7 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>236</v>
+        <v>39</v>
       </c>
       <c r="B163" t="s">
         <v>13</v>
@@ -4077,7 +4068,7 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>237</v>
+        <v>39</v>
       </c>
       <c r="B164" t="s">
         <v>13</v>
@@ -4088,7 +4079,7 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B165" t="s">
         <v>13</v>
@@ -4099,7 +4090,7 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>39</v>
+        <v>365</v>
       </c>
       <c r="B166" t="s">
         <v>13</v>
@@ -4110,7 +4101,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>40</v>
+        <v>366</v>
       </c>
       <c r="B167" t="s">
         <v>13</v>
@@ -4124,7 +4115,7 @@
         <v>367</v>
       </c>
       <c r="B168" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C168" t="s">
         <v>17</v>
@@ -4157,7 +4148,7 @@
         <v>370</v>
       </c>
       <c r="B171" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C171" t="s">
         <v>17</v>
@@ -4176,7 +4167,7 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>372</v>
+        <v>560</v>
       </c>
       <c r="B173" t="s">
         <v>7</v>
@@ -4187,10 +4178,10 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>373</v>
+        <v>41</v>
       </c>
       <c r="B174" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C174" t="s">
         <v>17</v>
@@ -4198,10 +4189,10 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>564</v>
+        <v>42</v>
       </c>
       <c r="B175" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C175" t="s">
         <v>17</v>
@@ -4209,7 +4200,7 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>41</v>
+        <v>561</v>
       </c>
       <c r="B176" t="s">
         <v>13</v>
@@ -4220,10 +4211,10 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>42</v>
+        <v>562</v>
       </c>
       <c r="B177" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C177" t="s">
         <v>17</v>
@@ -4231,10 +4222,10 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B178" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C178" t="s">
         <v>17</v>
@@ -4242,7 +4233,7 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>566</v>
+        <v>241</v>
       </c>
       <c r="B179" t="s">
         <v>7</v>
@@ -4253,10 +4244,10 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>567</v>
+        <v>43</v>
       </c>
       <c r="B180" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C180" t="s">
         <v>17</v>
@@ -4264,10 +4255,10 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>242</v>
+        <v>44</v>
       </c>
       <c r="B181" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C181" t="s">
         <v>17</v>
@@ -4275,7 +4266,7 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>43</v>
+        <v>232</v>
       </c>
       <c r="B182" t="s">
         <v>16</v>
@@ -4286,10 +4277,10 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>44</v>
+        <v>372</v>
       </c>
       <c r="B183" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C183" t="s">
         <v>17</v>
@@ -4297,10 +4288,10 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="B184" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C184" t="s">
         <v>17</v>
@@ -4308,7 +4299,7 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B185" t="s">
         <v>11</v>
@@ -4319,7 +4310,7 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>270</v>
+        <v>46</v>
       </c>
       <c r="B186" t="s">
         <v>11</v>
@@ -4330,7 +4321,7 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>375</v>
+        <v>47</v>
       </c>
       <c r="B187" t="s">
         <v>11</v>
@@ -4341,10 +4332,10 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B188" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C188" t="s">
         <v>17</v>
@@ -4352,10 +4343,10 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>47</v>
+        <v>374</v>
       </c>
       <c r="B189" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C189" t="s">
         <v>17</v>
@@ -4363,10 +4354,10 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>48</v>
+        <v>375</v>
       </c>
       <c r="B190" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C190" t="s">
         <v>17</v>
@@ -4396,7 +4387,7 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>378</v>
+        <v>534</v>
       </c>
       <c r="B193" t="s">
         <v>16</v>
@@ -4407,7 +4398,7 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B194" t="s">
         <v>16</v>
@@ -4418,7 +4409,7 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>537</v>
+        <v>251</v>
       </c>
       <c r="B195" t="s">
         <v>16</v>
@@ -4429,7 +4420,7 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>380</v>
+        <v>49</v>
       </c>
       <c r="B196" t="s">
         <v>16</v>
@@ -4440,7 +4431,7 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>252</v>
+        <v>379</v>
       </c>
       <c r="B197" t="s">
         <v>16</v>
@@ -4451,10 +4442,10 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>49</v>
+        <v>380</v>
       </c>
       <c r="B198" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="C198" t="s">
         <v>17</v>
@@ -4473,32 +4464,32 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>382</v>
+        <v>271</v>
       </c>
       <c r="B200" t="s">
-        <v>538</v>
+        <v>104</v>
       </c>
       <c r="C200" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B201" t="s">
-        <v>16</v>
+        <v>227</v>
       </c>
       <c r="C201" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>272</v>
+        <v>383</v>
       </c>
       <c r="B202" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="C202" t="s">
         <v>51</v>
@@ -4506,10 +4497,10 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>384</v>
+        <v>564</v>
       </c>
       <c r="B203" t="s">
-        <v>228</v>
+        <v>4</v>
       </c>
       <c r="C203" t="s">
         <v>51</v>
@@ -4517,10 +4508,10 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B204" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C204" t="s">
         <v>51</v>
@@ -4528,7 +4519,7 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>568</v>
+        <v>385</v>
       </c>
       <c r="B205" t="s">
         <v>4</v>
@@ -4542,7 +4533,7 @@
         <v>386</v>
       </c>
       <c r="B206" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C206" t="s">
         <v>51</v>
@@ -4553,7 +4544,7 @@
         <v>387</v>
       </c>
       <c r="B207" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C207" t="s">
         <v>51</v>
@@ -4561,10 +4552,10 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>388</v>
+        <v>50</v>
       </c>
       <c r="B208" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C208" t="s">
         <v>51</v>
@@ -4572,10 +4563,10 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>389</v>
+        <v>256</v>
       </c>
       <c r="B209" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C209" t="s">
         <v>51</v>
@@ -4583,7 +4574,7 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B210" t="s">
         <v>4</v>
@@ -4594,10 +4585,10 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>257</v>
+        <v>389</v>
       </c>
       <c r="B211" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C211" t="s">
         <v>51</v>
@@ -4605,10 +4596,10 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B212" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C212" t="s">
         <v>51</v>
@@ -4616,10 +4607,10 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B213" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C213" t="s">
         <v>51</v>
@@ -4627,10 +4618,10 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B214" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C214" t="s">
         <v>51</v>
@@ -4638,7 +4629,7 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>392</v>
+        <v>56</v>
       </c>
       <c r="B215" t="s">
         <v>16</v>
@@ -4649,10 +4640,10 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>55</v>
+        <v>391</v>
       </c>
       <c r="B216" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C216" t="s">
         <v>51</v>
@@ -4660,7 +4651,7 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>56</v>
+        <v>392</v>
       </c>
       <c r="B217" t="s">
         <v>16</v>
@@ -4671,10 +4662,10 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>393</v>
+        <v>57</v>
       </c>
       <c r="B218" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C218" t="s">
         <v>51</v>
@@ -4682,10 +4673,10 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B219" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C219" t="s">
         <v>51</v>
@@ -4693,7 +4684,7 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B220" t="s">
         <v>16</v>
@@ -4704,10 +4695,10 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>395</v>
+        <v>222</v>
       </c>
       <c r="B221" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="C221" t="s">
         <v>51</v>
@@ -4715,10 +4706,10 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>58</v>
+        <v>394</v>
       </c>
       <c r="B222" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C222" t="s">
         <v>51</v>
@@ -4726,10 +4717,10 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>223</v>
+        <v>395</v>
       </c>
       <c r="B223" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C223" t="s">
         <v>51</v>
@@ -4737,10 +4728,10 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>396</v>
+        <v>592</v>
       </c>
       <c r="B224" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C224" t="s">
         <v>51</v>
@@ -4748,10 +4739,10 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>397</v>
+        <v>565</v>
       </c>
       <c r="B225" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C225" t="s">
         <v>51</v>
@@ -4759,7 +4750,7 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>596</v>
+        <v>566</v>
       </c>
       <c r="B226" t="s">
         <v>7</v>
@@ -4770,7 +4761,7 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>569</v>
+        <v>59</v>
       </c>
       <c r="B227" t="s">
         <v>7</v>
@@ -4781,7 +4772,7 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B228" t="s">
         <v>7</v>
@@ -4792,7 +4783,7 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>59</v>
+        <v>242</v>
       </c>
       <c r="B229" t="s">
         <v>7</v>
@@ -4803,7 +4794,7 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>571</v>
+        <v>60</v>
       </c>
       <c r="B230" t="s">
         <v>7</v>
@@ -4814,7 +4805,7 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>243</v>
+        <v>568</v>
       </c>
       <c r="B231" t="s">
         <v>7</v>
@@ -4825,7 +4816,7 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>60</v>
+        <v>396</v>
       </c>
       <c r="B232" t="s">
         <v>7</v>
@@ -4836,7 +4827,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>572</v>
+        <v>61</v>
       </c>
       <c r="B233" t="s">
         <v>7</v>
@@ -4847,7 +4838,7 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B234" t="s">
         <v>7</v>
@@ -4858,7 +4849,7 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>61</v>
+        <v>398</v>
       </c>
       <c r="B235" t="s">
         <v>7</v>
@@ -4869,7 +4860,7 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>399</v>
+        <v>62</v>
       </c>
       <c r="B236" t="s">
         <v>7</v>
@@ -4880,7 +4871,7 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B237" t="s">
         <v>7</v>
@@ -4891,10 +4882,10 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B238" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C238" t="s">
         <v>51</v>
@@ -4902,10 +4893,10 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>401</v>
+        <v>64</v>
       </c>
       <c r="B239" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C239" t="s">
         <v>51</v>
@@ -4913,7 +4904,7 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B240" t="s">
         <v>16</v>
@@ -4924,7 +4915,7 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B241" t="s">
         <v>16</v>
@@ -4935,10 +4926,10 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B242" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C242" t="s">
         <v>51</v>
@@ -4946,7 +4937,7 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>66</v>
+        <v>400</v>
       </c>
       <c r="B243" t="s">
         <v>16</v>
@@ -4957,10 +4948,10 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>67</v>
+        <v>401</v>
       </c>
       <c r="B244" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C244" t="s">
         <v>51</v>
@@ -4971,7 +4962,7 @@
         <v>402</v>
       </c>
       <c r="B245" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C245" t="s">
         <v>51</v>
@@ -4979,10 +4970,10 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>403</v>
+        <v>228</v>
       </c>
       <c r="B246" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C246" t="s">
         <v>51</v>
@@ -4990,10 +4981,10 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>404</v>
+        <v>68</v>
       </c>
       <c r="B247" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C247" t="s">
         <v>51</v>
@@ -5001,10 +4992,10 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>229</v>
+        <v>69</v>
       </c>
       <c r="B248" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C248" t="s">
         <v>51</v>
@@ -5012,7 +5003,7 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B249" t="s">
         <v>16</v>
@@ -5023,7 +5014,7 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B250" t="s">
         <v>16</v>
@@ -5034,7 +5025,7 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B251" t="s">
         <v>16</v>
@@ -5045,7 +5036,7 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B252" t="s">
         <v>16</v>
@@ -5056,7 +5047,7 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B253" t="s">
         <v>16</v>
@@ -5067,7 +5058,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>73</v>
+        <v>257</v>
       </c>
       <c r="B254" t="s">
         <v>16</v>
@@ -5078,10 +5069,10 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>74</v>
+        <v>403</v>
       </c>
       <c r="B255" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="C255" t="s">
         <v>51</v>
@@ -5089,10 +5080,10 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>258</v>
+        <v>593</v>
       </c>
       <c r="B256" t="s">
-        <v>16</v>
+        <v>295</v>
       </c>
       <c r="C256" t="s">
         <v>51</v>
@@ -5100,10 +5091,10 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B257" t="s">
-        <v>538</v>
+        <v>16</v>
       </c>
       <c r="C257" t="s">
         <v>51</v>
@@ -5111,10 +5102,10 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>597</v>
+        <v>75</v>
       </c>
       <c r="B258" t="s">
-        <v>296</v>
+        <v>4</v>
       </c>
       <c r="C258" t="s">
         <v>51</v>
@@ -5122,7 +5113,7 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B259" t="s">
         <v>16</v>
@@ -5133,10 +5124,10 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>75</v>
+        <v>255</v>
       </c>
       <c r="B260" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C260" t="s">
         <v>51</v>
@@ -5144,10 +5135,10 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>407</v>
+        <v>76</v>
       </c>
       <c r="B261" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C261" t="s">
         <v>51</v>
@@ -5155,10 +5146,10 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>256</v>
+        <v>77</v>
       </c>
       <c r="B262" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C262" t="s">
         <v>51</v>
@@ -5166,7 +5157,7 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>76</v>
+        <v>406</v>
       </c>
       <c r="B263" t="s">
         <v>4</v>
@@ -5177,10 +5168,10 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>77</v>
+        <v>407</v>
       </c>
       <c r="B264" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C264" t="s">
         <v>51</v>
@@ -5199,10 +5190,10 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>409</v>
+        <v>594</v>
       </c>
       <c r="B266" t="s">
-        <v>4</v>
+        <v>295</v>
       </c>
       <c r="C266" t="s">
         <v>51</v>
@@ -5210,10 +5201,10 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B267" t="s">
-        <v>4</v>
+        <v>295</v>
       </c>
       <c r="C267" t="s">
         <v>51</v>
@@ -5221,10 +5212,10 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>598</v>
+        <v>78</v>
       </c>
       <c r="B268" t="s">
-        <v>296</v>
+        <v>16</v>
       </c>
       <c r="C268" t="s">
         <v>51</v>
@@ -5232,10 +5223,10 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>411</v>
+        <v>79</v>
       </c>
       <c r="B269" t="s">
-        <v>296</v>
+        <v>16</v>
       </c>
       <c r="C269" t="s">
         <v>51</v>
@@ -5243,10 +5234,10 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B270" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C270" t="s">
         <v>51</v>
@@ -5254,10 +5245,10 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="B271" t="s">
-        <v>16</v>
+        <v>535</v>
       </c>
       <c r="C271" t="s">
         <v>51</v>
@@ -5265,10 +5256,10 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>80</v>
+        <v>411</v>
       </c>
       <c r="B272" t="s">
-        <v>54</v>
+        <v>535</v>
       </c>
       <c r="C272" t="s">
         <v>51</v>
@@ -5276,10 +5267,10 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>412</v>
+        <v>569</v>
       </c>
       <c r="B273" t="s">
-        <v>538</v>
+        <v>295</v>
       </c>
       <c r="C273" t="s">
         <v>51</v>
@@ -5287,10 +5278,10 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>413</v>
+        <v>81</v>
       </c>
       <c r="B274" t="s">
-        <v>538</v>
+        <v>16</v>
       </c>
       <c r="C274" t="s">
         <v>51</v>
@@ -5298,10 +5289,10 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>573</v>
+        <v>412</v>
       </c>
       <c r="B275" t="s">
-        <v>296</v>
+        <v>16</v>
       </c>
       <c r="C275" t="s">
         <v>51</v>
@@ -5309,10 +5300,10 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>81</v>
+        <v>595</v>
       </c>
       <c r="B276" t="s">
-        <v>16</v>
+        <v>295</v>
       </c>
       <c r="C276" t="s">
         <v>51</v>
@@ -5320,10 +5311,10 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>414</v>
+        <v>596</v>
       </c>
       <c r="B277" t="s">
-        <v>16</v>
+        <v>295</v>
       </c>
       <c r="C277" t="s">
         <v>51</v>
@@ -5331,10 +5322,10 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B278" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C278" t="s">
         <v>51</v>
@@ -5342,10 +5333,10 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B279" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C279" t="s">
         <v>51</v>
@@ -5353,10 +5344,10 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>601</v>
+        <v>82</v>
       </c>
       <c r="B280" t="s">
-        <v>296</v>
+        <v>16</v>
       </c>
       <c r="C280" t="s">
         <v>51</v>
@@ -5364,10 +5355,10 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>602</v>
+        <v>413</v>
       </c>
       <c r="B281" t="s">
-        <v>296</v>
+        <v>13</v>
       </c>
       <c r="C281" t="s">
         <v>51</v>
@@ -5375,10 +5366,10 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B282" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C282" t="s">
         <v>51</v>
@@ -5386,10 +5377,10 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B283" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C283" t="s">
         <v>51</v>
@@ -5397,10 +5388,10 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>83</v>
+        <v>415</v>
       </c>
       <c r="B284" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C284" t="s">
         <v>51</v>
@@ -5411,7 +5402,7 @@
         <v>416</v>
       </c>
       <c r="B285" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C285" t="s">
         <v>51</v>
@@ -5419,7 +5410,7 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>417</v>
+        <v>84</v>
       </c>
       <c r="B286" t="s">
         <v>13</v>
@@ -5430,10 +5421,10 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="B287" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C287" t="s">
         <v>51</v>
@@ -5441,10 +5432,10 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>84</v>
+        <v>417</v>
       </c>
       <c r="B288" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C288" t="s">
         <v>51</v>
@@ -5452,10 +5443,10 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>84</v>
+        <v>418</v>
       </c>
       <c r="B289" t="s">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="C289" t="s">
         <v>51</v>
@@ -5485,10 +5476,10 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>421</v>
+        <v>86</v>
       </c>
       <c r="B292" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C292" t="s">
         <v>51</v>
@@ -5496,10 +5487,10 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>422</v>
+        <v>87</v>
       </c>
       <c r="B293" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C293" t="s">
         <v>51</v>
@@ -5507,10 +5498,10 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>86</v>
+        <v>421</v>
       </c>
       <c r="B294" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C294" t="s">
         <v>51</v>
@@ -5518,7 +5509,7 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B295" t="s">
         <v>13</v>
@@ -5529,10 +5520,10 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B296" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C296" t="s">
         <v>51</v>
@@ -5540,7 +5531,7 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>88</v>
+        <v>423</v>
       </c>
       <c r="B297" t="s">
         <v>13</v>
@@ -5562,7 +5553,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>425</v>
+        <v>570</v>
       </c>
       <c r="B299" t="s">
         <v>13</v>
@@ -5573,10 +5564,10 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B300" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C300" t="s">
         <v>51</v>
@@ -5584,7 +5575,7 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>574</v>
+        <v>89</v>
       </c>
       <c r="B301" t="s">
         <v>13</v>
@@ -5595,10 +5586,10 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>427</v>
+        <v>90</v>
       </c>
       <c r="B302" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C302" t="s">
         <v>51</v>
@@ -5606,10 +5597,10 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>89</v>
+        <v>426</v>
       </c>
       <c r="B303" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C303" t="s">
         <v>51</v>
@@ -5617,10 +5608,10 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>90</v>
+        <v>427</v>
       </c>
       <c r="B304" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C304" t="s">
         <v>51</v>
@@ -5628,10 +5619,10 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>428</v>
+        <v>91</v>
       </c>
       <c r="B305" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C305" t="s">
         <v>51</v>
@@ -5639,10 +5630,10 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>429</v>
+        <v>92</v>
       </c>
       <c r="B306" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C306" t="s">
         <v>51</v>
@@ -5650,10 +5641,10 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="B307" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C307" t="s">
         <v>51</v>
@@ -5661,7 +5652,7 @@
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B308" t="s">
         <v>13</v>
@@ -5672,7 +5663,7 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>244</v>
+        <v>428</v>
       </c>
       <c r="B309" t="s">
         <v>7</v>
@@ -5683,10 +5674,10 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>93</v>
+        <v>571</v>
       </c>
       <c r="B310" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C310" t="s">
         <v>51</v>
@@ -5694,10 +5685,10 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>430</v>
+        <v>94</v>
       </c>
       <c r="B311" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C311" t="s">
         <v>51</v>
@@ -5705,7 +5696,7 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>431</v>
+        <v>268</v>
       </c>
       <c r="B312" t="s">
         <v>11</v>
@@ -5716,7 +5707,7 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B313" t="s">
         <v>11</v>
@@ -5727,7 +5718,7 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>94</v>
+        <v>429</v>
       </c>
       <c r="B314" t="s">
         <v>11</v>
@@ -5738,7 +5729,7 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>269</v>
+        <v>573</v>
       </c>
       <c r="B315" t="s">
         <v>11</v>
@@ -5749,7 +5740,7 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>576</v>
+        <v>95</v>
       </c>
       <c r="B316" t="s">
         <v>11</v>
@@ -5760,7 +5751,7 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>432</v>
+        <v>574</v>
       </c>
       <c r="B317" t="s">
         <v>11</v>
@@ -5771,7 +5762,7 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>577</v>
+        <v>430</v>
       </c>
       <c r="B318" t="s">
         <v>11</v>
@@ -5782,7 +5773,7 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B319" t="s">
         <v>11</v>
@@ -5793,7 +5784,7 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B320" t="s">
         <v>11</v>
@@ -5804,10 +5795,10 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>433</v>
+        <v>99</v>
       </c>
       <c r="B321" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C321" t="s">
         <v>51</v>
@@ -5815,10 +5806,10 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B322" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C322" t="s">
         <v>51</v>
@@ -5826,10 +5817,10 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>579</v>
+        <v>101</v>
       </c>
       <c r="B323" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C323" t="s">
         <v>51</v>
@@ -5837,10 +5828,10 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>99</v>
+        <v>431</v>
       </c>
       <c r="B324" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C324" t="s">
         <v>51</v>
@@ -5848,10 +5839,10 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>100</v>
+        <v>432</v>
       </c>
       <c r="B325" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C325" t="s">
         <v>51</v>
@@ -5859,10 +5850,10 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B326" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C326" t="s">
         <v>51</v>
@@ -5870,10 +5861,10 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>434</v>
+        <v>238</v>
       </c>
       <c r="B327" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C327" t="s">
         <v>51</v>
@@ -5881,10 +5872,10 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>435</v>
+        <v>576</v>
       </c>
       <c r="B328" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C328" t="s">
         <v>51</v>
@@ -5892,43 +5883,43 @@
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>102</v>
+        <v>248</v>
       </c>
       <c r="B329" t="s">
-        <v>13</v>
+        <v>227</v>
       </c>
       <c r="C329" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>239</v>
+        <v>433</v>
       </c>
       <c r="B330" t="s">
-        <v>13</v>
+        <v>227</v>
       </c>
       <c r="C330" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>580</v>
+        <v>103</v>
       </c>
       <c r="B331" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="C331" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>249</v>
+        <v>106</v>
       </c>
       <c r="B332" t="s">
-        <v>228</v>
+        <v>104</v>
       </c>
       <c r="C332" t="s">
         <v>105</v>
@@ -5936,10 +5927,10 @@
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B333" t="s">
-        <v>228</v>
+        <v>45</v>
       </c>
       <c r="C333" t="s">
         <v>105</v>
@@ -5947,10 +5938,10 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>103</v>
+        <v>435</v>
       </c>
       <c r="B334" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="C334" t="s">
         <v>105</v>
@@ -5958,10 +5949,10 @@
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>106</v>
+        <v>436</v>
       </c>
       <c r="B335" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="C335" t="s">
         <v>105</v>
@@ -5972,7 +5963,7 @@
         <v>437</v>
       </c>
       <c r="B336" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C336" t="s">
         <v>105</v>
@@ -5983,7 +5974,7 @@
         <v>438</v>
       </c>
       <c r="B337" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C337" t="s">
         <v>105</v>
@@ -6005,7 +5996,7 @@
         <v>440</v>
       </c>
       <c r="B339" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C339" t="s">
         <v>105</v>
@@ -6027,7 +6018,7 @@
         <v>442</v>
       </c>
       <c r="B341" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C341" t="s">
         <v>105</v>
@@ -6038,7 +6029,7 @@
         <v>443</v>
       </c>
       <c r="B342" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C342" t="s">
         <v>105</v>
@@ -6049,7 +6040,7 @@
         <v>444</v>
       </c>
       <c r="B343" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C343" t="s">
         <v>105</v>
@@ -6057,10 +6048,10 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>445</v>
+        <v>388</v>
       </c>
       <c r="B344" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C344" t="s">
         <v>105</v>
@@ -6068,10 +6059,10 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B345" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C345" t="s">
         <v>105</v>
@@ -6079,10 +6070,10 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>447</v>
+        <v>107</v>
       </c>
       <c r="B346" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C346" t="s">
         <v>105</v>
@@ -6090,10 +6081,10 @@
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>390</v>
+        <v>108</v>
       </c>
       <c r="B347" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C347" t="s">
         <v>105</v>
@@ -6101,10 +6092,10 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>448</v>
+        <v>109</v>
       </c>
       <c r="B348" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C348" t="s">
         <v>105</v>
@@ -6112,7 +6103,7 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B349" t="s">
         <v>45</v>
@@ -6123,10 +6114,10 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>108</v>
+        <v>446</v>
       </c>
       <c r="B350" t="s">
-        <v>45</v>
+        <v>227</v>
       </c>
       <c r="C350" t="s">
         <v>105</v>
@@ -6134,10 +6125,10 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>109</v>
+        <v>599</v>
       </c>
       <c r="B351" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C351" t="s">
         <v>105</v>
@@ -6145,10 +6136,10 @@
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B352" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C352" t="s">
         <v>105</v>
@@ -6156,10 +6147,10 @@
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>449</v>
+        <v>112</v>
       </c>
       <c r="B353" t="s">
-        <v>228</v>
+        <v>16</v>
       </c>
       <c r="C353" t="s">
         <v>105</v>
@@ -6167,7 +6158,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>111</v>
+        <v>261</v>
       </c>
       <c r="B354" t="s">
         <v>16</v>
@@ -6178,7 +6169,7 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B355" t="s">
         <v>16</v>
@@ -6189,7 +6180,7 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>262</v>
+        <v>114</v>
       </c>
       <c r="B356" t="s">
         <v>16</v>
@@ -6200,7 +6191,7 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>113</v>
+        <v>262</v>
       </c>
       <c r="B357" t="s">
         <v>16</v>
@@ -6211,7 +6202,7 @@
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="B358" t="s">
         <v>16</v>
@@ -6222,7 +6213,7 @@
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>263</v>
+        <v>115</v>
       </c>
       <c r="B359" t="s">
         <v>16</v>
@@ -6233,7 +6224,7 @@
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>264</v>
+        <v>447</v>
       </c>
       <c r="B360" t="s">
         <v>16</v>
@@ -6244,7 +6235,7 @@
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B361" t="s">
         <v>16</v>
@@ -6255,10 +6246,10 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B362" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C362" t="s">
         <v>105</v>
@@ -6266,7 +6257,7 @@
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A363" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B363" t="s">
         <v>16</v>
@@ -6277,10 +6268,10 @@
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>451</v>
+        <v>118</v>
       </c>
       <c r="B364" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C364" t="s">
         <v>105</v>
@@ -6288,7 +6279,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B365" t="s">
         <v>16</v>
@@ -6299,7 +6290,7 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B366" t="s">
         <v>16</v>
@@ -6310,7 +6301,7 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>119</v>
+        <v>449</v>
       </c>
       <c r="B367" t="s">
         <v>16</v>
@@ -6321,10 +6312,10 @@
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="B368" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C368" t="s">
         <v>105</v>
@@ -6332,10 +6323,10 @@
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B369" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C369" t="s">
         <v>105</v>
@@ -6343,10 +6334,10 @@
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>453</v>
+        <v>121</v>
       </c>
       <c r="B370" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C370" t="s">
         <v>105</v>
@@ -6354,10 +6345,10 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B371" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C371" t="s">
         <v>105</v>
@@ -6365,10 +6356,10 @@
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B372" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C372" t="s">
         <v>105</v>
@@ -6376,10 +6367,10 @@
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B373" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C373" t="s">
         <v>105</v>
@@ -6387,7 +6378,7 @@
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>122</v>
+        <v>577</v>
       </c>
       <c r="B374" t="s">
         <v>7</v>
@@ -6398,7 +6389,7 @@
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>456</v>
+        <v>578</v>
       </c>
       <c r="B375" t="s">
         <v>7</v>
@@ -6409,7 +6400,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>581</v>
+        <v>454</v>
       </c>
       <c r="B376" t="s">
         <v>7</v>
@@ -6420,7 +6411,7 @@
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>582</v>
+        <v>123</v>
       </c>
       <c r="B377" t="s">
         <v>7</v>
@@ -6431,7 +6422,7 @@
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>457</v>
+        <v>124</v>
       </c>
       <c r="B378" t="s">
         <v>7</v>
@@ -6442,7 +6433,7 @@
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B379" t="s">
         <v>7</v>
@@ -6453,7 +6444,7 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B380" t="s">
         <v>7</v>
@@ -6464,7 +6455,7 @@
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B381" t="s">
         <v>7</v>
@@ -6475,7 +6466,7 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B382" t="s">
         <v>7</v>
@@ -6486,7 +6477,7 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>127</v>
+        <v>455</v>
       </c>
       <c r="B383" t="s">
         <v>7</v>
@@ -6497,7 +6488,7 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>128</v>
+        <v>456</v>
       </c>
       <c r="B384" t="s">
         <v>7</v>
@@ -6508,7 +6499,7 @@
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>458</v>
+        <v>129</v>
       </c>
       <c r="B385" t="s">
         <v>7</v>
@@ -6519,7 +6510,7 @@
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>459</v>
+        <v>130</v>
       </c>
       <c r="B386" t="s">
         <v>7</v>
@@ -6530,7 +6521,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B387" t="s">
         <v>7</v>
@@ -6541,7 +6532,7 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B388" t="s">
         <v>7</v>
@@ -6552,7 +6543,7 @@
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B389" t="s">
         <v>7</v>
@@ -6563,7 +6554,7 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B390" t="s">
         <v>7</v>
@@ -6574,7 +6565,7 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B391" t="s">
         <v>7</v>
@@ -6585,7 +6576,7 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B392" t="s">
         <v>7</v>
@@ -6596,7 +6587,7 @@
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B393" t="s">
         <v>7</v>
@@ -6607,7 +6598,7 @@
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B394" t="s">
         <v>7</v>
@@ -6618,7 +6609,7 @@
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B395" t="s">
         <v>7</v>
@@ -6629,7 +6620,7 @@
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B396" t="s">
         <v>7</v>
@@ -6640,7 +6631,7 @@
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B397" t="s">
         <v>7</v>
@@ -6651,7 +6642,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B398" t="s">
         <v>7</v>
@@ -6662,7 +6653,7 @@
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B399" t="s">
         <v>7</v>
@@ -6673,7 +6664,7 @@
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B400" t="s">
         <v>7</v>
@@ -6684,7 +6675,7 @@
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B401" t="s">
         <v>7</v>
@@ -6695,7 +6686,7 @@
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B402" t="s">
         <v>7</v>
@@ -6706,7 +6697,7 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B403" t="s">
         <v>7</v>
@@ -6717,7 +6708,7 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B404" t="s">
         <v>7</v>
@@ -6728,10 +6719,10 @@
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>147</v>
+        <v>579</v>
       </c>
       <c r="B405" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C405" t="s">
         <v>105</v>
@@ -6739,10 +6730,10 @@
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>148</v>
+        <v>244</v>
       </c>
       <c r="B406" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C406" t="s">
         <v>105</v>
@@ -6750,7 +6741,7 @@
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>583</v>
+        <v>149</v>
       </c>
       <c r="B407" t="s">
         <v>45</v>
@@ -6761,7 +6752,7 @@
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>245</v>
+        <v>150</v>
       </c>
       <c r="B408" t="s">
         <v>45</v>
@@ -6772,7 +6763,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B409" t="s">
         <v>45</v>
@@ -6783,7 +6774,7 @@
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B410" t="s">
         <v>45</v>
@@ -6794,7 +6785,7 @@
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B411" t="s">
         <v>45</v>
@@ -6805,7 +6796,7 @@
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B412" t="s">
         <v>45</v>
@@ -6816,10 +6807,10 @@
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>153</v>
+        <v>228</v>
       </c>
       <c r="B413" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C413" t="s">
         <v>105</v>
@@ -6827,10 +6818,10 @@
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>154</v>
+        <v>457</v>
       </c>
       <c r="B414" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C414" t="s">
         <v>105</v>
@@ -6838,10 +6829,10 @@
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>229</v>
+        <v>155</v>
       </c>
       <c r="B415" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C415" t="s">
         <v>105</v>
@@ -6849,10 +6840,10 @@
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>460</v>
+        <v>155</v>
       </c>
       <c r="B416" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C416" t="s">
         <v>105</v>
@@ -6860,7 +6851,7 @@
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B417" t="s">
         <v>16</v>
@@ -6871,7 +6862,7 @@
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B418" t="s">
         <v>16</v>
@@ -6882,7 +6873,7 @@
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B419" t="s">
         <v>16</v>
@@ -6893,7 +6884,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B420" t="s">
         <v>16</v>
@@ -6904,7 +6895,7 @@
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B421" t="s">
         <v>16</v>
@@ -6915,7 +6906,7 @@
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B422" t="s">
         <v>16</v>
@@ -6926,7 +6917,7 @@
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B423" t="s">
         <v>16</v>
@@ -6937,7 +6928,7 @@
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B424" t="s">
         <v>16</v>
@@ -6948,7 +6939,7 @@
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B425" t="s">
         <v>16</v>
@@ -6959,7 +6950,7 @@
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B426" t="s">
         <v>16</v>
@@ -6970,7 +6961,7 @@
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B427" t="s">
         <v>16</v>
@@ -6981,7 +6972,7 @@
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B428" t="s">
         <v>16</v>
@@ -6992,7 +6983,7 @@
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B429" t="s">
         <v>16</v>
@@ -7003,7 +6994,7 @@
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B430" t="s">
         <v>16</v>
@@ -7014,7 +7005,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B431" t="s">
         <v>16</v>
@@ -7025,7 +7016,7 @@
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B432" t="s">
         <v>16</v>
@@ -7036,7 +7027,7 @@
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>170</v>
+        <v>458</v>
       </c>
       <c r="B433" t="s">
         <v>16</v>
@@ -7047,7 +7038,7 @@
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>171</v>
+        <v>459</v>
       </c>
       <c r="B434" t="s">
         <v>16</v>
@@ -7058,7 +7049,7 @@
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B435" t="s">
         <v>16</v>
@@ -7069,7 +7060,7 @@
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>462</v>
+        <v>172</v>
       </c>
       <c r="B436" t="s">
         <v>16</v>
@@ -7080,7 +7071,7 @@
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>463</v>
+        <v>173</v>
       </c>
       <c r="B437" t="s">
         <v>16</v>
@@ -7091,7 +7082,7 @@
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>172</v>
+        <v>461</v>
       </c>
       <c r="B438" t="s">
         <v>16</v>
@@ -7102,7 +7093,7 @@
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>173</v>
+        <v>462</v>
       </c>
       <c r="B439" t="s">
         <v>16</v>
@@ -7113,10 +7104,10 @@
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
+        <v>463</v>
+      </c>
+      <c r="B440" t="s">
         <v>464</v>
-      </c>
-      <c r="B440" t="s">
-        <v>16</v>
       </c>
       <c r="C440" t="s">
         <v>105</v>
@@ -7127,7 +7118,7 @@
         <v>465</v>
       </c>
       <c r="B441" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C441" t="s">
         <v>105</v>
@@ -7138,7 +7129,7 @@
         <v>466</v>
       </c>
       <c r="B442" t="s">
-        <v>467</v>
+        <v>16</v>
       </c>
       <c r="C442" t="s">
         <v>105</v>
@@ -7146,10 +7137,10 @@
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B443" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C443" t="s">
         <v>105</v>
@@ -7157,10 +7148,10 @@
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B444" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C444" t="s">
         <v>105</v>
@@ -7168,10 +7159,10 @@
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>470</v>
+        <v>174</v>
       </c>
       <c r="B445" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C445" t="s">
         <v>105</v>
@@ -7179,10 +7170,10 @@
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>471</v>
+        <v>250</v>
       </c>
       <c r="B446" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C446" t="s">
         <v>105</v>
@@ -7190,10 +7181,10 @@
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B447" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C447" t="s">
         <v>105</v>
@@ -7201,10 +7192,10 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>251</v>
+        <v>176</v>
       </c>
       <c r="B448" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C448" t="s">
         <v>105</v>
@@ -7212,10 +7203,10 @@
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B449" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C449" t="s">
         <v>105</v>
@@ -7223,7 +7214,7 @@
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B450" t="s">
         <v>54</v>
@@ -7234,7 +7225,7 @@
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B451" t="s">
         <v>54</v>
@@ -7245,7 +7236,7 @@
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>178</v>
+        <v>536</v>
       </c>
       <c r="B452" t="s">
         <v>54</v>
@@ -7256,10 +7247,10 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>179</v>
+        <v>469</v>
       </c>
       <c r="B453" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C453" t="s">
         <v>105</v>
@@ -7267,10 +7258,10 @@
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>539</v>
+        <v>180</v>
       </c>
       <c r="B454" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C454" t="s">
         <v>105</v>
@@ -7278,10 +7269,10 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B455" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="C455" t="s">
         <v>105</v>
@@ -7289,10 +7280,10 @@
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>180</v>
+        <v>471</v>
       </c>
       <c r="B456" t="s">
-        <v>45</v>
+        <v>535</v>
       </c>
       <c r="C456" t="s">
         <v>105</v>
@@ -7300,10 +7291,10 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>473</v>
+        <v>181</v>
       </c>
       <c r="B457" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C457" t="s">
         <v>105</v>
@@ -7311,10 +7302,10 @@
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>474</v>
+        <v>182</v>
       </c>
       <c r="B458" t="s">
-        <v>538</v>
+        <v>16</v>
       </c>
       <c r="C458" t="s">
         <v>105</v>
@@ -7322,7 +7313,7 @@
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B459" t="s">
         <v>16</v>
@@ -7333,7 +7324,7 @@
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B460" t="s">
         <v>16</v>
@@ -7344,7 +7335,7 @@
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B461" t="s">
         <v>16</v>
@@ -7355,7 +7346,7 @@
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B462" t="s">
         <v>16</v>
@@ -7366,7 +7357,7 @@
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B463" t="s">
         <v>16</v>
@@ -7377,7 +7368,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B464" t="s">
         <v>16</v>
@@ -7388,10 +7379,10 @@
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B465" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C465" t="s">
         <v>105</v>
@@ -7399,10 +7390,10 @@
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B466" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C466" t="s">
         <v>105</v>
@@ -7410,7 +7401,7 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B467" t="s">
         <v>13</v>
@@ -7421,7 +7412,7 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>189</v>
+        <v>472</v>
       </c>
       <c r="B468" t="s">
         <v>13</v>
@@ -7432,7 +7423,7 @@
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B469" t="s">
         <v>13</v>
@@ -7443,7 +7434,7 @@
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>475</v>
+        <v>192</v>
       </c>
       <c r="B470" t="s">
         <v>13</v>
@@ -7454,7 +7445,7 @@
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>191</v>
+        <v>473</v>
       </c>
       <c r="B471" t="s">
         <v>13</v>
@@ -7465,10 +7456,10 @@
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>192</v>
+        <v>474</v>
       </c>
       <c r="B472" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C472" t="s">
         <v>105</v>
@@ -7476,10 +7467,10 @@
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B473" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C473" t="s">
         <v>105</v>
@@ -7487,7 +7478,7 @@
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B474" t="s">
         <v>7</v>
@@ -7498,10 +7489,10 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>478</v>
+        <v>230</v>
       </c>
       <c r="B475" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C475" t="s">
         <v>105</v>
@@ -7509,10 +7500,10 @@
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>479</v>
+        <v>229</v>
       </c>
       <c r="B476" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C476" t="s">
         <v>105</v>
@@ -7520,7 +7511,7 @@
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>231</v>
+        <v>580</v>
       </c>
       <c r="B477" t="s">
         <v>13</v>
@@ -7531,7 +7522,7 @@
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="B478" t="s">
         <v>13</v>
@@ -7542,7 +7533,7 @@
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>584</v>
+        <v>194</v>
       </c>
       <c r="B479" t="s">
         <v>13</v>
@@ -7553,7 +7544,7 @@
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B480" t="s">
         <v>13</v>
@@ -7564,7 +7555,7 @@
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B481" t="s">
         <v>13</v>
@@ -7575,7 +7566,7 @@
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B482" t="s">
         <v>13</v>
@@ -7586,7 +7577,7 @@
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>196</v>
+        <v>581</v>
       </c>
       <c r="B483" t="s">
         <v>13</v>
@@ -7597,7 +7588,7 @@
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>197</v>
+        <v>477</v>
       </c>
       <c r="B484" t="s">
         <v>13</v>
@@ -7608,7 +7599,7 @@
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>585</v>
+        <v>198</v>
       </c>
       <c r="B485" t="s">
         <v>13</v>
@@ -7619,7 +7610,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>198</v>
+        <v>478</v>
       </c>
       <c r="B486" t="s">
         <v>13</v>
@@ -7630,7 +7621,7 @@
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>480</v>
+        <v>199</v>
       </c>
       <c r="B487" t="s">
         <v>13</v>
@@ -7641,7 +7632,7 @@
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>199</v>
+        <v>479</v>
       </c>
       <c r="B488" t="s">
         <v>13</v>
@@ -7652,7 +7643,7 @@
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B489" t="s">
         <v>13</v>
@@ -7663,10 +7654,10 @@
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>200</v>
+        <v>481</v>
       </c>
       <c r="B490" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C490" t="s">
         <v>105</v>
@@ -7674,10 +7665,10 @@
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>482</v>
+        <v>200</v>
       </c>
       <c r="B491" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C491" t="s">
         <v>105</v>
@@ -7685,10 +7676,10 @@
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>483</v>
+        <v>201</v>
       </c>
       <c r="B492" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C492" t="s">
         <v>105</v>
@@ -7696,10 +7687,10 @@
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>484</v>
+        <v>202</v>
       </c>
       <c r="B493" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C493" t="s">
         <v>105</v>
@@ -7707,7 +7698,7 @@
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>201</v>
+        <v>582</v>
       </c>
       <c r="B494" t="s">
         <v>11</v>
@@ -7718,7 +7709,7 @@
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B495" t="s">
         <v>11</v>
@@ -7729,7 +7720,7 @@
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B496" t="s">
         <v>11</v>
@@ -7740,7 +7731,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B497" t="s">
         <v>11</v>
@@ -7751,7 +7742,7 @@
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B498" t="s">
         <v>11</v>
@@ -7762,7 +7753,7 @@
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B499" t="s">
         <v>11</v>
@@ -7773,7 +7764,7 @@
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>587</v>
+        <v>270</v>
       </c>
       <c r="B500" t="s">
         <v>11</v>
@@ -7784,7 +7775,7 @@
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>206</v>
+        <v>482</v>
       </c>
       <c r="B501" t="s">
         <v>11</v>
@@ -7795,7 +7786,7 @@
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>207</v>
+        <v>483</v>
       </c>
       <c r="B502" t="s">
         <v>11</v>
@@ -7806,7 +7797,7 @@
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>271</v>
+        <v>484</v>
       </c>
       <c r="B503" t="s">
         <v>11</v>
@@ -7817,7 +7808,7 @@
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>485</v>
+        <v>429</v>
       </c>
       <c r="B504" t="s">
         <v>11</v>
@@ -7828,7 +7819,7 @@
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>486</v>
+        <v>584</v>
       </c>
       <c r="B505" t="s">
         <v>11</v>
@@ -7839,7 +7830,7 @@
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>487</v>
+        <v>207</v>
       </c>
       <c r="B506" t="s">
         <v>11</v>
@@ -7850,7 +7841,7 @@
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>432</v>
+        <v>585</v>
       </c>
       <c r="B507" t="s">
         <v>11</v>
@@ -7861,7 +7852,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>588</v>
+        <v>208</v>
       </c>
       <c r="B508" t="s">
         <v>11</v>
@@ -7872,7 +7863,7 @@
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B509" t="s">
         <v>11</v>
@@ -7883,7 +7874,7 @@
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>589</v>
+        <v>210</v>
       </c>
       <c r="B510" t="s">
         <v>11</v>
@@ -7894,7 +7885,7 @@
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>209</v>
+        <v>586</v>
       </c>
       <c r="B511" t="s">
         <v>11</v>
@@ -7905,7 +7896,7 @@
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>210</v>
+        <v>587</v>
       </c>
       <c r="B512" t="s">
         <v>11</v>
@@ -7916,10 +7907,10 @@
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>211</v>
+        <v>485</v>
       </c>
       <c r="B513" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C513" t="s">
         <v>105</v>
@@ -7927,10 +7918,10 @@
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>590</v>
+        <v>211</v>
       </c>
       <c r="B514" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C514" t="s">
         <v>105</v>
@@ -7938,10 +7929,10 @@
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>591</v>
+        <v>212</v>
       </c>
       <c r="B515" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C515" t="s">
         <v>105</v>
@@ -7949,7 +7940,7 @@
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>488</v>
+        <v>213</v>
       </c>
       <c r="B516" t="s">
         <v>45</v>
@@ -7960,7 +7951,7 @@
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B517" t="s">
         <v>45</v>
@@ -7971,7 +7962,7 @@
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B518" t="s">
         <v>45</v>
@@ -7982,7 +7973,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B519" t="s">
         <v>45</v>
@@ -7993,7 +7984,7 @@
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B520" t="s">
         <v>45</v>
@@ -8004,7 +7995,7 @@
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>216</v>
+        <v>486</v>
       </c>
       <c r="B521" t="s">
         <v>45</v>
@@ -8015,7 +8006,7 @@
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>217</v>
+        <v>487</v>
       </c>
       <c r="B522" t="s">
         <v>45</v>
@@ -8026,7 +8017,7 @@
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>218</v>
+        <v>488</v>
       </c>
       <c r="B523" t="s">
         <v>45</v>
@@ -8040,7 +8031,7 @@
         <v>489</v>
       </c>
       <c r="B524" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C524" t="s">
         <v>105</v>
@@ -8051,7 +8042,7 @@
         <v>490</v>
       </c>
       <c r="B525" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C525" t="s">
         <v>105</v>
@@ -8062,7 +8053,7 @@
         <v>491</v>
       </c>
       <c r="B526" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C526" t="s">
         <v>105</v>
@@ -8081,10 +8072,10 @@
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>493</v>
+        <v>218</v>
       </c>
       <c r="B528" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C528" t="s">
         <v>105</v>
@@ -8092,57 +8083,57 @@
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>494</v>
+        <v>219</v>
       </c>
       <c r="B529" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C529" t="s">
-        <v>105</v>
+        <v>220</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>495</v>
+        <v>221</v>
       </c>
       <c r="B530" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C530" t="s">
-        <v>105</v>
+        <v>220</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B531" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C531" t="s">
-        <v>105</v>
+        <v>220</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
+        <v>223</v>
+      </c>
+      <c r="B532" t="s">
+        <v>11</v>
+      </c>
+      <c r="C532" t="s">
         <v>220</v>
-      </c>
-      <c r="B532" t="s">
-        <v>4</v>
-      </c>
-      <c r="C532" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>222</v>
+        <v>588</v>
       </c>
       <c r="B533" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C533" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.35">
@@ -8150,10 +8141,10 @@
         <v>223</v>
       </c>
       <c r="B534" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C534" t="s">
-        <v>221</v>
+        <v>589</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.35">
@@ -8161,40 +8152,40 @@
         <v>224</v>
       </c>
       <c r="B535" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C535" t="s">
-        <v>221</v>
+        <v>97</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>592</v>
+        <v>225</v>
       </c>
       <c r="B536" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C536" t="s">
-        <v>221</v>
+        <v>97</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B537" t="s">
-        <v>11</v>
+        <v>227</v>
       </c>
       <c r="C537" t="s">
-        <v>593</v>
+        <v>97</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="B538" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C538" t="s">
         <v>97</v>
@@ -8202,10 +8193,10 @@
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>226</v>
+        <v>590</v>
       </c>
       <c r="B539" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C539" t="s">
         <v>97</v>
@@ -8213,10 +8204,10 @@
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>227</v>
+        <v>267</v>
       </c>
       <c r="B540" t="s">
-        <v>228</v>
+        <v>11</v>
       </c>
       <c r="C540" t="s">
         <v>97</v>
@@ -8224,7 +8215,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>267</v>
+        <v>96</v>
       </c>
       <c r="B541" t="s">
         <v>11</v>
@@ -8235,7 +8226,7 @@
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>594</v>
+        <v>96</v>
       </c>
       <c r="B542" t="s">
         <v>11</v>
@@ -8246,10 +8237,10 @@
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="B543" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C543" t="s">
         <v>97</v>
@@ -8257,10 +8248,10 @@
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>96</v>
+        <v>246</v>
       </c>
       <c r="B544" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C544" t="s">
         <v>97</v>
@@ -8268,46 +8259,46 @@
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>96</v>
+        <v>493</v>
       </c>
       <c r="B545" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C545" t="s">
-        <v>97</v>
+        <v>494</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>246</v>
+        <v>495</v>
       </c>
       <c r="B546" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C546" t="s">
-        <v>97</v>
+        <v>494</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>247</v>
+        <v>496</v>
       </c>
       <c r="B547" t="s">
         <v>45</v>
       </c>
       <c r="C547" t="s">
-        <v>97</v>
+        <v>494</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B548" t="s">
         <v>45</v>
       </c>
       <c r="C548" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.35">
@@ -8315,10 +8306,10 @@
         <v>498</v>
       </c>
       <c r="B549" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C549" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.35">
@@ -8326,10 +8317,10 @@
         <v>499</v>
       </c>
       <c r="B550" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C550" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.35">
@@ -8337,10 +8328,10 @@
         <v>500</v>
       </c>
       <c r="B551" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C551" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.35">
@@ -8348,10 +8339,10 @@
         <v>501</v>
       </c>
       <c r="B552" t="s">
-        <v>13</v>
+        <v>464</v>
       </c>
       <c r="C552" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.35">
@@ -8359,10 +8350,10 @@
         <v>502</v>
       </c>
       <c r="B553" t="s">
-        <v>13</v>
+        <v>464</v>
       </c>
       <c r="C553" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.35">
@@ -8370,10 +8361,10 @@
         <v>503</v>
       </c>
       <c r="B554" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C554" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.35">
@@ -8381,10 +8372,10 @@
         <v>504</v>
       </c>
       <c r="B555" t="s">
-        <v>467</v>
+        <v>4</v>
       </c>
       <c r="C555" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.35">
@@ -8392,10 +8383,10 @@
         <v>505</v>
       </c>
       <c r="B556" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C556" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.35">
@@ -8403,10 +8394,10 @@
         <v>506</v>
       </c>
       <c r="B557" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="C557" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.35">
@@ -8414,10 +8405,10 @@
         <v>507</v>
       </c>
       <c r="B558" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C558" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.35">
@@ -8425,10 +8416,10 @@
         <v>508</v>
       </c>
       <c r="B559" t="s">
-        <v>467</v>
+        <v>16</v>
       </c>
       <c r="C559" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.35">
@@ -8436,10 +8427,10 @@
         <v>509</v>
       </c>
       <c r="B560" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C560" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.35">
@@ -8447,10 +8438,10 @@
         <v>510</v>
       </c>
       <c r="B561" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C561" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.35">
@@ -8458,10 +8449,10 @@
         <v>511</v>
       </c>
       <c r="B562" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C562" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.35">
@@ -8469,54 +8460,54 @@
         <v>512</v>
       </c>
       <c r="B563" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C563" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>513</v>
+        <v>591</v>
       </c>
       <c r="B564" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C564" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B565" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C565" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B566" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C566" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>595</v>
+        <v>515</v>
       </c>
       <c r="B567" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C567" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.35">
@@ -8524,43 +8515,43 @@
         <v>516</v>
       </c>
       <c r="B568" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C568" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B569" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C569" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B570" t="s">
         <v>16</v>
       </c>
       <c r="C570" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B571" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C571" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.35">
@@ -8568,10 +8559,10 @@
         <v>519</v>
       </c>
       <c r="B572" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C572" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.35">
@@ -8582,7 +8573,7 @@
         <v>16</v>
       </c>
       <c r="C573" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.35">
@@ -8590,10 +8581,10 @@
         <v>521</v>
       </c>
       <c r="B574" t="s">
-        <v>45</v>
+        <v>227</v>
       </c>
       <c r="C574" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.35">
@@ -8601,10 +8592,10 @@
         <v>522</v>
       </c>
       <c r="B575" t="s">
-        <v>45</v>
+        <v>535</v>
       </c>
       <c r="C575" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.35">
@@ -8612,10 +8603,10 @@
         <v>523</v>
       </c>
       <c r="B576" t="s">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="C576" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.35">
@@ -8623,10 +8614,10 @@
         <v>524</v>
       </c>
       <c r="B577" t="s">
-        <v>228</v>
+        <v>4</v>
       </c>
       <c r="C577" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.35">
@@ -8634,10 +8625,10 @@
         <v>525</v>
       </c>
       <c r="B578" t="s">
-        <v>538</v>
+        <v>13</v>
       </c>
       <c r="C578" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.35">
@@ -8645,10 +8636,10 @@
         <v>526</v>
       </c>
       <c r="B579" t="s">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="C579" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.35">
@@ -8656,10 +8647,10 @@
         <v>527</v>
       </c>
       <c r="B580" t="s">
-        <v>4</v>
+        <v>295</v>
       </c>
       <c r="C580" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.35">
@@ -8667,43 +8658,43 @@
         <v>528</v>
       </c>
       <c r="B581" t="s">
-        <v>13</v>
+        <v>529</v>
       </c>
       <c r="C581" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B582" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C582" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B583" t="s">
-        <v>296</v>
+        <v>13</v>
       </c>
       <c r="C583" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B584" t="s">
-        <v>532</v>
+        <v>13</v>
       </c>
       <c r="C584" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.35">
@@ -8714,43 +8705,11 @@
         <v>13</v>
       </c>
       <c r="C585" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A586" t="s">
-        <v>534</v>
-      </c>
-      <c r="B586" t="s">
-        <v>13</v>
-      </c>
-      <c r="C586" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A587" t="s">
-        <v>535</v>
-      </c>
-      <c r="B587" t="s">
-        <v>13</v>
-      </c>
-      <c r="C587" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A588" t="s">
-        <v>536</v>
-      </c>
-      <c r="B588" t="s">
-        <v>13</v>
-      </c>
-      <c r="C588" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C585" xr:uid="{4C50DCCC-8446-4FAC-BA76-D53F2D86B716}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C273">
     <sortCondition ref="C1:C273"/>
   </sortState>
